--- a/Testcase-OrangeHRM.xlsx
+++ b/Testcase-OrangeHRM.xlsx
@@ -9,8 +9,7 @@
     <sheet state="visible" name="Danh sách nhân viên" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'Đăng nhập'!$A$2:$J$27</definedName>
-    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'Quản lý người dùng'!$A$2:$J$28</definedName>
+    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'Quản lý người dùng'!$A$2:$J$29</definedName>
     <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">'Danh sách nhân viên'!$A$2:$J$29</definedName>
   </definedNames>
   <calcPr/>
@@ -18,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="461">
   <si>
     <t>MA TRẬN KIỂM THỬ – KIỂM THỬ TỰ ĐỘNG ORANGEHRM (Playwright)</t>
   </si>
@@ -561,6 +560,9 @@
     <t>Bảng danh sách hiển thị với các cột: Tên tài khoản, Vai trò, Tên nhân viên, Trạng thái</t>
   </si>
   <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>Kiểm tra 4 tiêu đề cột tồn tại</t>
   </si>
   <si>
@@ -705,10 +707,30 @@
     <t>Kiểm tra ô tìm kiếm đã trống sau khi xóa bộ lọc</t>
   </si>
   <si>
+    <t>TC-U08</t>
+  </si>
+  <si>
+    <t>Tìm kiếm tên tài khoản chỉ gồm khoảng trắng</t>
+  </si>
+  <si>
+    <t>Hệ thống không trả về kết quả khi từ khóa tìm kiếm chỉ là khoảng trắng</t>
+  </si>
+  <si>
+    <t>1. Vào Quản lý người dùng
+2. Nhập 3 dấu cách vào ô Tên tài khoản
+3. Nhấn Tìm kiếm</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Trung bình</t>
+  </si>
+  <si>
+    <t>Observed on 2026-06-06: nhập khoảng trắng và Search vẫn hiển thị (10) Records Found</t>
+  </si>
+  <si>
     <t>Thêm người dùng mới</t>
-  </si>
-  <si>
-    <t>TC-U08</t>
   </si>
   <si>
     <t>Thêm người dùng mới với thông tin đầy đủ và hợp lệ</t>
@@ -1687,7 +1709,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -1757,6 +1779,11 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1962,7 +1989,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="47">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2009,6 +2036,9 @@
     <xf borderId="1" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="4" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="8" fillId="10" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2017,14 +2047,14 @@
     <xf borderId="11" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="11" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="11" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="11" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="11" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -2059,8 +2089,23 @@
     <xf borderId="4" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="12" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -3518,8 +3563,7 @@
     <col customWidth="1" min="4" max="4" width="28.0"/>
     <col customWidth="1" min="5" max="5" width="46.0"/>
     <col customWidth="1" min="6" max="6" width="44.0"/>
-    <col customWidth="1" min="7" max="7" width="20.0"/>
-    <col customWidth="1" min="8" max="8" width="14.0"/>
+    <col customWidth="1" min="7" max="8" width="20.0"/>
     <col customWidth="1" min="9" max="9" width="13.0"/>
     <col customWidth="1" min="10" max="10" width="34.0"/>
     <col customWidth="1" min="11" max="26" width="8.71"/>
@@ -3561,7 +3605,7 @@
       <c r="G2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="18" t="s">
         <v>41</v>
       </c>
       <c r="I2" s="5" t="s">
@@ -3572,46 +3616,46 @@
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="21"/>
     </row>
     <row r="4" ht="69.75" customHeight="1">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="21"/>
-      <c r="H4" s="22" t="s">
+      <c r="G4" s="22"/>
+      <c r="H4" s="9" t="s">
         <v>51</v>
       </c>
       <c r="I4" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="22" t="s">
         <v>53</v>
       </c>
     </row>
@@ -3635,7 +3679,7 @@
         <v>59</v>
       </c>
       <c r="G5" s="24"/>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="25" t="s">
         <v>51</v>
       </c>
       <c r="I5" s="23" t="s">
@@ -3646,32 +3690,32 @@
       </c>
     </row>
     <row r="6" ht="69.75" customHeight="1">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="21"/>
-      <c r="H6" s="22" t="s">
+      <c r="G6" s="22"/>
+      <c r="H6" s="25" t="s">
         <v>51</v>
       </c>
       <c r="I6" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="22" t="s">
         <v>67</v>
       </c>
     </row>
@@ -3695,7 +3739,7 @@
         <v>73</v>
       </c>
       <c r="G7" s="24"/>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="25" t="s">
         <v>51</v>
       </c>
       <c r="I7" s="23" t="s">
@@ -3706,32 +3750,32 @@
       </c>
     </row>
     <row r="8" ht="69.75" customHeight="1">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="21"/>
-      <c r="H8" s="22" t="s">
+      <c r="G8" s="22"/>
+      <c r="H8" s="25" t="s">
         <v>51</v>
       </c>
       <c r="I8" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="22" t="s">
         <v>81</v>
       </c>
     </row>
@@ -3755,7 +3799,7 @@
         <v>87</v>
       </c>
       <c r="G9" s="24"/>
-      <c r="H9" s="22" t="s">
+      <c r="H9" s="25" t="s">
         <v>51</v>
       </c>
       <c r="I9" s="23" t="s">
@@ -3766,18 +3810,18 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="29"/>
     </row>
     <row r="11" ht="69.75" customHeight="1">
       <c r="A11" s="24" t="s">
@@ -3799,7 +3843,7 @@
         <v>94</v>
       </c>
       <c r="G11" s="24"/>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="25" t="s">
         <v>51</v>
       </c>
       <c r="I11" s="23" t="s">
@@ -3810,32 +3854,32 @@
       </c>
     </row>
     <row r="12" ht="69.75" customHeight="1">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="F12" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="G12" s="21"/>
-      <c r="H12" s="29" t="s">
+      <c r="G12" s="22"/>
+      <c r="H12" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="I12" s="30" t="s">
+      <c r="I12" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="26" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3852,14 +3896,14 @@
       <c r="D13" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="32" t="s">
         <v>109</v>
       </c>
       <c r="F13" s="24" t="s">
         <v>110</v>
       </c>
       <c r="G13" s="24"/>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="25" t="s">
         <v>51</v>
       </c>
       <c r="I13" s="23" t="s">
@@ -3870,76 +3914,76 @@
       </c>
     </row>
     <row r="14" ht="69.75" customHeight="1">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="F14" s="25" t="s">
+      <c r="F14" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="G14" s="21"/>
-      <c r="H14" s="29" t="s">
+      <c r="G14" s="22"/>
+      <c r="H14" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="I14" s="30" t="s">
+      <c r="I14" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="26" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="28"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="29"/>
     </row>
     <row r="16" ht="69.75" customHeight="1">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="E16" s="21" t="s">
+      <c r="E16" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="F16" s="21" t="s">
+      <c r="F16" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="G16" s="21"/>
-      <c r="H16" s="22" t="s">
+      <c r="G16" s="22"/>
+      <c r="H16" s="25" t="s">
         <v>51</v>
       </c>
       <c r="I16" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="J16" s="21" t="s">
+      <c r="J16" s="22" t="s">
         <v>126</v>
       </c>
     </row>
@@ -3963,7 +4007,7 @@
         <v>131</v>
       </c>
       <c r="G17" s="24"/>
-      <c r="H17" s="22" t="s">
+      <c r="H17" s="25" t="s">
         <v>51</v>
       </c>
       <c r="I17" s="23" t="s">
@@ -3974,32 +4018,32 @@
       </c>
     </row>
     <row r="18" ht="69.75" customHeight="1">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="E18" s="21" t="s">
+      <c r="E18" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="F18" s="21" t="s">
+      <c r="F18" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="G18" s="21"/>
-      <c r="H18" s="22" t="s">
+      <c r="G18" s="22"/>
+      <c r="H18" s="25" t="s">
         <v>51</v>
       </c>
       <c r="I18" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="J18" s="21" t="s">
+      <c r="J18" s="22" t="s">
         <v>139</v>
       </c>
     </row>
@@ -4013,7 +4057,7 @@
       <c r="C19" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="D19" s="32" t="s">
         <v>143</v>
       </c>
       <c r="E19" s="24" t="s">
@@ -4023,7 +4067,7 @@
         <v>145</v>
       </c>
       <c r="G19" s="24"/>
-      <c r="H19" s="22" t="s">
+      <c r="H19" s="25" t="s">
         <v>51</v>
       </c>
       <c r="I19" s="23" t="s">
@@ -4034,118 +4078,118 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="33" t="s">
+      <c r="A20" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="28"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="29"/>
     </row>
     <row r="21" ht="69.75" customHeight="1">
       <c r="A21" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="D21" s="31" t="s">
+      <c r="D21" s="32" t="s">
         <v>151</v>
       </c>
-      <c r="E21" s="31" t="s">
+      <c r="E21" s="32" t="s">
         <v>152</v>
       </c>
-      <c r="F21" s="31" t="s">
+      <c r="F21" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="G21" s="31"/>
-      <c r="H21" s="22" t="s">
+      <c r="G21" s="32"/>
+      <c r="H21" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="I21" s="34" t="s">
+      <c r="I21" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="J21" s="31"/>
+      <c r="J21" s="32"/>
     </row>
     <row r="22" ht="69.75" customHeight="1">
-      <c r="A22" s="35"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
+      <c r="A22" s="36"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
     </row>
     <row r="23" ht="69.75" customHeight="1">
-      <c r="A23" s="35"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
+      <c r="A23" s="36"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
     </row>
     <row r="24" ht="69.75" customHeight="1">
-      <c r="A24" s="35"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="35"/>
+      <c r="A24" s="36"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="36"/>
     </row>
     <row r="25" ht="69.75" customHeight="1">
-      <c r="A25" s="35"/>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="35"/>
+      <c r="A25" s="36"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="36"/>
     </row>
     <row r="26" ht="69.75" customHeight="1">
-      <c r="A26" s="35"/>
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
+      <c r="A26" s="36"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="36"/>
+      <c r="J26" s="36"/>
     </row>
     <row r="27" ht="69.75" customHeight="1">
-      <c r="A27" s="35"/>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="35"/>
+      <c r="A27" s="36"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="36"/>
+      <c r="J27" s="36"/>
     </row>
     <row r="28" ht="15.75" customHeight="1"/>
     <row r="29" ht="15.75" customHeight="1"/>
@@ -5120,15 +5164,1019 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
+    <row r="1009" ht="15.75" customHeight="1"/>
+    <row r="1010" ht="15.75" customHeight="1"/>
+    <row r="1011" ht="15.75" customHeight="1"/>
+    <row r="1012" ht="15.75" customHeight="1"/>
+    <row r="1013" ht="15.75" customHeight="1"/>
+    <row r="1014" ht="15.75" customHeight="1"/>
+    <row r="1015" ht="15.75" customHeight="1"/>
+    <row r="1016" ht="15.75" customHeight="1"/>
+    <row r="1017" ht="15.75" customHeight="1"/>
+    <row r="1018" ht="15.75" customHeight="1"/>
+    <row r="1019" ht="15.75" customHeight="1"/>
+    <row r="1020" ht="15.75" customHeight="1"/>
+    <row r="1021" ht="15.75" customHeight="1"/>
+    <row r="1022" ht="15.75" customHeight="1"/>
+    <row r="1023" ht="15.75" customHeight="1"/>
+    <row r="1024" ht="15.75" customHeight="1"/>
+    <row r="1025" ht="15.75" customHeight="1"/>
+    <row r="1026" ht="15.75" customHeight="1"/>
+    <row r="1027" ht="15.75" customHeight="1"/>
+    <row r="1028" ht="15.75" customHeight="1"/>
+    <row r="1029" ht="15.75" customHeight="1"/>
+    <row r="1030" ht="15.75" customHeight="1"/>
+    <row r="1031" ht="15.75" customHeight="1"/>
+    <row r="1032" ht="15.75" customHeight="1"/>
+    <row r="1033" ht="15.75" customHeight="1"/>
+    <row r="1034" ht="15.75" customHeight="1"/>
+    <row r="1035" ht="15.75" customHeight="1"/>
+    <row r="1036" ht="15.75" customHeight="1"/>
+    <row r="1037" ht="15.75" customHeight="1"/>
+    <row r="1038" ht="15.75" customHeight="1"/>
+    <row r="1039" ht="15.75" customHeight="1"/>
+    <row r="1040" ht="15.75" customHeight="1"/>
+    <row r="1041" ht="15.75" customHeight="1"/>
+    <row r="1042" ht="15.75" customHeight="1"/>
+    <row r="1043" ht="15.75" customHeight="1"/>
+    <row r="1044" ht="15.75" customHeight="1"/>
+    <row r="1045" ht="15.75" customHeight="1"/>
+    <row r="1046" ht="15.75" customHeight="1"/>
+    <row r="1047" ht="15.75" customHeight="1"/>
+    <row r="1048" ht="15.75" customHeight="1"/>
+    <row r="1049" ht="15.75" customHeight="1"/>
+    <row r="1050" ht="15.75" customHeight="1"/>
+    <row r="1051" ht="15.75" customHeight="1"/>
+    <row r="1052" ht="15.75" customHeight="1"/>
+    <row r="1053" ht="15.75" customHeight="1"/>
+    <row r="1054" ht="15.75" customHeight="1"/>
+    <row r="1055" ht="15.75" customHeight="1"/>
+    <row r="1056" ht="15.75" customHeight="1"/>
+    <row r="1057" ht="15.75" customHeight="1"/>
+    <row r="1058" ht="15.75" customHeight="1"/>
+    <row r="1059" ht="15.75" customHeight="1"/>
+    <row r="1060" ht="15.75" customHeight="1"/>
+    <row r="1061" ht="15.75" customHeight="1"/>
+    <row r="1062" ht="15.75" customHeight="1"/>
+    <row r="1063" ht="15.75" customHeight="1"/>
+    <row r="1064" ht="15.75" customHeight="1"/>
+    <row r="1065" ht="15.75" customHeight="1"/>
+    <row r="1066" ht="15.75" customHeight="1"/>
+    <row r="1067" ht="15.75" customHeight="1"/>
+    <row r="1068" ht="15.75" customHeight="1"/>
+    <row r="1069" ht="15.75" customHeight="1"/>
+    <row r="1070" ht="15.75" customHeight="1"/>
+    <row r="1071" ht="15.75" customHeight="1"/>
+    <row r="1072" ht="15.75" customHeight="1"/>
+    <row r="1073" ht="15.75" customHeight="1"/>
+    <row r="1074" ht="15.75" customHeight="1"/>
+    <row r="1075" ht="15.75" customHeight="1"/>
+    <row r="1076" ht="15.75" customHeight="1"/>
+    <row r="1077" ht="15.75" customHeight="1"/>
+    <row r="1078" ht="15.75" customHeight="1"/>
+    <row r="1079" ht="15.75" customHeight="1"/>
+    <row r="1080" ht="15.75" customHeight="1"/>
+    <row r="1081" ht="15.75" customHeight="1"/>
+    <row r="1082" ht="15.75" customHeight="1"/>
+    <row r="1083" ht="15.75" customHeight="1"/>
+    <row r="1084" ht="15.75" customHeight="1"/>
+    <row r="1085" ht="15.75" customHeight="1"/>
+    <row r="1086" ht="15.75" customHeight="1"/>
+    <row r="1087" ht="15.75" customHeight="1"/>
+    <row r="1088" ht="15.75" customHeight="1"/>
+    <row r="1089" ht="15.75" customHeight="1"/>
+    <row r="1090" ht="15.75" customHeight="1"/>
+    <row r="1091" ht="15.75" customHeight="1"/>
+    <row r="1092" ht="15.75" customHeight="1"/>
+    <row r="1093" ht="15.75" customHeight="1"/>
+    <row r="1094" ht="15.75" customHeight="1"/>
+    <row r="1095" ht="15.75" customHeight="1"/>
+    <row r="1096" ht="15.75" customHeight="1"/>
+    <row r="1097" ht="15.75" customHeight="1"/>
+    <row r="1098" ht="15.75" customHeight="1"/>
+    <row r="1099" ht="15.75" customHeight="1"/>
+    <row r="1100" ht="15.75" customHeight="1"/>
+    <row r="1101" ht="15.75" customHeight="1"/>
+    <row r="1102" ht="15.75" customHeight="1"/>
+    <row r="1103" ht="15.75" customHeight="1"/>
+    <row r="1104" ht="15.75" customHeight="1"/>
+    <row r="1105" ht="15.75" customHeight="1"/>
+    <row r="1106" ht="15.75" customHeight="1"/>
+    <row r="1107" ht="15.75" customHeight="1"/>
+    <row r="1108" ht="15.75" customHeight="1"/>
+    <row r="1109" ht="15.75" customHeight="1"/>
+    <row r="1110" ht="15.75" customHeight="1"/>
+    <row r="1111" ht="15.75" customHeight="1"/>
+    <row r="1112" ht="15.75" customHeight="1"/>
+    <row r="1113" ht="15.75" customHeight="1"/>
+    <row r="1114" ht="15.75" customHeight="1"/>
+    <row r="1115" ht="15.75" customHeight="1"/>
+    <row r="1116" ht="15.75" customHeight="1"/>
+    <row r="1117" ht="15.75" customHeight="1"/>
+    <row r="1118" ht="15.75" customHeight="1"/>
+    <row r="1119" ht="15.75" customHeight="1"/>
+    <row r="1120" ht="15.75" customHeight="1"/>
+    <row r="1121" ht="15.75" customHeight="1"/>
+    <row r="1122" ht="15.75" customHeight="1"/>
+    <row r="1123" ht="15.75" customHeight="1"/>
+    <row r="1124" ht="15.75" customHeight="1"/>
+    <row r="1125" ht="15.75" customHeight="1"/>
+    <row r="1126" ht="15.75" customHeight="1"/>
+    <row r="1127" ht="15.75" customHeight="1"/>
+    <row r="1128" ht="15.75" customHeight="1"/>
+    <row r="1129" ht="15.75" customHeight="1"/>
+    <row r="1130" ht="15.75" customHeight="1"/>
+    <row r="1131" ht="15.75" customHeight="1"/>
+    <row r="1132" ht="15.75" customHeight="1"/>
+    <row r="1133" ht="15.75" customHeight="1"/>
+    <row r="1134" ht="15.75" customHeight="1"/>
+    <row r="1135" ht="15.75" customHeight="1"/>
+    <row r="1136" ht="15.75" customHeight="1"/>
+    <row r="1137" ht="15.75" customHeight="1"/>
+    <row r="1138" ht="15.75" customHeight="1"/>
+    <row r="1139" ht="15.75" customHeight="1"/>
+    <row r="1140" ht="15.75" customHeight="1"/>
+    <row r="1141" ht="15.75" customHeight="1"/>
+    <row r="1142" ht="15.75" customHeight="1"/>
+    <row r="1143" ht="15.75" customHeight="1"/>
+    <row r="1144" ht="15.75" customHeight="1"/>
+    <row r="1145" ht="15.75" customHeight="1"/>
+    <row r="1146" ht="15.75" customHeight="1"/>
+    <row r="1147" ht="15.75" customHeight="1"/>
+    <row r="1148" ht="15.75" customHeight="1"/>
+    <row r="1149" ht="15.75" customHeight="1"/>
+    <row r="1150" ht="15.75" customHeight="1"/>
+    <row r="1151" ht="15.75" customHeight="1"/>
+    <row r="1152" ht="15.75" customHeight="1"/>
+    <row r="1153" ht="15.75" customHeight="1"/>
+    <row r="1154" ht="15.75" customHeight="1"/>
+    <row r="1155" ht="15.75" customHeight="1"/>
+    <row r="1156" ht="15.75" customHeight="1"/>
+    <row r="1157" ht="15.75" customHeight="1"/>
+    <row r="1158" ht="15.75" customHeight="1"/>
+    <row r="1159" ht="15.75" customHeight="1"/>
+    <row r="1160" ht="15.75" customHeight="1"/>
+    <row r="1161" ht="15.75" customHeight="1"/>
+    <row r="1162" ht="15.75" customHeight="1"/>
+    <row r="1163" ht="15.75" customHeight="1"/>
+    <row r="1164" ht="15.75" customHeight="1"/>
+    <row r="1165" ht="15.75" customHeight="1"/>
+    <row r="1166" ht="15.75" customHeight="1"/>
+    <row r="1167" ht="15.75" customHeight="1"/>
+    <row r="1168" ht="15.75" customHeight="1"/>
+    <row r="1169" ht="15.75" customHeight="1"/>
+    <row r="1170" ht="15.75" customHeight="1"/>
+    <row r="1171" ht="15.75" customHeight="1"/>
+    <row r="1172" ht="15.75" customHeight="1"/>
+    <row r="1173" ht="15.75" customHeight="1"/>
+    <row r="1174" ht="15.75" customHeight="1"/>
+    <row r="1175" ht="15.75" customHeight="1"/>
+    <row r="1176" ht="15.75" customHeight="1"/>
+    <row r="1177" ht="15.75" customHeight="1"/>
+    <row r="1178" ht="15.75" customHeight="1"/>
+    <row r="1179" ht="15.75" customHeight="1"/>
+    <row r="1180" ht="15.75" customHeight="1"/>
+    <row r="1181" ht="15.75" customHeight="1"/>
+    <row r="1182" ht="15.75" customHeight="1"/>
+    <row r="1183" ht="15.75" customHeight="1"/>
+    <row r="1184" ht="15.75" customHeight="1"/>
+    <row r="1185" ht="15.75" customHeight="1"/>
+    <row r="1186" ht="15.75" customHeight="1"/>
+    <row r="1187" ht="15.75" customHeight="1"/>
+    <row r="1188" ht="15.75" customHeight="1"/>
+    <row r="1189" ht="15.75" customHeight="1"/>
+    <row r="1190" ht="15.75" customHeight="1"/>
+    <row r="1191" ht="15.75" customHeight="1"/>
+    <row r="1192" ht="15.75" customHeight="1"/>
+    <row r="1193" ht="15.75" customHeight="1"/>
+    <row r="1194" ht="15.75" customHeight="1"/>
+    <row r="1195" ht="15.75" customHeight="1"/>
+    <row r="1196" ht="15.75" customHeight="1"/>
+    <row r="1197" ht="15.75" customHeight="1"/>
+    <row r="1198" ht="15.75" customHeight="1"/>
+    <row r="1199" ht="15.75" customHeight="1"/>
+    <row r="1200" ht="15.75" customHeight="1"/>
+    <row r="1201" ht="15.75" customHeight="1"/>
+    <row r="1202" ht="15.75" customHeight="1"/>
+    <row r="1203" ht="15.75" customHeight="1"/>
+    <row r="1204" ht="15.75" customHeight="1"/>
+    <row r="1205" ht="15.75" customHeight="1"/>
+    <row r="1206" ht="15.75" customHeight="1"/>
+    <row r="1207" ht="15.75" customHeight="1"/>
+    <row r="1208" ht="15.75" customHeight="1"/>
+    <row r="1209" ht="15.75" customHeight="1"/>
+    <row r="1210" ht="15.75" customHeight="1"/>
+    <row r="1211" ht="15.75" customHeight="1"/>
+    <row r="1212" ht="15.75" customHeight="1"/>
+    <row r="1213" ht="15.75" customHeight="1"/>
+    <row r="1214" ht="15.75" customHeight="1"/>
+    <row r="1215" ht="15.75" customHeight="1"/>
+    <row r="1216" ht="15.75" customHeight="1"/>
+    <row r="1217" ht="15.75" customHeight="1"/>
+    <row r="1218" ht="15.75" customHeight="1"/>
+    <row r="1219" ht="15.75" customHeight="1"/>
+    <row r="1220" ht="15.75" customHeight="1"/>
+    <row r="1221" ht="15.75" customHeight="1"/>
+    <row r="1222" ht="15.75" customHeight="1"/>
+    <row r="1223" ht="15.75" customHeight="1"/>
+    <row r="1224" ht="15.75" customHeight="1"/>
+    <row r="1225" ht="15.75" customHeight="1"/>
+    <row r="1226" ht="15.75" customHeight="1"/>
+    <row r="1227" ht="15.75" customHeight="1"/>
+    <row r="1228" ht="15.75" customHeight="1"/>
+    <row r="1229" ht="15.75" customHeight="1"/>
+    <row r="1230" ht="15.75" customHeight="1"/>
+    <row r="1231" ht="15.75" customHeight="1"/>
+    <row r="1232" ht="15.75" customHeight="1"/>
+    <row r="1233" ht="15.75" customHeight="1"/>
+    <row r="1234" ht="15.75" customHeight="1"/>
+    <row r="1235" ht="15.75" customHeight="1"/>
+    <row r="1236" ht="15.75" customHeight="1"/>
+    <row r="1237" ht="15.75" customHeight="1"/>
+    <row r="1238" ht="15.75" customHeight="1"/>
+    <row r="1239" ht="15.75" customHeight="1"/>
+    <row r="1240" ht="15.75" customHeight="1"/>
+    <row r="1241" ht="15.75" customHeight="1"/>
+    <row r="1242" ht="15.75" customHeight="1"/>
+    <row r="1243" ht="15.75" customHeight="1"/>
+    <row r="1244" ht="15.75" customHeight="1"/>
+    <row r="1245" ht="15.75" customHeight="1"/>
+    <row r="1246" ht="15.75" customHeight="1"/>
+    <row r="1247" ht="15.75" customHeight="1"/>
+    <row r="1248" ht="15.75" customHeight="1"/>
+    <row r="1249" ht="15.75" customHeight="1"/>
+    <row r="1250" ht="15.75" customHeight="1"/>
+    <row r="1251" ht="15.75" customHeight="1"/>
+    <row r="1252" ht="15.75" customHeight="1"/>
+    <row r="1253" ht="15.75" customHeight="1"/>
+    <row r="1254" ht="15.75" customHeight="1"/>
+    <row r="1255" ht="15.75" customHeight="1"/>
+    <row r="1256" ht="15.75" customHeight="1"/>
+    <row r="1257" ht="15.75" customHeight="1"/>
+    <row r="1258" ht="15.75" customHeight="1"/>
+    <row r="1259" ht="15.75" customHeight="1"/>
+    <row r="1260" ht="15.75" customHeight="1"/>
+    <row r="1261" ht="15.75" customHeight="1"/>
+    <row r="1262" ht="15.75" customHeight="1"/>
+    <row r="1263" ht="15.75" customHeight="1"/>
+    <row r="1264" ht="15.75" customHeight="1"/>
+    <row r="1265" ht="15.75" customHeight="1"/>
+    <row r="1266" ht="15.75" customHeight="1"/>
+    <row r="1267" ht="15.75" customHeight="1"/>
+    <row r="1268" ht="15.75" customHeight="1"/>
+    <row r="1269" ht="15.75" customHeight="1"/>
+    <row r="1270" ht="15.75" customHeight="1"/>
+    <row r="1271" ht="15.75" customHeight="1"/>
+    <row r="1272" ht="15.75" customHeight="1"/>
+    <row r="1273" ht="15.75" customHeight="1"/>
+    <row r="1274" ht="15.75" customHeight="1"/>
+    <row r="1275" ht="15.75" customHeight="1"/>
+    <row r="1276" ht="15.75" customHeight="1"/>
+    <row r="1277" ht="15.75" customHeight="1"/>
+    <row r="1278" ht="15.75" customHeight="1"/>
+    <row r="1279" ht="15.75" customHeight="1"/>
+    <row r="1280" ht="15.75" customHeight="1"/>
+    <row r="1281" ht="15.75" customHeight="1"/>
+    <row r="1282" ht="15.75" customHeight="1"/>
+    <row r="1283" ht="15.75" customHeight="1"/>
+    <row r="1284" ht="15.75" customHeight="1"/>
+    <row r="1285" ht="15.75" customHeight="1"/>
+    <row r="1286" ht="15.75" customHeight="1"/>
+    <row r="1287" ht="15.75" customHeight="1"/>
+    <row r="1288" ht="15.75" customHeight="1"/>
+    <row r="1289" ht="15.75" customHeight="1"/>
+    <row r="1290" ht="15.75" customHeight="1"/>
+    <row r="1291" ht="15.75" customHeight="1"/>
+    <row r="1292" ht="15.75" customHeight="1"/>
+    <row r="1293" ht="15.75" customHeight="1"/>
+    <row r="1294" ht="15.75" customHeight="1"/>
+    <row r="1295" ht="15.75" customHeight="1"/>
+    <row r="1296" ht="15.75" customHeight="1"/>
+    <row r="1297" ht="15.75" customHeight="1"/>
+    <row r="1298" ht="15.75" customHeight="1"/>
+    <row r="1299" ht="15.75" customHeight="1"/>
+    <row r="1300" ht="15.75" customHeight="1"/>
+    <row r="1301" ht="15.75" customHeight="1"/>
+    <row r="1302" ht="15.75" customHeight="1"/>
+    <row r="1303" ht="15.75" customHeight="1"/>
+    <row r="1304" ht="15.75" customHeight="1"/>
+    <row r="1305" ht="15.75" customHeight="1"/>
+    <row r="1306" ht="15.75" customHeight="1"/>
+    <row r="1307" ht="15.75" customHeight="1"/>
+    <row r="1308" ht="15.75" customHeight="1"/>
+    <row r="1309" ht="15.75" customHeight="1"/>
+    <row r="1310" ht="15.75" customHeight="1"/>
+    <row r="1311" ht="15.75" customHeight="1"/>
+    <row r="1312" ht="15.75" customHeight="1"/>
+    <row r="1313" ht="15.75" customHeight="1"/>
+    <row r="1314" ht="15.75" customHeight="1"/>
+    <row r="1315" ht="15.75" customHeight="1"/>
+    <row r="1316" ht="15.75" customHeight="1"/>
+    <row r="1317" ht="15.75" customHeight="1"/>
+    <row r="1318" ht="15.75" customHeight="1"/>
+    <row r="1319" ht="15.75" customHeight="1"/>
+    <row r="1320" ht="15.75" customHeight="1"/>
+    <row r="1321" ht="15.75" customHeight="1"/>
+    <row r="1322" ht="15.75" customHeight="1"/>
+    <row r="1323" ht="15.75" customHeight="1"/>
+    <row r="1324" ht="15.75" customHeight="1"/>
+    <row r="1325" ht="15.75" customHeight="1"/>
+    <row r="1326" ht="15.75" customHeight="1"/>
+    <row r="1327" ht="15.75" customHeight="1"/>
+    <row r="1328" ht="15.75" customHeight="1"/>
+    <row r="1329" ht="15.75" customHeight="1"/>
+    <row r="1330" ht="15.75" customHeight="1"/>
+    <row r="1331" ht="15.75" customHeight="1"/>
+    <row r="1332" ht="15.75" customHeight="1"/>
+    <row r="1333" ht="15.75" customHeight="1"/>
+    <row r="1334" ht="15.75" customHeight="1"/>
+    <row r="1335" ht="15.75" customHeight="1"/>
+    <row r="1336" ht="15.75" customHeight="1"/>
+    <row r="1337" ht="15.75" customHeight="1"/>
+    <row r="1338" ht="15.75" customHeight="1"/>
+    <row r="1339" ht="15.75" customHeight="1"/>
+    <row r="1340" ht="15.75" customHeight="1"/>
+    <row r="1341" ht="15.75" customHeight="1"/>
+    <row r="1342" ht="15.75" customHeight="1"/>
+    <row r="1343" ht="15.75" customHeight="1"/>
+    <row r="1344" ht="15.75" customHeight="1"/>
+    <row r="1345" ht="15.75" customHeight="1"/>
+    <row r="1346" ht="15.75" customHeight="1"/>
+    <row r="1347" ht="15.75" customHeight="1"/>
+    <row r="1348" ht="15.75" customHeight="1"/>
+    <row r="1349" ht="15.75" customHeight="1"/>
+    <row r="1350" ht="15.75" customHeight="1"/>
+    <row r="1351" ht="15.75" customHeight="1"/>
+    <row r="1352" ht="15.75" customHeight="1"/>
+    <row r="1353" ht="15.75" customHeight="1"/>
+    <row r="1354" ht="15.75" customHeight="1"/>
+    <row r="1355" ht="15.75" customHeight="1"/>
+    <row r="1356" ht="15.75" customHeight="1"/>
+    <row r="1357" ht="15.75" customHeight="1"/>
+    <row r="1358" ht="15.75" customHeight="1"/>
+    <row r="1359" ht="15.75" customHeight="1"/>
+    <row r="1360" ht="15.75" customHeight="1"/>
+    <row r="1361" ht="15.75" customHeight="1"/>
+    <row r="1362" ht="15.75" customHeight="1"/>
+    <row r="1363" ht="15.75" customHeight="1"/>
+    <row r="1364" ht="15.75" customHeight="1"/>
+    <row r="1365" ht="15.75" customHeight="1"/>
+    <row r="1366" ht="15.75" customHeight="1"/>
+    <row r="1367" ht="15.75" customHeight="1"/>
+    <row r="1368" ht="15.75" customHeight="1"/>
+    <row r="1369" ht="15.75" customHeight="1"/>
+    <row r="1370" ht="15.75" customHeight="1"/>
+    <row r="1371" ht="15.75" customHeight="1"/>
+    <row r="1372" ht="15.75" customHeight="1"/>
+    <row r="1373" ht="15.75" customHeight="1"/>
+    <row r="1374" ht="15.75" customHeight="1"/>
+    <row r="1375" ht="15.75" customHeight="1"/>
+    <row r="1376" ht="15.75" customHeight="1"/>
+    <row r="1377" ht="15.75" customHeight="1"/>
+    <row r="1378" ht="15.75" customHeight="1"/>
+    <row r="1379" ht="15.75" customHeight="1"/>
+    <row r="1380" ht="15.75" customHeight="1"/>
+    <row r="1381" ht="15.75" customHeight="1"/>
+    <row r="1382" ht="15.75" customHeight="1"/>
+    <row r="1383" ht="15.75" customHeight="1"/>
+    <row r="1384" ht="15.75" customHeight="1"/>
+    <row r="1385" ht="15.75" customHeight="1"/>
+    <row r="1386" ht="15.75" customHeight="1"/>
+    <row r="1387" ht="15.75" customHeight="1"/>
+    <row r="1388" ht="15.75" customHeight="1"/>
+    <row r="1389" ht="15.75" customHeight="1"/>
+    <row r="1390" ht="15.75" customHeight="1"/>
+    <row r="1391" ht="15.75" customHeight="1"/>
+    <row r="1392" ht="15.75" customHeight="1"/>
+    <row r="1393" ht="15.75" customHeight="1"/>
+    <row r="1394" ht="15.75" customHeight="1"/>
+    <row r="1395" ht="15.75" customHeight="1"/>
+    <row r="1396" ht="15.75" customHeight="1"/>
+    <row r="1397" ht="15.75" customHeight="1"/>
+    <row r="1398" ht="15.75" customHeight="1"/>
+    <row r="1399" ht="15.75" customHeight="1"/>
+    <row r="1400" ht="15.75" customHeight="1"/>
+    <row r="1401" ht="15.75" customHeight="1"/>
+    <row r="1402" ht="15.75" customHeight="1"/>
+    <row r="1403" ht="15.75" customHeight="1"/>
+    <row r="1404" ht="15.75" customHeight="1"/>
+    <row r="1405" ht="15.75" customHeight="1"/>
+    <row r="1406" ht="15.75" customHeight="1"/>
+    <row r="1407" ht="15.75" customHeight="1"/>
+    <row r="1408" ht="15.75" customHeight="1"/>
+    <row r="1409" ht="15.75" customHeight="1"/>
+    <row r="1410" ht="15.75" customHeight="1"/>
+    <row r="1411" ht="15.75" customHeight="1"/>
+    <row r="1412" ht="15.75" customHeight="1"/>
+    <row r="1413" ht="15.75" customHeight="1"/>
+    <row r="1414" ht="15.75" customHeight="1"/>
+    <row r="1415" ht="15.75" customHeight="1"/>
+    <row r="1416" ht="15.75" customHeight="1"/>
+    <row r="1417" ht="15.75" customHeight="1"/>
+    <row r="1418" ht="15.75" customHeight="1"/>
+    <row r="1419" ht="15.75" customHeight="1"/>
+    <row r="1420" ht="15.75" customHeight="1"/>
+    <row r="1421" ht="15.75" customHeight="1"/>
+    <row r="1422" ht="15.75" customHeight="1"/>
+    <row r="1423" ht="15.75" customHeight="1"/>
+    <row r="1424" ht="15.75" customHeight="1"/>
+    <row r="1425" ht="15.75" customHeight="1"/>
+    <row r="1426" ht="15.75" customHeight="1"/>
+    <row r="1427" ht="15.75" customHeight="1"/>
+    <row r="1428" ht="15.75" customHeight="1"/>
+    <row r="1429" ht="15.75" customHeight="1"/>
+    <row r="1430" ht="15.75" customHeight="1"/>
+    <row r="1431" ht="15.75" customHeight="1"/>
+    <row r="1432" ht="15.75" customHeight="1"/>
+    <row r="1433" ht="15.75" customHeight="1"/>
+    <row r="1434" ht="15.75" customHeight="1"/>
+    <row r="1435" ht="15.75" customHeight="1"/>
+    <row r="1436" ht="15.75" customHeight="1"/>
+    <row r="1437" ht="15.75" customHeight="1"/>
+    <row r="1438" ht="15.75" customHeight="1"/>
+    <row r="1439" ht="15.75" customHeight="1"/>
+    <row r="1440" ht="15.75" customHeight="1"/>
+    <row r="1441" ht="15.75" customHeight="1"/>
+    <row r="1442" ht="15.75" customHeight="1"/>
+    <row r="1443" ht="15.75" customHeight="1"/>
+    <row r="1444" ht="15.75" customHeight="1"/>
+    <row r="1445" ht="15.75" customHeight="1"/>
+    <row r="1446" ht="15.75" customHeight="1"/>
+    <row r="1447" ht="15.75" customHeight="1"/>
+    <row r="1448" ht="15.75" customHeight="1"/>
+    <row r="1449" ht="15.75" customHeight="1"/>
+    <row r="1450" ht="15.75" customHeight="1"/>
+    <row r="1451" ht="15.75" customHeight="1"/>
+    <row r="1452" ht="15.75" customHeight="1"/>
+    <row r="1453" ht="15.75" customHeight="1"/>
+    <row r="1454" ht="15.75" customHeight="1"/>
+    <row r="1455" ht="15.75" customHeight="1"/>
+    <row r="1456" ht="15.75" customHeight="1"/>
+    <row r="1457" ht="15.75" customHeight="1"/>
+    <row r="1458" ht="15.75" customHeight="1"/>
+    <row r="1459" ht="15.75" customHeight="1"/>
+    <row r="1460" ht="15.75" customHeight="1"/>
+    <row r="1461" ht="15.75" customHeight="1"/>
+    <row r="1462" ht="15.75" customHeight="1"/>
+    <row r="1463" ht="15.75" customHeight="1"/>
+    <row r="1464" ht="15.75" customHeight="1"/>
+    <row r="1465" ht="15.75" customHeight="1"/>
+    <row r="1466" ht="15.75" customHeight="1"/>
+    <row r="1467" ht="15.75" customHeight="1"/>
+    <row r="1468" ht="15.75" customHeight="1"/>
+    <row r="1469" ht="15.75" customHeight="1"/>
+    <row r="1470" ht="15.75" customHeight="1"/>
+    <row r="1471" ht="15.75" customHeight="1"/>
+    <row r="1472" ht="15.75" customHeight="1"/>
+    <row r="1473" ht="15.75" customHeight="1"/>
+    <row r="1474" ht="15.75" customHeight="1"/>
+    <row r="1475" ht="15.75" customHeight="1"/>
+    <row r="1476" ht="15.75" customHeight="1"/>
+    <row r="1477" ht="15.75" customHeight="1"/>
+    <row r="1478" ht="15.75" customHeight="1"/>
+    <row r="1479" ht="15.75" customHeight="1"/>
+    <row r="1480" ht="15.75" customHeight="1"/>
+    <row r="1481" ht="15.75" customHeight="1"/>
+    <row r="1482" ht="15.75" customHeight="1"/>
+    <row r="1483" ht="15.75" customHeight="1"/>
+    <row r="1484" ht="15.75" customHeight="1"/>
+    <row r="1485" ht="15.75" customHeight="1"/>
+    <row r="1486" ht="15.75" customHeight="1"/>
+    <row r="1487" ht="15.75" customHeight="1"/>
+    <row r="1488" ht="15.75" customHeight="1"/>
+    <row r="1489" ht="15.75" customHeight="1"/>
+    <row r="1490" ht="15.75" customHeight="1"/>
+    <row r="1491" ht="15.75" customHeight="1"/>
+    <row r="1492" ht="15.75" customHeight="1"/>
+    <row r="1493" ht="15.75" customHeight="1"/>
+    <row r="1494" ht="15.75" customHeight="1"/>
+    <row r="1495" ht="15.75" customHeight="1"/>
+    <row r="1496" ht="15.75" customHeight="1"/>
+    <row r="1497" ht="15.75" customHeight="1"/>
+    <row r="1498" ht="15.75" customHeight="1"/>
+    <row r="1499" ht="15.75" customHeight="1"/>
+    <row r="1500" ht="15.75" customHeight="1"/>
+    <row r="1501" ht="15.75" customHeight="1"/>
+    <row r="1502" ht="15.75" customHeight="1"/>
+    <row r="1503" ht="15.75" customHeight="1"/>
+    <row r="1504" ht="15.75" customHeight="1"/>
+    <row r="1505" ht="15.75" customHeight="1"/>
+    <row r="1506" ht="15.75" customHeight="1"/>
+    <row r="1507" ht="15.75" customHeight="1"/>
+    <row r="1508" ht="15.75" customHeight="1"/>
+    <row r="1509" ht="15.75" customHeight="1"/>
+    <row r="1510" ht="15.75" customHeight="1"/>
+    <row r="1511" ht="15.75" customHeight="1"/>
+    <row r="1512" ht="15.75" customHeight="1"/>
+    <row r="1513" ht="15.75" customHeight="1"/>
+    <row r="1514" ht="15.75" customHeight="1"/>
+    <row r="1515" ht="15.75" customHeight="1"/>
+    <row r="1516" ht="15.75" customHeight="1"/>
+    <row r="1517" ht="15.75" customHeight="1"/>
+    <row r="1518" ht="15.75" customHeight="1"/>
+    <row r="1519" ht="15.75" customHeight="1"/>
+    <row r="1520" ht="15.75" customHeight="1"/>
+    <row r="1521" ht="15.75" customHeight="1"/>
+    <row r="1522" ht="15.75" customHeight="1"/>
+    <row r="1523" ht="15.75" customHeight="1"/>
+    <row r="1524" ht="15.75" customHeight="1"/>
+    <row r="1525" ht="15.75" customHeight="1"/>
+    <row r="1526" ht="15.75" customHeight="1"/>
+    <row r="1527" ht="15.75" customHeight="1"/>
+    <row r="1528" ht="15.75" customHeight="1"/>
+    <row r="1529" ht="15.75" customHeight="1"/>
+    <row r="1530" ht="15.75" customHeight="1"/>
+    <row r="1531" ht="15.75" customHeight="1"/>
+    <row r="1532" ht="15.75" customHeight="1"/>
+    <row r="1533" ht="15.75" customHeight="1"/>
+    <row r="1534" ht="15.75" customHeight="1"/>
+    <row r="1535" ht="15.75" customHeight="1"/>
+    <row r="1536" ht="15.75" customHeight="1"/>
+    <row r="1537" ht="15.75" customHeight="1"/>
+    <row r="1538" ht="15.75" customHeight="1"/>
+    <row r="1539" ht="15.75" customHeight="1"/>
+    <row r="1540" ht="15.75" customHeight="1"/>
+    <row r="1541" ht="15.75" customHeight="1"/>
+    <row r="1542" ht="15.75" customHeight="1"/>
+    <row r="1543" ht="15.75" customHeight="1"/>
+    <row r="1544" ht="15.75" customHeight="1"/>
+    <row r="1545" ht="15.75" customHeight="1"/>
+    <row r="1546" ht="15.75" customHeight="1"/>
+    <row r="1547" ht="15.75" customHeight="1"/>
+    <row r="1548" ht="15.75" customHeight="1"/>
+    <row r="1549" ht="15.75" customHeight="1"/>
+    <row r="1550" ht="15.75" customHeight="1"/>
+    <row r="1551" ht="15.75" customHeight="1"/>
+    <row r="1552" ht="15.75" customHeight="1"/>
+    <row r="1553" ht="15.75" customHeight="1"/>
+    <row r="1554" ht="15.75" customHeight="1"/>
+    <row r="1555" ht="15.75" customHeight="1"/>
+    <row r="1556" ht="15.75" customHeight="1"/>
+    <row r="1557" ht="15.75" customHeight="1"/>
+    <row r="1558" ht="15.75" customHeight="1"/>
+    <row r="1559" ht="15.75" customHeight="1"/>
+    <row r="1560" ht="15.75" customHeight="1"/>
+    <row r="1561" ht="15.75" customHeight="1"/>
+    <row r="1562" ht="15.75" customHeight="1"/>
+    <row r="1563" ht="15.75" customHeight="1"/>
+    <row r="1564" ht="15.75" customHeight="1"/>
+    <row r="1565" ht="15.75" customHeight="1"/>
+    <row r="1566" ht="15.75" customHeight="1"/>
+    <row r="1567" ht="15.75" customHeight="1"/>
+    <row r="1568" ht="15.75" customHeight="1"/>
+    <row r="1569" ht="15.75" customHeight="1"/>
+    <row r="1570" ht="15.75" customHeight="1"/>
+    <row r="1571" ht="15.75" customHeight="1"/>
+    <row r="1572" ht="15.75" customHeight="1"/>
+    <row r="1573" ht="15.75" customHeight="1"/>
+    <row r="1574" ht="15.75" customHeight="1"/>
+    <row r="1575" ht="15.75" customHeight="1"/>
+    <row r="1576" ht="15.75" customHeight="1"/>
+    <row r="1577" ht="15.75" customHeight="1"/>
+    <row r="1578" ht="15.75" customHeight="1"/>
+    <row r="1579" ht="15.75" customHeight="1"/>
+    <row r="1580" ht="15.75" customHeight="1"/>
+    <row r="1581" ht="15.75" customHeight="1"/>
+    <row r="1582" ht="15.75" customHeight="1"/>
+    <row r="1583" ht="15.75" customHeight="1"/>
+    <row r="1584" ht="15.75" customHeight="1"/>
+    <row r="1585" ht="15.75" customHeight="1"/>
+    <row r="1586" ht="15.75" customHeight="1"/>
+    <row r="1587" ht="15.75" customHeight="1"/>
+    <row r="1588" ht="15.75" customHeight="1"/>
+    <row r="1589" ht="15.75" customHeight="1"/>
+    <row r="1590" ht="15.75" customHeight="1"/>
+    <row r="1591" ht="15.75" customHeight="1"/>
+    <row r="1592" ht="15.75" customHeight="1"/>
+    <row r="1593" ht="15.75" customHeight="1"/>
+    <row r="1594" ht="15.75" customHeight="1"/>
+    <row r="1595" ht="15.75" customHeight="1"/>
+    <row r="1596" ht="15.75" customHeight="1"/>
+    <row r="1597" ht="15.75" customHeight="1"/>
+    <row r="1598" ht="15.75" customHeight="1"/>
+    <row r="1599" ht="15.75" customHeight="1"/>
+    <row r="1600" ht="15.75" customHeight="1"/>
+    <row r="1601" ht="15.75" customHeight="1"/>
+    <row r="1602" ht="15.75" customHeight="1"/>
+    <row r="1603" ht="15.75" customHeight="1"/>
+    <row r="1604" ht="15.75" customHeight="1"/>
+    <row r="1605" ht="15.75" customHeight="1"/>
+    <row r="1606" ht="15.75" customHeight="1"/>
+    <row r="1607" ht="15.75" customHeight="1"/>
+    <row r="1608" ht="15.75" customHeight="1"/>
+    <row r="1609" ht="15.75" customHeight="1"/>
+    <row r="1610" ht="15.75" customHeight="1"/>
+    <row r="1611" ht="15.75" customHeight="1"/>
+    <row r="1612" ht="15.75" customHeight="1"/>
+    <row r="1613" ht="15.75" customHeight="1"/>
+    <row r="1614" ht="15.75" customHeight="1"/>
+    <row r="1615" ht="15.75" customHeight="1"/>
+    <row r="1616" ht="15.75" customHeight="1"/>
+    <row r="1617" ht="15.75" customHeight="1"/>
+    <row r="1618" ht="15.75" customHeight="1"/>
+    <row r="1619" ht="15.75" customHeight="1"/>
+    <row r="1620" ht="15.75" customHeight="1"/>
+    <row r="1621" ht="15.75" customHeight="1"/>
+    <row r="1622" ht="15.75" customHeight="1"/>
+    <row r="1623" ht="15.75" customHeight="1"/>
+    <row r="1624" ht="15.75" customHeight="1"/>
+    <row r="1625" ht="15.75" customHeight="1"/>
+    <row r="1626" ht="15.75" customHeight="1"/>
+    <row r="1627" ht="15.75" customHeight="1"/>
+    <row r="1628" ht="15.75" customHeight="1"/>
+    <row r="1629" ht="15.75" customHeight="1"/>
+    <row r="1630" ht="15.75" customHeight="1"/>
+    <row r="1631" ht="15.75" customHeight="1"/>
+    <row r="1632" ht="15.75" customHeight="1"/>
+    <row r="1633" ht="15.75" customHeight="1"/>
+    <row r="1634" ht="15.75" customHeight="1"/>
+    <row r="1635" ht="15.75" customHeight="1"/>
+    <row r="1636" ht="15.75" customHeight="1"/>
+    <row r="1637" ht="15.75" customHeight="1"/>
+    <row r="1638" ht="15.75" customHeight="1"/>
+    <row r="1639" ht="15.75" customHeight="1"/>
+    <row r="1640" ht="15.75" customHeight="1"/>
+    <row r="1641" ht="15.75" customHeight="1"/>
+    <row r="1642" ht="15.75" customHeight="1"/>
+    <row r="1643" ht="15.75" customHeight="1"/>
+    <row r="1644" ht="15.75" customHeight="1"/>
+    <row r="1645" ht="15.75" customHeight="1"/>
+    <row r="1646" ht="15.75" customHeight="1"/>
+    <row r="1647" ht="15.75" customHeight="1"/>
+    <row r="1648" ht="15.75" customHeight="1"/>
+    <row r="1649" ht="15.75" customHeight="1"/>
+    <row r="1650" ht="15.75" customHeight="1"/>
+    <row r="1651" ht="15.75" customHeight="1"/>
+    <row r="1652" ht="15.75" customHeight="1"/>
+    <row r="1653" ht="15.75" customHeight="1"/>
+    <row r="1654" ht="15.75" customHeight="1"/>
+    <row r="1655" ht="15.75" customHeight="1"/>
+    <row r="1656" ht="15.75" customHeight="1"/>
+    <row r="1657" ht="15.75" customHeight="1"/>
+    <row r="1658" ht="15.75" customHeight="1"/>
+    <row r="1659" ht="15.75" customHeight="1"/>
+    <row r="1660" ht="15.75" customHeight="1"/>
+    <row r="1661" ht="15.75" customHeight="1"/>
+    <row r="1662" ht="15.75" customHeight="1"/>
+    <row r="1663" ht="15.75" customHeight="1"/>
+    <row r="1664" ht="15.75" customHeight="1"/>
+    <row r="1665" ht="15.75" customHeight="1"/>
+    <row r="1666" ht="15.75" customHeight="1"/>
+    <row r="1667" ht="15.75" customHeight="1"/>
+    <row r="1668" ht="15.75" customHeight="1"/>
+    <row r="1669" ht="15.75" customHeight="1"/>
+    <row r="1670" ht="15.75" customHeight="1"/>
+    <row r="1671" ht="15.75" customHeight="1"/>
+    <row r="1672" ht="15.75" customHeight="1"/>
+    <row r="1673" ht="15.75" customHeight="1"/>
+    <row r="1674" ht="15.75" customHeight="1"/>
+    <row r="1675" ht="15.75" customHeight="1"/>
+    <row r="1676" ht="15.75" customHeight="1"/>
+    <row r="1677" ht="15.75" customHeight="1"/>
+    <row r="1678" ht="15.75" customHeight="1"/>
+    <row r="1679" ht="15.75" customHeight="1"/>
+    <row r="1680" ht="15.75" customHeight="1"/>
+    <row r="1681" ht="15.75" customHeight="1"/>
+    <row r="1682" ht="15.75" customHeight="1"/>
+    <row r="1683" ht="15.75" customHeight="1"/>
+    <row r="1684" ht="15.75" customHeight="1"/>
+    <row r="1685" ht="15.75" customHeight="1"/>
+    <row r="1686" ht="15.75" customHeight="1"/>
+    <row r="1687" ht="15.75" customHeight="1"/>
+    <row r="1688" ht="15.75" customHeight="1"/>
+    <row r="1689" ht="15.75" customHeight="1"/>
+    <row r="1690" ht="15.75" customHeight="1"/>
+    <row r="1691" ht="15.75" customHeight="1"/>
+    <row r="1692" ht="15.75" customHeight="1"/>
+    <row r="1693" ht="15.75" customHeight="1"/>
+    <row r="1694" ht="15.75" customHeight="1"/>
+    <row r="1695" ht="15.75" customHeight="1"/>
+    <row r="1696" ht="15.75" customHeight="1"/>
+    <row r="1697" ht="15.75" customHeight="1"/>
+    <row r="1698" ht="15.75" customHeight="1"/>
+    <row r="1699" ht="15.75" customHeight="1"/>
+    <row r="1700" ht="15.75" customHeight="1"/>
+    <row r="1701" ht="15.75" customHeight="1"/>
+    <row r="1702" ht="15.75" customHeight="1"/>
+    <row r="1703" ht="15.75" customHeight="1"/>
+    <row r="1704" ht="15.75" customHeight="1"/>
+    <row r="1705" ht="15.75" customHeight="1"/>
+    <row r="1706" ht="15.75" customHeight="1"/>
+    <row r="1707" ht="15.75" customHeight="1"/>
+    <row r="1708" ht="15.75" customHeight="1"/>
+    <row r="1709" ht="15.75" customHeight="1"/>
+    <row r="1710" ht="15.75" customHeight="1"/>
+    <row r="1711" ht="15.75" customHeight="1"/>
+    <row r="1712" ht="15.75" customHeight="1"/>
+    <row r="1713" ht="15.75" customHeight="1"/>
+    <row r="1714" ht="15.75" customHeight="1"/>
+    <row r="1715" ht="15.75" customHeight="1"/>
+    <row r="1716" ht="15.75" customHeight="1"/>
+    <row r="1717" ht="15.75" customHeight="1"/>
+    <row r="1718" ht="15.75" customHeight="1"/>
+    <row r="1719" ht="15.75" customHeight="1"/>
+    <row r="1720" ht="15.75" customHeight="1"/>
+    <row r="1721" ht="15.75" customHeight="1"/>
+    <row r="1722" ht="15.75" customHeight="1"/>
+    <row r="1723" ht="15.75" customHeight="1"/>
+    <row r="1724" ht="15.75" customHeight="1"/>
+    <row r="1725" ht="15.75" customHeight="1"/>
+    <row r="1726" ht="15.75" customHeight="1"/>
+    <row r="1727" ht="15.75" customHeight="1"/>
+    <row r="1728" ht="15.75" customHeight="1"/>
+    <row r="1729" ht="15.75" customHeight="1"/>
+    <row r="1730" ht="15.75" customHeight="1"/>
+    <row r="1731" ht="15.75" customHeight="1"/>
+    <row r="1732" ht="15.75" customHeight="1"/>
+    <row r="1733" ht="15.75" customHeight="1"/>
+    <row r="1734" ht="15.75" customHeight="1"/>
+    <row r="1735" ht="15.75" customHeight="1"/>
+    <row r="1736" ht="15.75" customHeight="1"/>
+    <row r="1737" ht="15.75" customHeight="1"/>
+    <row r="1738" ht="15.75" customHeight="1"/>
+    <row r="1739" ht="15.75" customHeight="1"/>
+    <row r="1740" ht="15.75" customHeight="1"/>
+    <row r="1741" ht="15.75" customHeight="1"/>
+    <row r="1742" ht="15.75" customHeight="1"/>
+    <row r="1743" ht="15.75" customHeight="1"/>
+    <row r="1744" ht="15.75" customHeight="1"/>
+    <row r="1745" ht="15.75" customHeight="1"/>
+    <row r="1746" ht="15.75" customHeight="1"/>
+    <row r="1747" ht="15.75" customHeight="1"/>
+    <row r="1748" ht="15.75" customHeight="1"/>
+    <row r="1749" ht="15.75" customHeight="1"/>
+    <row r="1750" ht="15.75" customHeight="1"/>
+    <row r="1751" ht="15.75" customHeight="1"/>
+    <row r="1752" ht="15.75" customHeight="1"/>
+    <row r="1753" ht="15.75" customHeight="1"/>
+    <row r="1754" ht="15.75" customHeight="1"/>
+    <row r="1755" ht="15.75" customHeight="1"/>
+    <row r="1756" ht="15.75" customHeight="1"/>
+    <row r="1757" ht="15.75" customHeight="1"/>
+    <row r="1758" ht="15.75" customHeight="1"/>
+    <row r="1759" ht="15.75" customHeight="1"/>
+    <row r="1760" ht="15.75" customHeight="1"/>
+    <row r="1761" ht="15.75" customHeight="1"/>
+    <row r="1762" ht="15.75" customHeight="1"/>
+    <row r="1763" ht="15.75" customHeight="1"/>
+    <row r="1764" ht="15.75" customHeight="1"/>
+    <row r="1765" ht="15.75" customHeight="1"/>
+    <row r="1766" ht="15.75" customHeight="1"/>
+    <row r="1767" ht="15.75" customHeight="1"/>
+    <row r="1768" ht="15.75" customHeight="1"/>
+    <row r="1769" ht="15.75" customHeight="1"/>
+    <row r="1770" ht="15.75" customHeight="1"/>
+    <row r="1771" ht="15.75" customHeight="1"/>
+    <row r="1772" ht="15.75" customHeight="1"/>
+    <row r="1773" ht="15.75" customHeight="1"/>
+    <row r="1774" ht="15.75" customHeight="1"/>
+    <row r="1775" ht="15.75" customHeight="1"/>
+    <row r="1776" ht="15.75" customHeight="1"/>
+    <row r="1777" ht="15.75" customHeight="1"/>
+    <row r="1778" ht="15.75" customHeight="1"/>
+    <row r="1779" ht="15.75" customHeight="1"/>
+    <row r="1780" ht="15.75" customHeight="1"/>
+    <row r="1781" ht="15.75" customHeight="1"/>
+    <row r="1782" ht="15.75" customHeight="1"/>
+    <row r="1783" ht="15.75" customHeight="1"/>
+    <row r="1784" ht="15.75" customHeight="1"/>
+    <row r="1785" ht="15.75" customHeight="1"/>
+    <row r="1786" ht="15.75" customHeight="1"/>
+    <row r="1787" ht="15.75" customHeight="1"/>
+    <row r="1788" ht="15.75" customHeight="1"/>
+    <row r="1789" ht="15.75" customHeight="1"/>
+    <row r="1790" ht="15.75" customHeight="1"/>
+    <row r="1791" ht="15.75" customHeight="1"/>
+    <row r="1792" ht="15.75" customHeight="1"/>
+    <row r="1793" ht="15.75" customHeight="1"/>
+    <row r="1794" ht="15.75" customHeight="1"/>
+    <row r="1795" ht="15.75" customHeight="1"/>
+    <row r="1796" ht="15.75" customHeight="1"/>
+    <row r="1797" ht="15.75" customHeight="1"/>
+    <row r="1798" ht="15.75" customHeight="1"/>
+    <row r="1799" ht="15.75" customHeight="1"/>
+    <row r="1800" ht="15.75" customHeight="1"/>
+    <row r="1801" ht="15.75" customHeight="1"/>
+    <row r="1802" ht="15.75" customHeight="1"/>
+    <row r="1803" ht="15.75" customHeight="1"/>
+    <row r="1804" ht="15.75" customHeight="1"/>
+    <row r="1805" ht="15.75" customHeight="1"/>
+    <row r="1806" ht="15.75" customHeight="1"/>
+    <row r="1807" ht="15.75" customHeight="1"/>
+    <row r="1808" ht="15.75" customHeight="1"/>
+    <row r="1809" ht="15.75" customHeight="1"/>
+    <row r="1810" ht="15.75" customHeight="1"/>
+    <row r="1811" ht="15.75" customHeight="1"/>
+    <row r="1812" ht="15.75" customHeight="1"/>
+    <row r="1813" ht="15.75" customHeight="1"/>
+    <row r="1814" ht="15.75" customHeight="1"/>
+    <row r="1815" ht="15.75" customHeight="1"/>
+    <row r="1816" ht="15.75" customHeight="1"/>
+    <row r="1817" ht="15.75" customHeight="1"/>
+    <row r="1818" ht="15.75" customHeight="1"/>
+    <row r="1819" ht="15.75" customHeight="1"/>
+    <row r="1820" ht="15.75" customHeight="1"/>
+    <row r="1821" ht="15.75" customHeight="1"/>
+    <row r="1822" ht="15.75" customHeight="1"/>
+    <row r="1823" ht="15.75" customHeight="1"/>
+    <row r="1824" ht="15.75" customHeight="1"/>
+    <row r="1825" ht="15.75" customHeight="1"/>
+    <row r="1826" ht="15.75" customHeight="1"/>
+    <row r="1827" ht="15.75" customHeight="1"/>
+    <row r="1828" ht="15.75" customHeight="1"/>
+    <row r="1829" ht="15.75" customHeight="1"/>
+    <row r="1830" ht="15.75" customHeight="1"/>
+    <row r="1831" ht="15.75" customHeight="1"/>
+    <row r="1832" ht="15.75" customHeight="1"/>
+    <row r="1833" ht="15.75" customHeight="1"/>
+    <row r="1834" ht="15.75" customHeight="1"/>
+    <row r="1835" ht="15.75" customHeight="1"/>
+    <row r="1836" ht="15.75" customHeight="1"/>
+    <row r="1837" ht="15.75" customHeight="1"/>
+    <row r="1838" ht="15.75" customHeight="1"/>
+    <row r="1839" ht="15.75" customHeight="1"/>
+    <row r="1840" ht="15.75" customHeight="1"/>
+    <row r="1841" ht="15.75" customHeight="1"/>
+    <row r="1842" ht="15.75" customHeight="1"/>
+    <row r="1843" ht="15.75" customHeight="1"/>
+    <row r="1844" ht="15.75" customHeight="1"/>
+    <row r="1845" ht="15.75" customHeight="1"/>
+    <row r="1846" ht="15.75" customHeight="1"/>
+    <row r="1847" ht="15.75" customHeight="1"/>
+    <row r="1848" ht="15.75" customHeight="1"/>
+    <row r="1849" ht="15.75" customHeight="1"/>
+    <row r="1850" ht="15.75" customHeight="1"/>
+    <row r="1851" ht="15.75" customHeight="1"/>
+    <row r="1852" ht="15.75" customHeight="1"/>
+    <row r="1853" ht="15.75" customHeight="1"/>
+    <row r="1854" ht="15.75" customHeight="1"/>
+    <row r="1855" ht="15.75" customHeight="1"/>
+    <row r="1856" ht="15.75" customHeight="1"/>
+    <row r="1857" ht="15.75" customHeight="1"/>
+    <row r="1858" ht="15.75" customHeight="1"/>
+    <row r="1859" ht="15.75" customHeight="1"/>
+    <row r="1860" ht="15.75" customHeight="1"/>
+    <row r="1861" ht="15.75" customHeight="1"/>
+    <row r="1862" ht="15.75" customHeight="1"/>
+    <row r="1863" ht="15.75" customHeight="1"/>
+    <row r="1864" ht="15.75" customHeight="1"/>
+    <row r="1865" ht="15.75" customHeight="1"/>
+    <row r="1866" ht="15.75" customHeight="1"/>
+    <row r="1867" ht="15.75" customHeight="1"/>
+    <row r="1868" ht="15.75" customHeight="1"/>
+    <row r="1869" ht="15.75" customHeight="1"/>
+    <row r="1870" ht="15.75" customHeight="1"/>
+    <row r="1871" ht="15.75" customHeight="1"/>
+    <row r="1872" ht="15.75" customHeight="1"/>
+    <row r="1873" ht="15.75" customHeight="1"/>
+    <row r="1874" ht="15.75" customHeight="1"/>
+    <row r="1875" ht="15.75" customHeight="1"/>
+    <row r="1876" ht="15.75" customHeight="1"/>
+    <row r="1877" ht="15.75" customHeight="1"/>
+    <row r="1878" ht="15.75" customHeight="1"/>
+    <row r="1879" ht="15.75" customHeight="1"/>
+    <row r="1880" ht="15.75" customHeight="1"/>
+    <row r="1881" ht="15.75" customHeight="1"/>
+    <row r="1882" ht="15.75" customHeight="1"/>
+    <row r="1883" ht="15.75" customHeight="1"/>
+    <row r="1884" ht="15.75" customHeight="1"/>
+    <row r="1885" ht="15.75" customHeight="1"/>
+    <row r="1886" ht="15.75" customHeight="1"/>
+    <row r="1887" ht="15.75" customHeight="1"/>
+    <row r="1888" ht="15.75" customHeight="1"/>
+    <row r="1889" ht="15.75" customHeight="1"/>
+    <row r="1890" ht="15.75" customHeight="1"/>
+    <row r="1891" ht="15.75" customHeight="1"/>
+    <row r="1892" ht="15.75" customHeight="1"/>
+    <row r="1893" ht="15.75" customHeight="1"/>
+    <row r="1894" ht="15.75" customHeight="1"/>
+    <row r="1895" ht="15.75" customHeight="1"/>
+    <row r="1896" ht="15.75" customHeight="1"/>
+    <row r="1897" ht="15.75" customHeight="1"/>
+    <row r="1898" ht="15.75" customHeight="1"/>
+    <row r="1899" ht="15.75" customHeight="1"/>
+    <row r="1900" ht="15.75" customHeight="1"/>
+    <row r="1901" ht="15.75" customHeight="1"/>
+    <row r="1902" ht="15.75" customHeight="1"/>
+    <row r="1903" ht="15.75" customHeight="1"/>
+    <row r="1904" ht="15.75" customHeight="1"/>
+    <row r="1905" ht="15.75" customHeight="1"/>
+    <row r="1906" ht="15.75" customHeight="1"/>
+    <row r="1907" ht="15.75" customHeight="1"/>
+    <row r="1908" ht="15.75" customHeight="1"/>
+    <row r="1909" ht="15.75" customHeight="1"/>
+    <row r="1910" ht="15.75" customHeight="1"/>
+    <row r="1911" ht="15.75" customHeight="1"/>
+    <row r="1912" ht="15.75" customHeight="1"/>
+    <row r="1913" ht="15.75" customHeight="1"/>
+    <row r="1914" ht="15.75" customHeight="1"/>
+    <row r="1915" ht="15.75" customHeight="1"/>
+    <row r="1916" ht="15.75" customHeight="1"/>
+    <row r="1917" ht="15.75" customHeight="1"/>
+    <row r="1918" ht="15.75" customHeight="1"/>
+    <row r="1919" ht="15.75" customHeight="1"/>
+    <row r="1920" ht="15.75" customHeight="1"/>
+    <row r="1921" ht="15.75" customHeight="1"/>
+    <row r="1922" ht="15.75" customHeight="1"/>
+    <row r="1923" ht="15.75" customHeight="1"/>
+    <row r="1924" ht="15.75" customHeight="1"/>
+    <row r="1925" ht="15.75" customHeight="1"/>
+    <row r="1926" ht="15.75" customHeight="1"/>
+    <row r="1927" ht="15.75" customHeight="1"/>
+    <row r="1928" ht="15.75" customHeight="1"/>
+    <row r="1929" ht="15.75" customHeight="1"/>
+    <row r="1930" ht="15.75" customHeight="1"/>
+    <row r="1931" ht="15.75" customHeight="1"/>
+    <row r="1932" ht="15.75" customHeight="1"/>
+    <row r="1933" ht="15.75" customHeight="1"/>
+    <row r="1934" ht="15.75" customHeight="1"/>
+    <row r="1935" ht="15.75" customHeight="1"/>
+    <row r="1936" ht="15.75" customHeight="1"/>
+    <row r="1937" ht="15.75" customHeight="1"/>
+    <row r="1938" ht="15.75" customHeight="1"/>
+    <row r="1939" ht="15.75" customHeight="1"/>
+    <row r="1940" ht="15.75" customHeight="1"/>
+    <row r="1941" ht="15.75" customHeight="1"/>
+    <row r="1942" ht="15.75" customHeight="1"/>
+    <row r="1943" ht="15.75" customHeight="1"/>
+    <row r="1944" ht="15.75" customHeight="1"/>
+    <row r="1945" ht="15.75" customHeight="1"/>
+    <row r="1946" ht="15.75" customHeight="1"/>
+    <row r="1947" ht="15.75" customHeight="1"/>
+    <row r="1948" ht="15.75" customHeight="1"/>
+    <row r="1949" ht="15.75" customHeight="1"/>
+    <row r="1950" ht="15.75" customHeight="1"/>
+    <row r="1951" ht="15.75" customHeight="1"/>
+    <row r="1952" ht="15.75" customHeight="1"/>
+    <row r="1953" ht="15.75" customHeight="1"/>
+    <row r="1954" ht="15.75" customHeight="1"/>
+    <row r="1955" ht="15.75" customHeight="1"/>
+    <row r="1956" ht="15.75" customHeight="1"/>
+    <row r="1957" ht="15.75" customHeight="1"/>
+    <row r="1958" ht="15.75" customHeight="1"/>
+    <row r="1959" ht="15.75" customHeight="1"/>
+    <row r="1960" ht="15.75" customHeight="1"/>
+    <row r="1961" ht="15.75" customHeight="1"/>
+    <row r="1962" ht="15.75" customHeight="1"/>
+    <row r="1963" ht="15.75" customHeight="1"/>
+    <row r="1964" ht="15.75" customHeight="1"/>
+    <row r="1965" ht="15.75" customHeight="1"/>
+    <row r="1966" ht="15.75" customHeight="1"/>
+    <row r="1967" ht="15.75" customHeight="1"/>
+    <row r="1968" ht="15.75" customHeight="1"/>
+    <row r="1969" ht="15.75" customHeight="1"/>
+    <row r="1970" ht="15.75" customHeight="1"/>
+    <row r="1971" ht="15.75" customHeight="1"/>
+    <row r="1972" ht="15.75" customHeight="1"/>
+    <row r="1973" ht="15.75" customHeight="1"/>
+    <row r="1974" ht="15.75" customHeight="1"/>
+    <row r="1975" ht="15.75" customHeight="1"/>
+    <row r="1976" ht="15.75" customHeight="1"/>
+    <row r="1977" ht="15.75" customHeight="1"/>
+    <row r="1978" ht="15.75" customHeight="1"/>
+    <row r="1979" ht="15.75" customHeight="1"/>
+    <row r="1980" ht="15.75" customHeight="1"/>
+    <row r="1981" ht="15.75" customHeight="1"/>
+    <row r="1982" ht="15.75" customHeight="1"/>
+    <row r="1983" ht="15.75" customHeight="1"/>
+    <row r="1984" ht="15.75" customHeight="1"/>
+    <row r="1985" ht="15.75" customHeight="1"/>
+    <row r="1986" ht="15.75" customHeight="1"/>
+    <row r="1987" ht="15.75" customHeight="1"/>
+    <row r="1988" ht="15.75" customHeight="1"/>
+    <row r="1989" ht="15.75" customHeight="1"/>
+    <row r="1990" ht="15.75" customHeight="1"/>
+    <row r="1991" ht="15.75" customHeight="1"/>
+    <row r="1992" ht="15.75" customHeight="1"/>
+    <row r="1993" ht="15.75" customHeight="1"/>
+    <row r="1994" ht="15.75" customHeight="1"/>
+    <row r="1995" ht="15.75" customHeight="1"/>
+    <row r="1996" ht="15.75" customHeight="1"/>
+    <row r="1997" ht="15.75" customHeight="1"/>
+    <row r="1998" ht="15.75" customHeight="1"/>
+    <row r="1999" ht="15.75" customHeight="1"/>
+    <row r="2000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$2:$J$27"/>
   <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A10:J10"/>
     <mergeCell ref="A15:J15"/>
     <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H9 H11:H14 H16:H19 H21">
+      <formula1>"Fail,Pass"</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
   <pageSetup orientation="landscape"/>
@@ -5192,7 +6240,7 @@
       <c r="G2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="18" t="s">
         <v>41</v>
       </c>
       <c r="I2" s="5" t="s">
@@ -5203,7 +6251,7 @@
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="37" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="15"/>
@@ -5217,692 +6265,729 @@
       <c r="J3" s="16"/>
     </row>
     <row r="4" ht="69.75" customHeight="1">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="37" t="s">
+      <c r="E4" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="G4" s="37"/>
-      <c r="H4" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="38" t="s">
+      <c r="G4" s="38"/>
+      <c r="H4" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J4" s="37" t="s">
-        <v>161</v>
+      <c r="J4" s="38" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="5" ht="69.75" customHeight="1">
       <c r="A5" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G5" s="13"/>
-      <c r="H5" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="38" t="s">
+      <c r="H5" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="I5" s="40" t="s">
         <v>52</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" ht="69.75" customHeight="1">
-      <c r="A6" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="B6" s="37" t="s">
+      <c r="A6" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="B6" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="D6" s="37" t="s">
+      <c r="C6" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="D6" s="38" t="s">
         <v>173</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="E6" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="G6" s="37"/>
-      <c r="H6" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" s="38" t="s">
+      <c r="F6" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="G6" s="38"/>
+      <c r="H6" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="I6" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="37" t="s">
-        <v>175</v>
+      <c r="J6" s="38" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="7" ht="69.75" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G7" s="13"/>
-      <c r="H7" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" s="38" t="s">
+      <c r="H7" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="I7" s="40" t="s">
         <v>52</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" ht="69.75" customHeight="1">
-      <c r="A8" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="B8" s="37" t="s">
+      <c r="A8" s="38" t="s">
         <v>183</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="B8" s="38" t="s">
         <v>184</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="C8" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="D8" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="F8" s="37" t="s">
+      <c r="E8" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="G8" s="37"/>
-      <c r="H8" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I8" s="38" t="s">
+      <c r="F8" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="G8" s="38"/>
+      <c r="H8" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="I8" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="37" t="s">
-        <v>188</v>
+      <c r="J8" s="38" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="9" ht="69.75" customHeight="1">
       <c r="A9" s="13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="G9" s="42"/>
+      <c r="H9" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="I9" s="40" t="s">
         <v>52</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" ht="69.75" customHeight="1">
-      <c r="A10" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="B10" s="37" t="s">
+      <c r="A10" s="38" t="s">
         <v>197</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="B10" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="D10" s="37" t="s">
-        <v>165</v>
-      </c>
-      <c r="E10" s="37" t="s">
+      <c r="C10" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="D10" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="E10" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="G10" s="37"/>
-      <c r="H10" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I10" s="38" t="s">
+      <c r="F10" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="G10" s="38"/>
+      <c r="H10" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="I10" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="37" t="s">
-        <v>201</v>
+      <c r="J10" s="38" t="s">
+        <v>202</v>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="36" t="s">
-        <v>202</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="16"/>
+    <row r="11" ht="69.75" customHeight="1">
+      <c r="A11" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="I11" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="J11" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="K11" s="43"/>
+      <c r="L11" s="43"/>
+      <c r="M11" s="43"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="43"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="43"/>
     </row>
-    <row r="12" ht="69.75" customHeight="1">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="37" t="s">
-        <v>203</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="C12" s="37" t="s">
-        <v>205</v>
-      </c>
-      <c r="D12" s="37" t="s">
-        <v>206</v>
-      </c>
-      <c r="E12" s="37" t="s">
-        <v>207</v>
-      </c>
-      <c r="F12" s="37" t="s">
-        <v>208</v>
-      </c>
-      <c r="G12" s="37"/>
-      <c r="H12" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I12" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="J12" s="37" t="s">
-        <v>209</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="16"/>
     </row>
     <row r="13" ht="69.75" customHeight="1">
-      <c r="A13" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="B13" s="13" t="s">
+      <c r="A13" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="B13" s="38" t="s">
         <v>211</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="38" t="s">
         <v>212</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="38" t="s">
         <v>213</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="38" t="s">
         <v>214</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="38" t="s">
         <v>215</v>
       </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I13" s="38" t="s">
+      <c r="G13" s="38"/>
+      <c r="H13" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="I13" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="38" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="14" ht="69.75" customHeight="1">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="E14" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="F14" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="G14" s="37"/>
-      <c r="H14" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I14" s="38" t="s">
+      <c r="G14" s="13"/>
+      <c r="H14" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="I14" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J14" s="37" t="s">
+      <c r="J14" s="13" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="15" ht="69.75" customHeight="1">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="38" t="s">
         <v>224</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="38" t="s">
         <v>225</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="38" t="s">
         <v>226</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="38" t="s">
         <v>227</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="38" t="s">
         <v>228</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I15" s="38" t="s">
+      <c r="G15" s="38"/>
+      <c r="H15" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="I15" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J15" s="13" t="s">
+      <c r="J15" s="38" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="16" ht="69.75" customHeight="1">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="D16" s="37" t="s">
+      <c r="D16" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E16" s="37" t="s">
+      <c r="E16" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="F16" s="37" t="s">
+      <c r="F16" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="G16" s="37"/>
-      <c r="H16" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="I16" s="39" t="s">
+      <c r="G16" s="13"/>
+      <c r="H16" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="I16" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="J16" s="13" t="s">
         <v>237</v>
-      </c>
-      <c r="J16" s="37" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="17" ht="69.75" customHeight="1">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="38" t="s">
+        <v>238</v>
+      </c>
+      <c r="B17" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="C17" s="38" t="s">
         <v>240</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="D17" s="38" t="s">
         <v>241</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="E17" s="38" t="s">
         <v>242</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="F17" s="38" t="s">
         <v>243</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="G17" s="38"/>
+      <c r="H17" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="I17" s="45" t="s">
         <v>244</v>
       </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="I17" s="39" t="s">
-        <v>237</v>
-      </c>
-      <c r="J17" s="13" t="s">
+      <c r="J17" s="38" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="18" ht="69.75" customHeight="1">
-      <c r="A18" s="37" t="s">
+      <c r="A18" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="B18" s="37" t="s">
+      <c r="B18" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="D18" s="37" t="s">
+      <c r="D18" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="E18" s="37" t="s">
+      <c r="E18" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="F18" s="37" t="s">
+      <c r="F18" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="G18" s="37"/>
-      <c r="H18" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I18" s="38" t="s">
+      <c r="G18" s="13"/>
+      <c r="H18" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="I18" s="45" t="s">
+        <v>244</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="19" ht="69.75" customHeight="1">
+      <c r="A19" s="38" t="s">
+        <v>253</v>
+      </c>
+      <c r="B19" s="38" t="s">
+        <v>254</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>255</v>
+      </c>
+      <c r="D19" s="38" t="s">
+        <v>256</v>
+      </c>
+      <c r="E19" s="38" t="s">
+        <v>257</v>
+      </c>
+      <c r="F19" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="G19" s="38"/>
+      <c r="H19" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="I19" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J18" s="37" t="s">
-        <v>252</v>
+      <c r="J19" s="38" t="s">
+        <v>259</v>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="36" t="s">
-        <v>253</v>
-      </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="16"/>
-    </row>
-    <row r="20" ht="69.75" customHeight="1">
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="B20" s="37" t="s">
-        <v>255</v>
-      </c>
-      <c r="C20" s="37" t="s">
-        <v>256</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>165</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>257</v>
-      </c>
-      <c r="F20" s="37" t="s">
-        <v>258</v>
-      </c>
-      <c r="G20" s="37"/>
-      <c r="H20" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I20" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="J20" s="37" t="s">
-        <v>259</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="16"/>
     </row>
     <row r="21" ht="69.75" customHeight="1">
-      <c r="A21" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="B21" s="13" t="s">
+      <c r="A21" s="38" t="s">
         <v>261</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="B21" s="38" t="s">
         <v>262</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="C21" s="38" t="s">
         <v>263</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="D21" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="E21" s="38" t="s">
         <v>264</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="38" t="s">
         <v>265</v>
       </c>
-      <c r="G21" s="13"/>
-      <c r="H21" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I21" s="38" t="s">
+      <c r="G21" s="38"/>
+      <c r="H21" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="I21" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J21" s="13" t="s">
+      <c r="J21" s="38" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="36" t="s">
+    <row r="22" ht="69.75" customHeight="1">
+      <c r="A22" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="16"/>
+      <c r="B22" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G22" s="13"/>
+      <c r="H22" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="I22" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>273</v>
+      </c>
     </row>
-    <row r="23" ht="69.75" customHeight="1">
-      <c r="A23" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="G23" s="13"/>
-      <c r="H23" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I23" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="J23" s="13" t="s">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="37" t="s">
         <v>274</v>
       </c>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="16"/>
     </row>
     <row r="24" ht="69.75" customHeight="1">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="B24" s="37" t="s">
+      <c r="B24" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="D24" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="E24" s="37" t="s">
+      <c r="D24" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="F24" s="37" t="s">
+      <c r="E24" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="G24" s="37"/>
-      <c r="H24" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I24" s="38" t="s">
+      <c r="F24" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="G24" s="13"/>
+      <c r="H24" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="I24" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J24" s="37" t="s">
-        <v>280</v>
+      <c r="J24" s="13" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="25" ht="69.75" customHeight="1">
-      <c r="A25" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="B25" s="13" t="s">
+      <c r="A25" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="B25" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="C25" s="38" t="s">
+        <v>284</v>
+      </c>
+      <c r="D25" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="E25" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="F25" s="13" t="s">
+      <c r="E25" s="38" t="s">
         <v>285</v>
       </c>
-      <c r="G25" s="13"/>
-      <c r="H25" s="10" t="s">
-        <v>7</v>
+      <c r="F25" s="38" t="s">
+        <v>286</v>
+      </c>
+      <c r="G25" s="38"/>
+      <c r="H25" s="41" t="s">
+        <v>161</v>
       </c>
       <c r="I25" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="J25" s="38" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="26" ht="69.75" customHeight="1">
+      <c r="A26" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="G26" s="13"/>
+      <c r="H26" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="I26" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="J25" s="13" t="s">
-        <v>286</v>
+      <c r="J26" s="13" t="s">
+        <v>293</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="36" t="s">
-        <v>287</v>
-      </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="16"/>
-    </row>
-    <row r="27" ht="69.75" customHeight="1">
-      <c r="A27" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="G27" s="13"/>
-      <c r="H27" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I27" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="J27" s="13" t="s">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="37" t="s">
         <v>294</v>
       </c>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="16"/>
     </row>
     <row r="28" ht="69.75" customHeight="1">
-      <c r="A28" s="37" t="s">
+      <c r="A28" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="B28" s="37" t="s">
+      <c r="B28" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="C28" s="37" t="s">
+      <c r="C28" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="D28" s="37" t="s">
+      <c r="D28" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="E28" s="37" t="s">
+      <c r="E28" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="F28" s="37" t="s">
+      <c r="F28" s="13" t="s">
         <v>300</v>
       </c>
-      <c r="G28" s="37"/>
-      <c r="H28" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I28" s="38" t="s">
+      <c r="G28" s="13"/>
+      <c r="H28" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="I28" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J28" s="37" t="s">
+      <c r="J28" s="13" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="29" ht="69.75" customHeight="1">
+      <c r="A29" s="38" t="s">
+        <v>302</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="D29" s="38" t="s">
+        <v>305</v>
+      </c>
+      <c r="E29" s="38" t="s">
+        <v>306</v>
+      </c>
+      <c r="F29" s="38" t="s">
+        <v>307</v>
+      </c>
+      <c r="G29" s="38"/>
+      <c r="H29" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="I29" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="J29" s="38" t="s">
+        <v>308</v>
+      </c>
+    </row>
     <row r="30" ht="15.75" customHeight="1"/>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -6874,21 +7959,22 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$2:$J$28"/>
+  <autoFilter ref="$A$2:$J$29"/>
   <mergeCells count="6">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A27:J27"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H10 H12:H18 H20:H21 H23:H25 H27:H28">
-      <formula1>"Đạt,Không đạt"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H11 H13:H19 H21:H22 H24:H26 H28:H29">
+      <formula1>"Failed,Passed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I10 I12:I18 I20:I21 I23:I25 I27:I28">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I11 I13:I19 I21:I22 I24:I26 I28:I29">
       <formula1>"Không có,Thấp,Cao"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6921,7 +8007,7 @@
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6966,7 +8052,7 @@
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="37" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="15"/>
@@ -6980,218 +8066,218 @@
       <c r="J3" s="16"/>
     </row>
     <row r="4" ht="69.75" customHeight="1">
-      <c r="A4" s="37" t="s">
-        <v>303</v>
-      </c>
-      <c r="B4" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>305</v>
-      </c>
-      <c r="D4" s="37" t="s">
+      <c r="A4" s="38" t="s">
+        <v>310</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>311</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>312</v>
+      </c>
+      <c r="D4" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="37" t="s">
-        <v>306</v>
-      </c>
-      <c r="F4" s="37" t="s">
-        <v>307</v>
-      </c>
-      <c r="G4" s="37"/>
+      <c r="E4" s="38" t="s">
+        <v>313</v>
+      </c>
+      <c r="F4" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="G4" s="38"/>
       <c r="H4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="38" t="s">
+      <c r="I4" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J4" s="37" t="s">
-        <v>308</v>
+      <c r="J4" s="38" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="5" ht="69.75" customHeight="1">
       <c r="A5" s="13" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="G5" s="13"/>
       <c r="H5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="40" t="s">
         <v>52</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" ht="69.75" customHeight="1">
-      <c r="A6" s="37" t="s">
-        <v>316</v>
-      </c>
-      <c r="B6" s="37" t="s">
-        <v>317</v>
-      </c>
-      <c r="C6" s="37" t="s">
-        <v>318</v>
-      </c>
-      <c r="D6" s="37" t="s">
-        <v>319</v>
-      </c>
-      <c r="E6" s="37" t="s">
-        <v>320</v>
-      </c>
-      <c r="F6" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="G6" s="37"/>
+      <c r="A6" s="38" t="s">
+        <v>323</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>324</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>325</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>327</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="G6" s="38"/>
       <c r="H6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="38" t="s">
+      <c r="I6" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="37" t="s">
-        <v>321</v>
+      <c r="J6" s="38" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="7" ht="69.75" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="G7" s="13"/>
       <c r="H7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="38" t="s">
+      <c r="I7" s="40" t="s">
         <v>52</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" ht="69.75" customHeight="1">
-      <c r="A8" s="37" t="s">
-        <v>329</v>
-      </c>
-      <c r="B8" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>331</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>332</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>333</v>
-      </c>
-      <c r="F8" s="37" t="s">
-        <v>334</v>
-      </c>
-      <c r="G8" s="37"/>
+      <c r="A8" s="38" t="s">
+        <v>336</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>339</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>341</v>
+      </c>
+      <c r="G8" s="38"/>
       <c r="H8" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="38" t="s">
+      <c r="I8" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="37" t="s">
-        <v>335</v>
+      <c r="J8" s="38" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="9" ht="69.75" customHeight="1">
       <c r="A9" s="13" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>48</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="38" t="s">
+      <c r="I9" s="40" t="s">
         <v>52</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10" ht="69.75" customHeight="1">
-      <c r="A10" s="37" t="s">
-        <v>342</v>
-      </c>
-      <c r="B10" s="37" t="s">
-        <v>343</v>
-      </c>
-      <c r="C10" s="37" t="s">
-        <v>344</v>
-      </c>
-      <c r="D10" s="37" t="s">
+      <c r="A10" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>350</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>351</v>
+      </c>
+      <c r="D10" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="37" t="s">
-        <v>345</v>
-      </c>
-      <c r="F10" s="37" t="s">
-        <v>346</v>
-      </c>
-      <c r="G10" s="37"/>
+      <c r="E10" s="38" t="s">
+        <v>352</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>353</v>
+      </c>
+      <c r="G10" s="38"/>
       <c r="H10" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I10" s="38" t="s">
+      <c r="I10" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="37" t="s">
-        <v>347</v>
+      <c r="J10" s="38" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="36" t="s">
-        <v>348</v>
+      <c r="A11" s="37" t="s">
+        <v>355</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -7204,218 +8290,218 @@
       <c r="J11" s="16"/>
     </row>
     <row r="12" ht="69.75" customHeight="1">
-      <c r="A12" s="37" t="s">
-        <v>349</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>350</v>
-      </c>
-      <c r="C12" s="37" t="s">
-        <v>351</v>
-      </c>
-      <c r="D12" s="37" t="s">
-        <v>352</v>
-      </c>
-      <c r="E12" s="37" t="s">
-        <v>353</v>
-      </c>
-      <c r="F12" s="37" t="s">
-        <v>354</v>
-      </c>
-      <c r="G12" s="37"/>
+      <c r="A12" s="38" t="s">
+        <v>356</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>357</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>359</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>360</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>361</v>
+      </c>
+      <c r="G12" s="38"/>
       <c r="H12" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I12" s="38" t="s">
+      <c r="I12" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J12" s="37" t="s">
-        <v>355</v>
+      <c r="J12" s="38" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="13" ht="69.75" customHeight="1">
       <c r="A13" s="13" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I13" s="40" t="s">
+      <c r="I13" s="46" t="s">
         <v>103</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
     </row>
     <row r="14" ht="69.75" customHeight="1">
-      <c r="A14" s="37" t="s">
-        <v>363</v>
-      </c>
-      <c r="B14" s="37" t="s">
-        <v>364</v>
-      </c>
-      <c r="C14" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>366</v>
-      </c>
-      <c r="E14" s="37" t="s">
-        <v>367</v>
-      </c>
-      <c r="F14" s="37" t="s">
-        <v>368</v>
-      </c>
-      <c r="G14" s="37"/>
+      <c r="A14" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>371</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>372</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>373</v>
+      </c>
+      <c r="E14" s="38" t="s">
+        <v>374</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>375</v>
+      </c>
+      <c r="G14" s="38"/>
       <c r="H14" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I14" s="38" t="s">
+      <c r="I14" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J14" s="37" t="s">
-        <v>369</v>
+      <c r="J14" s="38" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="15" ht="69.75" customHeight="1">
       <c r="A15" s="13" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I15" s="38" t="s">
+      <c r="I15" s="40" t="s">
         <v>52</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
     </row>
     <row r="16" ht="69.75" customHeight="1">
-      <c r="A16" s="37" t="s">
-        <v>377</v>
-      </c>
-      <c r="B16" s="37" t="s">
-        <v>378</v>
-      </c>
-      <c r="C16" s="37" t="s">
-        <v>379</v>
-      </c>
-      <c r="D16" s="37" t="s">
-        <v>380</v>
-      </c>
-      <c r="E16" s="37" t="s">
-        <v>381</v>
-      </c>
-      <c r="F16" s="37" t="s">
-        <v>382</v>
-      </c>
-      <c r="G16" s="37"/>
+      <c r="A16" s="38" t="s">
+        <v>384</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>385</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>386</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>387</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>388</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>389</v>
+      </c>
+      <c r="G16" s="38"/>
       <c r="H16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I16" s="40" t="s">
+      <c r="I16" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="J16" s="37" t="s">
-        <v>383</v>
+      <c r="J16" s="38" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="17" ht="69.75" customHeight="1">
       <c r="A17" s="13" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I17" s="38" t="s">
+      <c r="I17" s="40" t="s">
         <v>52</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="18" ht="69.75" customHeight="1">
-      <c r="A18" s="37" t="s">
-        <v>391</v>
-      </c>
-      <c r="B18" s="37" t="s">
-        <v>392</v>
-      </c>
-      <c r="C18" s="37" t="s">
-        <v>393</v>
-      </c>
-      <c r="D18" s="37" t="s">
-        <v>394</v>
-      </c>
-      <c r="E18" s="37" t="s">
-        <v>395</v>
-      </c>
-      <c r="F18" s="37" t="s">
-        <v>396</v>
-      </c>
-      <c r="G18" s="37"/>
+      <c r="A18" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>399</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>400</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>401</v>
+      </c>
+      <c r="E18" s="38" t="s">
+        <v>402</v>
+      </c>
+      <c r="F18" s="38" t="s">
+        <v>403</v>
+      </c>
+      <c r="G18" s="38"/>
       <c r="H18" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I18" s="38" t="s">
+      <c r="I18" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J18" s="37" t="s">
-        <v>397</v>
+      <c r="J18" s="38" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="36" t="s">
-        <v>398</v>
+      <c r="A19" s="37" t="s">
+        <v>405</v>
       </c>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
@@ -7428,68 +8514,68 @@
       <c r="J19" s="16"/>
     </row>
     <row r="20" ht="69.75" customHeight="1">
-      <c r="A20" s="37" t="s">
-        <v>399</v>
-      </c>
-      <c r="B20" s="37" t="s">
-        <v>400</v>
-      </c>
-      <c r="C20" s="37" t="s">
-        <v>401</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>402</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>403</v>
-      </c>
-      <c r="F20" s="37" t="s">
-        <v>404</v>
-      </c>
-      <c r="G20" s="37"/>
+      <c r="A20" s="38" t="s">
+        <v>406</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>407</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>409</v>
+      </c>
+      <c r="E20" s="38" t="s">
+        <v>410</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>411</v>
+      </c>
+      <c r="G20" s="38"/>
       <c r="H20" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I20" s="38" t="s">
+      <c r="I20" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J20" s="37" t="s">
-        <v>405</v>
+      <c r="J20" s="38" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="21" ht="69.75" customHeight="1">
       <c r="A21" s="13" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="38" t="s">
+      <c r="I21" s="40" t="s">
         <v>52</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="36" t="s">
-        <v>413</v>
+      <c r="A22" s="37" t="s">
+        <v>420</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -7503,67 +8589,67 @@
     </row>
     <row r="23" ht="69.75" customHeight="1">
       <c r="A23" s="13" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G23" s="13"/>
       <c r="H23" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I23" s="38" t="s">
+      <c r="I23" s="40" t="s">
         <v>52</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
     </row>
     <row r="24" ht="69.75" customHeight="1">
-      <c r="A24" s="37" t="s">
-        <v>421</v>
-      </c>
-      <c r="B24" s="37" t="s">
-        <v>422</v>
-      </c>
-      <c r="C24" s="37" t="s">
-        <v>423</v>
-      </c>
-      <c r="D24" s="37" t="s">
+      <c r="A24" s="38" t="s">
+        <v>428</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>429</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>430</v>
+      </c>
+      <c r="D24" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="E24" s="37" t="s">
-        <v>424</v>
-      </c>
-      <c r="F24" s="37" t="s">
-        <v>425</v>
-      </c>
-      <c r="G24" s="37"/>
+      <c r="E24" s="38" t="s">
+        <v>431</v>
+      </c>
+      <c r="F24" s="38" t="s">
+        <v>432</v>
+      </c>
+      <c r="G24" s="38"/>
       <c r="H24" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I24" s="38" t="s">
+      <c r="I24" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J24" s="37" t="s">
-        <v>426</v>
+      <c r="J24" s="38" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="36" t="s">
-        <v>427</v>
+      <c r="A25" s="37" t="s">
+        <v>434</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -7576,123 +8662,123 @@
       <c r="J25" s="16"/>
     </row>
     <row r="26" ht="69.75" customHeight="1">
-      <c r="A26" s="37" t="s">
-        <v>428</v>
-      </c>
-      <c r="B26" s="37" t="s">
-        <v>429</v>
-      </c>
-      <c r="C26" s="37" t="s">
-        <v>430</v>
-      </c>
-      <c r="D26" s="37" t="s">
-        <v>431</v>
-      </c>
-      <c r="E26" s="37" t="s">
-        <v>432</v>
-      </c>
-      <c r="F26" s="37" t="s">
-        <v>433</v>
-      </c>
-      <c r="G26" s="37"/>
+      <c r="A26" s="38" t="s">
+        <v>435</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>436</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>437</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>438</v>
+      </c>
+      <c r="E26" s="38" t="s">
+        <v>439</v>
+      </c>
+      <c r="F26" s="38" t="s">
+        <v>440</v>
+      </c>
+      <c r="G26" s="38"/>
       <c r="H26" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I26" s="38" t="s">
+      <c r="I26" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J26" s="37" t="s">
-        <v>294</v>
+      <c r="J26" s="38" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="27" ht="69.75" customHeight="1">
       <c r="A27" s="13" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="G27" s="13"/>
       <c r="H27" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I27" s="38" t="s">
+      <c r="I27" s="40" t="s">
         <v>52</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
     </row>
     <row r="28" ht="69.75" customHeight="1">
-      <c r="A28" s="37" t="s">
-        <v>441</v>
-      </c>
-      <c r="B28" s="37" t="s">
-        <v>442</v>
-      </c>
-      <c r="C28" s="37" t="s">
-        <v>443</v>
-      </c>
-      <c r="D28" s="37" t="s">
-        <v>444</v>
-      </c>
-      <c r="E28" s="37" t="s">
-        <v>445</v>
-      </c>
-      <c r="F28" s="37" t="s">
-        <v>446</v>
-      </c>
-      <c r="G28" s="37"/>
+      <c r="A28" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>449</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>450</v>
+      </c>
+      <c r="D28" s="38" t="s">
+        <v>451</v>
+      </c>
+      <c r="E28" s="38" t="s">
+        <v>452</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>453</v>
+      </c>
+      <c r="G28" s="38"/>
       <c r="H28" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I28" s="38" t="s">
+      <c r="I28" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="J28" s="37" t="s">
-        <v>447</v>
+      <c r="J28" s="38" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="29" ht="69.75" customHeight="1">
       <c r="A29" s="13" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>48</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="G29" s="13"/>
       <c r="H29" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I29" s="38" t="s">
+      <c r="I29" s="40" t="s">
         <v>52</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/Testcase-OrangeHRM.xlsx
+++ b/Testcase-OrangeHRM.xlsx
@@ -1,23 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="28800" windowHeight="12930" activeTab="2"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Tổng quan" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Đăng nhập" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Quản lý người dùng" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="Danh sách nhân viên" sheetId="4" r:id="rId8"/>
+    <sheet name="Tổng quan" sheetId="1" r:id="rId1"/>
+    <sheet name="Đăng nhập" sheetId="2" r:id="rId2"/>
+    <sheet name="Quản lý người dùng" sheetId="3" r:id="rId3"/>
+    <sheet name="Danh sách nhân viên" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'Quản lý người dùng'!$A$2:$J$29</definedName>
-    <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">'Danh sách nhân viên'!$A$2:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Quản lý người dùng'!$A$2:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Danh sách nhân viên'!$A$2:$J$29</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="462">
   <si>
     <t>MA TRẬN KIỂM THỬ – KIỂM THỬ TỰ ĐỘNG ORANGEHRM (Playwright)</t>
   </si>
@@ -731,6 +735,9 @@
   </si>
   <si>
     <t>Thêm người dùng mới</t>
+  </si>
+  <si>
+    <t>TC-U09</t>
   </si>
   <si>
     <t>Thêm người dùng mới với thông tin đầy đủ và hợp lệ</t>
@@ -762,7 +769,7 @@
     <t>Dòng 3=tên tài khoản, dòng 4=vai trò, dòng 5=trạng thái, dòng 6=tên nhân viên</t>
   </si>
   <si>
-    <t>TC-U09</t>
+    <t>TC-U010</t>
   </si>
   <si>
     <t>Thêm người dùng với vai trò Quản trị viên</t>
@@ -792,7 +799,7 @@
     <t>Kiểm tra đủ hai loại vai trò: ESS và Admin</t>
   </si>
   <si>
-    <t>TC-U10</t>
+    <t>TC-U11</t>
   </si>
   <si>
     <t>Bỏ trống tên tài khoản khi thêm mới</t>
@@ -821,7 +828,7 @@
     <t>Dòng thứ 3 rỗng tương ứng tên tài khoản trống</t>
   </si>
   <si>
-    <t>TC-U11</t>
+    <t>TC-U12</t>
   </si>
   <si>
     <t>Thêm mới với tên tài khoản đã được sử dụng</t>
@@ -851,7 +858,7 @@
     <t>Dòng thứ 3 là tên tài khoản đã tồn tại</t>
   </si>
   <si>
-    <t>TC-U12</t>
+    <t>TC-U13</t>
   </si>
   <si>
     <t>Tên tài khoản có chứa ký tự đặc biệt</t>
@@ -884,7 +891,7 @@
     <t>Lỗi BG05/BG07 (09/04/2026): Tên tài khoản với @ và - được lưu thành công, không có kiểm tra dữ liệu</t>
   </si>
   <si>
-    <t>TC-U13</t>
+    <t>TC-U14</t>
   </si>
   <si>
     <t>Tên tài khoản quá dài</t>
@@ -915,7 +922,7 @@
     <t>Lỗi BG06/BG07 (09/04/2026): Tên tài khoản dài trên 60 ký tự được lưu thành công</t>
   </si>
   <si>
-    <t>TC-U14</t>
+    <t>TC-U15</t>
   </si>
   <si>
     <t>Mật khẩu và xác nhận mật khẩu không trùng khớp</t>
@@ -950,7 +957,7 @@
     <t>Chỉnh sửa người dùng</t>
   </si>
   <si>
-    <t>TC-U15</t>
+    <t>TC-U16</t>
   </si>
   <si>
     <t>Xem thông tin chi tiết của người dùng</t>
@@ -971,7 +978,7 @@
     <t>Dòng thứ 3 là tên tài khoản cần xem</t>
   </si>
   <si>
-    <t>TC-U16</t>
+    <t>TC-U17</t>
   </si>
   <si>
     <t>Thay đổi trạng thái hoạt động của người dùng</t>
@@ -1002,7 +1009,7 @@
     <t>Xóa người dùng</t>
   </si>
   <si>
-    <t>TC-U17</t>
+    <t>TC-U18</t>
   </si>
   <si>
     <t>Xóa người dùng sau khi xác nhận</t>
@@ -1028,7 +1035,7 @@
     <t>Dòng thứ 3 là tên tài khoản cần xóa</t>
   </si>
   <si>
-    <t>TC-U18</t>
+    <t>TC-U19</t>
   </si>
   <si>
     <t>Thử xóa khi chưa chọn dòng nào</t>
@@ -1049,7 +1056,7 @@
     <t>Kiểm tra nút có thuộc tính disabled hoặc không hiển thị</t>
   </si>
   <si>
-    <t>TC-U19</t>
+    <t>TC-U20</t>
   </si>
   <si>
     <t>Kiểm tra ô chọn hiển thị đầy đủ cho tất cả người dùng</t>
@@ -1073,7 +1080,7 @@
     <t>Tích hợp</t>
   </si>
   <si>
-    <t>TC-U20</t>
+    <t>TC-U21</t>
   </si>
   <si>
     <t>Tìm kiếm ngay sau khi thêm người dùng mới</t>
@@ -1100,7 +1107,7 @@
     <t>Không cần tải lại trang mới tìm được</t>
   </si>
   <si>
-    <t>TC-U21</t>
+    <t>TC-U22</t>
   </si>
   <si>
     <t>Kiểm tra thông tin người dùng sau khi lưu</t>
@@ -1708,101 +1715,257 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="14">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="32">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <charset val="134"/>
     </font>
-    <font/>
     <font>
-      <i/>
-      <sz val="9.0"/>
-      <color rgb="FF404040"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9.0"/>
-      <color rgb="FF276221"/>
+      <sz val="9"/>
+      <color rgb="FF1F3864"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9.0"/>
-      <color rgb="FF9C0006"/>
+      <sz val="9"/>
+      <color rgb="FF276221"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9.0"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+      <color rgb="FF9C0006"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9.0"/>
-      <color rgb="FF1F3864"/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
-      <color theme="1"/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12.0"/>
-      <color rgb="FF000000"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="44">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF375623"/>
         <bgColor rgb="FF375623"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5E9"/>
-        <bgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -1813,8 +1976,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0F8F0"/>
-        <bgColor rgb="FFF0F8F0"/>
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor rgb="FFD9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FBF4"/>
+        <bgColor rgb="FFF7FBF4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -1831,8 +2006,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
+        <bgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F8F0"/>
+        <bgColor rgb="FFF0F8F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -1843,38 +2030,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-        <bgColor rgb="FFD9EAD3"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7FBF4"/>
-        <bgColor rgb="FFF7FBF4"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
-    <border/>
+  <borders count="20">
     <border>
       <left/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1889,27 +2236,34 @@
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FFBFBFBF"/>
       </right>
@@ -1919,27 +2273,27 @@
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1954,27 +2308,45 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -1984,165 +2356,417 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+  <cellXfs count="38">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="10" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="10" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf quotePrefix="1" borderId="11" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="10" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="11" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="10" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="12" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -2332,26 +2956,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G1000"/>
+  <sheetFormatPr defaultColWidth="14.4333333333333" defaultRowHeight="15" customHeight="1" outlineLevelCol="6"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.14"/>
-    <col customWidth="1" min="2" max="2" width="28.0"/>
-    <col customWidth="1" min="3" max="3" width="22.0"/>
-    <col customWidth="1" min="4" max="6" width="10.0"/>
-    <col customWidth="1" min="7" max="7" width="50.0"/>
-    <col customWidth="1" min="8" max="26" width="8.71"/>
+    <col min="1" max="1" width="14.1416666666667" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="50" customWidth="1"/>
+    <col min="8" max="26" width="8.70833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30.0" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="30" customHeight="1" spans="1:7">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
@@ -2359,10 +2983,10 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="3"/>
+      <c r="G1" s="2"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="4" t="s">
+    <row r="2" ht="15.75" customHeight="1" spans="1:7">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2"/>
@@ -2370,104 +2994,104 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="3"/>
+      <c r="G2" s="2"/>
     </row>
-    <row r="3" ht="6.0" customHeight="1"/>
-    <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="5" t="s">
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="19.5" customHeight="1" spans="1:7">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="55.5" customHeight="1">
-      <c r="A5" s="6" t="s">
+    <row r="5" ht="55.5" customHeight="1" spans="1:7">
+      <c r="A5" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="6">
-        <v>21.0</v>
-      </c>
-      <c r="E5" s="9">
-        <v>19.0</v>
-      </c>
-      <c r="F5" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="G5" s="11" t="s">
+      <c r="D5" s="32">
+        <v>21</v>
+      </c>
+      <c r="E5" s="8">
+        <v>19</v>
+      </c>
+      <c r="F5" s="9">
+        <v>2</v>
+      </c>
+      <c r="G5" s="37" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" ht="55.5" customHeight="1">
-      <c r="A6" s="6" t="s">
+    <row r="6" ht="55.5" customHeight="1" spans="1:7">
+      <c r="A6" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="6">
-        <v>21.0</v>
-      </c>
-      <c r="E6" s="9">
-        <v>18.0</v>
-      </c>
-      <c r="F6" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="G6" s="11" t="s">
+      <c r="D6" s="32">
+        <v>21</v>
+      </c>
+      <c r="E6" s="8">
+        <v>18</v>
+      </c>
+      <c r="F6" s="9">
+        <v>3</v>
+      </c>
+      <c r="G6" s="37" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" ht="55.5" customHeight="1">
-      <c r="A7" s="6" t="s">
+    <row r="7" ht="55.5" customHeight="1" spans="1:7">
+      <c r="A7" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="6">
-        <v>22.0</v>
-      </c>
-      <c r="E7" s="9">
-        <v>20.0</v>
-      </c>
-      <c r="F7" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="G7" s="11" t="s">
+      <c r="D7" s="32">
+        <v>22</v>
+      </c>
+      <c r="E7" s="8">
+        <v>20</v>
+      </c>
+      <c r="F7" s="9">
+        <v>2</v>
+      </c>
+      <c r="G7" s="37" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" ht="13.5" customHeight="1"/>
-    <row r="9" ht="18.0" customHeight="1">
-      <c r="A9" s="12" t="s">
+    <row r="9" ht="18" customHeight="1" spans="1:7">
+      <c r="A9" s="35" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="2"/>
@@ -2475,82 +3099,82 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="3"/>
+      <c r="G9" s="2"/>
     </row>
-    <row r="10" ht="54.75" customHeight="1">
-      <c r="A10" s="6" t="s">
+    <row r="10" ht="54.75" customHeight="1" spans="1:7">
+      <c r="A10" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="10"/>
     </row>
-    <row r="11" ht="49.5" customHeight="1">
-      <c r="A11" s="6" t="s">
+    <row r="11" ht="49.5" customHeight="1" spans="1:7">
+      <c r="A11" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="10"/>
     </row>
-    <row r="12" ht="49.5" customHeight="1">
-      <c r="A12" s="6" t="s">
+    <row r="12" ht="49.5" customHeight="1" spans="1:7">
+      <c r="A12" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="10"/>
     </row>
-    <row r="13" ht="37.5" customHeight="1">
-      <c r="A13" s="6" t="s">
+    <row r="13" ht="37.5" customHeight="1" spans="1:7">
+      <c r="A13" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="10"/>
     </row>
-    <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="6" t="s">
+    <row r="14" ht="19.5" customHeight="1" spans="1:7">
+      <c r="A14" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="16"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="10"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -3543,34 +4167,32 @@
     <mergeCell ref="C13:G13"/>
     <mergeCell ref="C14:G14"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J2000"/>
+  <sheetFormatPr defaultColWidth="14.4333333333333" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="9.0"/>
-    <col customWidth="1" min="2" max="2" width="32.0"/>
-    <col customWidth="1" min="3" max="3" width="36.0"/>
-    <col customWidth="1" min="4" max="4" width="28.0"/>
-    <col customWidth="1" min="5" max="5" width="46.0"/>
-    <col customWidth="1" min="6" max="6" width="44.0"/>
-    <col customWidth="1" min="7" max="8" width="20.0"/>
-    <col customWidth="1" min="9" max="9" width="13.0"/>
-    <col customWidth="1" min="10" max="10" width="34.0"/>
-    <col customWidth="1" min="11" max="26" width="8.71"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="46" customWidth="1"/>
+    <col min="6" max="6" width="44" customWidth="1"/>
+    <col min="7" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="34" customWidth="1"/>
+    <col min="11" max="26" width="8.70833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" ht="25.5" customHeight="1" spans="1:10">
+      <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B1" s="2"/>
@@ -3581,615 +4203,615 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="3"/>
+      <c r="J1" s="2"/>
     </row>
-    <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="5" t="s">
+    <row r="2" ht="21.75" customHeight="1" spans="1:10">
+      <c r="A2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="19" t="s">
+    <row r="3" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A3" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="21"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="26"/>
     </row>
-    <row r="4" ht="69.75" customHeight="1">
-      <c r="A4" s="22" t="s">
+    <row r="4" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A4" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="9" t="s">
+      <c r="G4" s="19"/>
+      <c r="H4" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="J4" s="22" t="s">
+      <c r="J4" s="19" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" ht="69.75" customHeight="1">
-      <c r="A5" s="24" t="s">
+    <row r="5" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A5" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F5" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="24"/>
-      <c r="H5" s="25" t="s">
+      <c r="G5" s="20"/>
+      <c r="H5" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="24" t="s">
+      <c r="J5" s="20" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" ht="69.75" customHeight="1">
-      <c r="A6" s="22" t="s">
+    <row r="6" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A6" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="22"/>
-      <c r="H6" s="25" t="s">
+      <c r="G6" s="19"/>
+      <c r="H6" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="23" t="s">
+      <c r="I6" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="22" t="s">
+      <c r="J6" s="19" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="7" ht="69.75" customHeight="1">
-      <c r="A7" s="24" t="s">
+    <row r="7" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A7" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="G7" s="24"/>
-      <c r="H7" s="25" t="s">
+      <c r="G7" s="20"/>
+      <c r="H7" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="I7" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="24" t="s">
+      <c r="J7" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="8" ht="69.75" customHeight="1">
-      <c r="A8" s="22" t="s">
+    <row r="8" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A8" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="25" t="s">
+      <c r="G8" s="19"/>
+      <c r="H8" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="I8" s="23" t="s">
+      <c r="I8" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="22" t="s">
+      <c r="J8" s="19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="9" ht="69.75" customHeight="1">
-      <c r="A9" s="24" t="s">
+    <row r="9" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A9" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="G9" s="24"/>
-      <c r="H9" s="25" t="s">
+      <c r="G9" s="20"/>
+      <c r="H9" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="I9" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="24" t="s">
+      <c r="J9" s="20" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="27" t="s">
+    <row r="10" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A10" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="29"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="28"/>
     </row>
-    <row r="11" ht="69.75" customHeight="1">
-      <c r="A11" s="24" t="s">
+    <row r="11" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A11" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="G11" s="24"/>
-      <c r="H11" s="25" t="s">
+      <c r="G11" s="20"/>
+      <c r="H11" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="I11" s="23" t="s">
+      <c r="I11" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="J11" s="24" t="s">
+      <c r="J11" s="20" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="12" ht="69.75" customHeight="1">
-      <c r="A12" s="22" t="s">
+    <row r="12" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A12" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="G12" s="22"/>
-      <c r="H12" s="30" t="s">
+      <c r="G12" s="19"/>
+      <c r="H12" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="I12" s="31" t="s">
+      <c r="I12" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="J12" s="26" t="s">
+      <c r="J12" s="19" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="13" ht="69.75" customHeight="1">
-      <c r="A13" s="24" t="s">
+    <row r="13" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A13" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F13" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="G13" s="24"/>
-      <c r="H13" s="25" t="s">
+      <c r="G13" s="20"/>
+      <c r="H13" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="I13" s="23" t="s">
+      <c r="I13" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="J13" s="24" t="s">
+      <c r="J13" s="20" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="14" ht="69.75" customHeight="1">
-      <c r="A14" s="22" t="s">
+    <row r="14" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A14" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="F14" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="G14" s="22"/>
-      <c r="H14" s="30" t="s">
+      <c r="G14" s="19"/>
+      <c r="H14" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="I14" s="31" t="s">
+      <c r="I14" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="J14" s="26" t="s">
+      <c r="J14" s="19" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="27" t="s">
+    <row r="15" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A15" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="29"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="28"/>
     </row>
-    <row r="16" ht="69.75" customHeight="1">
-      <c r="A16" s="22" t="s">
+    <row r="16" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A16" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="G16" s="22"/>
-      <c r="H16" s="25" t="s">
+      <c r="G16" s="19"/>
+      <c r="H16" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="I16" s="23" t="s">
+      <c r="I16" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="J16" s="22" t="s">
+      <c r="J16" s="19" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="17" ht="69.75" customHeight="1">
-      <c r="A17" s="24" t="s">
+    <row r="17" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A17" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="F17" s="24" t="s">
+      <c r="F17" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="G17" s="24"/>
-      <c r="H17" s="25" t="s">
+      <c r="G17" s="20"/>
+      <c r="H17" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="23" t="s">
+      <c r="I17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="J17" s="24" t="s">
+      <c r="J17" s="20" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="18" ht="69.75" customHeight="1">
-      <c r="A18" s="22" t="s">
+    <row r="18" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A18" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="G18" s="22"/>
-      <c r="H18" s="25" t="s">
+      <c r="G18" s="19"/>
+      <c r="H18" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="I18" s="23" t="s">
+      <c r="I18" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="J18" s="22" t="s">
+      <c r="J18" s="19" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="19" ht="69.75" customHeight="1">
-      <c r="A19" s="24" t="s">
+    <row r="19" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A19" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="F19" s="24" t="s">
+      <c r="F19" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="G19" s="24"/>
-      <c r="H19" s="25" t="s">
+      <c r="G19" s="20"/>
+      <c r="H19" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="I19" s="23" t="s">
+      <c r="I19" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="J19" s="24" t="s">
+      <c r="J19" s="20" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="34" t="s">
+    <row r="20" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A20" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="29"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="28"/>
     </row>
-    <row r="21" ht="69.75" customHeight="1">
-      <c r="A21" s="24" t="s">
+    <row r="21" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A21" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="C21" s="32" t="s">
+      <c r="C21" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="E21" s="32" t="s">
+      <c r="E21" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F21" s="32" t="s">
+      <c r="F21" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="G21" s="32"/>
-      <c r="H21" s="25" t="s">
+      <c r="G21" s="20"/>
+      <c r="H21" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="I21" s="35" t="s">
+      <c r="I21" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="J21" s="32"/>
+      <c r="J21" s="20"/>
     </row>
-    <row r="22" ht="69.75" customHeight="1">
-      <c r="A22" s="36"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
+    <row r="22" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
     </row>
-    <row r="23" ht="69.75" customHeight="1">
-      <c r="A23" s="36"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
+    <row r="23" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
     </row>
-    <row r="24" ht="69.75" customHeight="1">
-      <c r="A24" s="36"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="36"/>
+    <row r="24" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
     </row>
-    <row r="25" ht="69.75" customHeight="1">
-      <c r="A25" s="36"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
+    <row r="25" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A25" s="23"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
     </row>
-    <row r="26" ht="69.75" customHeight="1">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="36"/>
+    <row r="26" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A26" s="23"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="23"/>
     </row>
-    <row r="27" ht="69.75" customHeight="1">
-      <c r="A27" s="36"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="36"/>
+    <row r="27" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23"/>
     </row>
     <row r="28" ht="15.75" customHeight="1"/>
     <row r="29" ht="15.75" customHeight="1"/>
@@ -6172,40 +6794,38 @@
     <mergeCell ref="A15:J15"/>
     <mergeCell ref="A20:J20"/>
   </mergeCells>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H9 H11:H14 H16:H19 H21">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H21 H4:H9 H11:H14 H16:H19">
       <formula1>"Fail,Pass"</formula1>
     </dataValidation>
   </dataValidations>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:R1001"/>
+  <sheetFormatPr defaultColWidth="14.4333333333333" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="9.0"/>
-    <col customWidth="1" min="2" max="2" width="32.0"/>
-    <col customWidth="1" min="3" max="3" width="36.0"/>
-    <col customWidth="1" min="4" max="4" width="28.0"/>
-    <col customWidth="1" min="5" max="5" width="46.0"/>
-    <col customWidth="1" min="6" max="6" width="44.0"/>
-    <col customWidth="1" min="7" max="7" width="20.0"/>
-    <col customWidth="1" min="8" max="8" width="14.0"/>
-    <col customWidth="1" min="9" max="9" width="13.0"/>
-    <col customWidth="1" min="10" max="10" width="34.0"/>
-    <col customWidth="1" min="11" max="26" width="8.71"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="46" customWidth="1"/>
+    <col min="6" max="6" width="44" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="34" customWidth="1"/>
+    <col min="11" max="26" width="8.70833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" ht="25.5" customHeight="1" spans="1:10">
+      <c r="A1" s="1" t="s">
         <v>154</v>
       </c>
       <c r="B1" s="2"/>
@@ -6216,776 +6836,776 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="3"/>
+      <c r="J1" s="2"/>
     </row>
-    <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="5" t="s">
+    <row r="2" ht="21.75" customHeight="1" spans="1:10">
+      <c r="A2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="37" t="s">
+    <row r="3" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A3" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="16"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="10"/>
     </row>
-    <row r="4" ht="69.75" customHeight="1">
-      <c r="A4" s="38" t="s">
+    <row r="4" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A4" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="E4" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="38" t="s">
+      <c r="F4" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="G4" s="38"/>
-      <c r="H4" s="39" t="s">
+      <c r="G4" s="6"/>
+      <c r="H4" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="I4" s="40" t="s">
+      <c r="I4" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J4" s="38" t="s">
+      <c r="J4" s="6" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="5" ht="69.75" customHeight="1">
-      <c r="A5" s="13" t="s">
+    <row r="5" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A5" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="41" t="s">
+      <c r="G5" s="7"/>
+      <c r="H5" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="I5" s="40" t="s">
+      <c r="I5" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="7" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="6" ht="69.75" customHeight="1">
-      <c r="A6" s="38" t="s">
+    <row r="6" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A6" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="E6" s="38" t="s">
+      <c r="E6" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F6" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="G6" s="38"/>
-      <c r="H6" s="41" t="s">
+      <c r="G6" s="6"/>
+      <c r="H6" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="I6" s="40" t="s">
+      <c r="I6" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="38" t="s">
+      <c r="J6" s="6" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="7" ht="69.75" customHeight="1">
-      <c r="A7" s="13" t="s">
+    <row r="7" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A7" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="39" t="s">
+      <c r="G7" s="7"/>
+      <c r="H7" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="I7" s="40" t="s">
+      <c r="I7" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="7" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="8" ht="69.75" customHeight="1">
-      <c r="A8" s="38" t="s">
+    <row r="8" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A8" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="F8" s="38" t="s">
+      <c r="F8" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="G8" s="38"/>
-      <c r="H8" s="41" t="s">
+      <c r="G8" s="6"/>
+      <c r="H8" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="I8" s="40" t="s">
+      <c r="I8" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="38" t="s">
+      <c r="J8" s="6" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="9" ht="69.75" customHeight="1">
-      <c r="A9" s="13" t="s">
+    <row r="9" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A9" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="G9" s="42"/>
-      <c r="H9" s="41" t="s">
+      <c r="G9" s="14"/>
+      <c r="H9" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="I9" s="40" t="s">
+      <c r="I9" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="7" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="10" ht="69.75" customHeight="1">
-      <c r="A10" s="38" t="s">
+    <row r="10" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A10" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="E10" s="38" t="s">
+      <c r="E10" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="G10" s="38"/>
-      <c r="H10" s="41" t="s">
+      <c r="G10" s="6"/>
+      <c r="H10" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="I10" s="40" t="s">
+      <c r="I10" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="38" t="s">
+      <c r="J10" s="6" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="11" ht="69.75" customHeight="1">
-      <c r="A11" s="38" t="s">
+    <row r="11" ht="69.75" customHeight="1" spans="1:18">
+      <c r="A11" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="F11" s="38" t="s">
+      <c r="F11" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38" t="s">
+      <c r="G11" s="6"/>
+      <c r="H11" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="I11" s="38" t="s">
+      <c r="I11" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="J11" s="38" t="s">
+      <c r="J11" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="K11" s="43"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="43"/>
-      <c r="N11" s="43"/>
-      <c r="O11" s="43"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15"/>
+      <c r="R11" s="15"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="37" t="s">
+    <row r="12" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A12" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="16"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="10"/>
     </row>
-    <row r="13" ht="69.75" customHeight="1">
-      <c r="A13" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="B13" s="38" t="s">
+    <row r="13" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A13" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="C13" s="38" t="s">
+      <c r="B13" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="C13" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="E13" s="38" t="s">
+      <c r="D13" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="F13" s="38" t="s">
+      <c r="E13" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="G13" s="38"/>
-      <c r="H13" s="39" t="s">
+      <c r="F13" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="G13" s="6"/>
+      <c r="H13" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="I13" s="40" t="s">
+      <c r="I13" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J13" s="38" t="s">
-        <v>216</v>
+      <c r="J13" s="6" t="s">
+        <v>217</v>
       </c>
     </row>
-    <row r="14" ht="69.75" customHeight="1">
-      <c r="A14" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="B14" s="13" t="s">
+    <row r="14" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A14" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="B14" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="C14" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="D14" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="E14" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="41" t="s">
+      <c r="F14" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="G14" s="7"/>
+      <c r="H14" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="I14" s="40" t="s">
+      <c r="I14" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>223</v>
+      <c r="J14" s="7" t="s">
+        <v>224</v>
       </c>
     </row>
-    <row r="15" ht="69.75" customHeight="1">
-      <c r="A15" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="B15" s="38" t="s">
+    <row r="15" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A15" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="B15" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="E15" s="38" t="s">
+      <c r="D15" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="F15" s="38" t="s">
+      <c r="E15" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="G15" s="38"/>
-      <c r="H15" s="41" t="s">
+      <c r="F15" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="I15" s="40" t="s">
+      <c r="I15" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J15" s="38" t="s">
-        <v>230</v>
+      <c r="J15" s="6" t="s">
+        <v>231</v>
       </c>
     </row>
-    <row r="16" ht="69.75" customHeight="1">
-      <c r="A16" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="B16" s="13" t="s">
+    <row r="16" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A16" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="B16" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="C16" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="D16" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="E16" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="41" t="s">
+      <c r="F16" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="I16" s="40" t="s">
+      <c r="I16" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J16" s="13" t="s">
-        <v>237</v>
+      <c r="J16" s="7" t="s">
+        <v>238</v>
       </c>
     </row>
-    <row r="17" ht="69.75" customHeight="1">
-      <c r="A17" s="38" t="s">
-        <v>238</v>
-      </c>
-      <c r="B17" s="38" t="s">
+    <row r="17" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A17" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="C17" s="38" t="s">
+      <c r="B17" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="C17" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="E17" s="38" t="s">
+      <c r="D17" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="F17" s="38" t="s">
+      <c r="E17" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="G17" s="38"/>
-      <c r="H17" s="44" t="s">
+      <c r="F17" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="I17" s="45" t="s">
-        <v>244</v>
-      </c>
-      <c r="J17" s="38" t="s">
+      <c r="I17" s="16" t="s">
         <v>245</v>
       </c>
+      <c r="J17" s="6" t="s">
+        <v>246</v>
+      </c>
     </row>
-    <row r="18" ht="69.75" customHeight="1">
-      <c r="A18" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="B18" s="13" t="s">
+    <row r="18" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A18" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="B18" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="C18" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="D18" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="E18" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="G18" s="13"/>
-      <c r="H18" s="44" t="s">
+      <c r="F18" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G18" s="7"/>
+      <c r="H18" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="I18" s="45" t="s">
-        <v>244</v>
-      </c>
-      <c r="J18" s="13" t="s">
-        <v>252</v>
+      <c r="I18" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>253</v>
       </c>
     </row>
-    <row r="19" ht="69.75" customHeight="1">
-      <c r="A19" s="38" t="s">
-        <v>253</v>
-      </c>
-      <c r="B19" s="38" t="s">
+    <row r="19" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A19" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="B19" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D19" s="38" t="s">
+      <c r="C19" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="E19" s="38" t="s">
+      <c r="D19" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="F19" s="38" t="s">
+      <c r="E19" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="G19" s="38"/>
-      <c r="H19" s="41" t="s">
+      <c r="F19" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="G19" s="6"/>
+      <c r="H19" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="I19" s="40" t="s">
+      <c r="I19" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J19" s="38" t="s">
-        <v>259</v>
+      <c r="J19" s="6" t="s">
+        <v>260</v>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="16"/>
+    <row r="20" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A20" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="10"/>
     </row>
-    <row r="21" ht="69.75" customHeight="1">
-      <c r="A21" s="38" t="s">
-        <v>261</v>
-      </c>
-      <c r="B21" s="38" t="s">
+    <row r="21" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A21" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="B21" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="D21" s="38" t="s">
+      <c r="C21" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="E21" s="38" t="s">
-        <v>264</v>
-      </c>
-      <c r="F21" s="38" t="s">
+      <c r="E21" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="G21" s="38"/>
-      <c r="H21" s="41" t="s">
+      <c r="F21" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="I21" s="40" t="s">
+      <c r="I21" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J21" s="38" t="s">
-        <v>266</v>
+      <c r="J21" s="6" t="s">
+        <v>267</v>
       </c>
     </row>
-    <row r="22" ht="69.75" customHeight="1">
-      <c r="A22" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B22" s="13" t="s">
+    <row r="22" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A22" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="B22" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="C22" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="D22" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="E22" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="G22" s="13"/>
-      <c r="H22" s="41" t="s">
+      <c r="F22" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="G22" s="7"/>
+      <c r="H22" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="I22" s="40" t="s">
+      <c r="I22" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="13" t="s">
-        <v>273</v>
+      <c r="J22" s="7" t="s">
+        <v>274</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="16"/>
+    <row r="23" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A23" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="10"/>
     </row>
-    <row r="24" ht="69.75" customHeight="1">
-      <c r="A24" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="B24" s="13" t="s">
+    <row r="24" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A24" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="B24" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="C24" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="D24" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="F24" s="13" t="s">
+      <c r="E24" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="G24" s="13"/>
-      <c r="H24" s="41" t="s">
+      <c r="F24" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="G24" s="7"/>
+      <c r="H24" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="I24" s="40" t="s">
+      <c r="I24" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J24" s="13" t="s">
-        <v>281</v>
+      <c r="J24" s="7" t="s">
+        <v>282</v>
       </c>
     </row>
-    <row r="25" ht="69.75" customHeight="1">
-      <c r="A25" s="38" t="s">
-        <v>282</v>
-      </c>
-      <c r="B25" s="38" t="s">
+    <row r="25" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A25" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="B25" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="D25" s="38" t="s">
+      <c r="C25" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E25" s="38" t="s">
-        <v>285</v>
-      </c>
-      <c r="F25" s="38" t="s">
+      <c r="E25" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="G25" s="38"/>
-      <c r="H25" s="41" t="s">
+      <c r="F25" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G25" s="6"/>
+      <c r="H25" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="I25" s="40" t="s">
+      <c r="I25" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J25" s="38" t="s">
-        <v>287</v>
+      <c r="J25" s="6" t="s">
+        <v>288</v>
       </c>
     </row>
-    <row r="26" ht="69.75" customHeight="1">
-      <c r="A26" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="B26" s="13" t="s">
+    <row r="26" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A26" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="B26" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="C26" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="F26" s="13" t="s">
+      <c r="E26" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="G26" s="13"/>
-      <c r="H26" s="44" t="s">
+      <c r="F26" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="G26" s="7"/>
+      <c r="H26" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="I26" s="46" t="s">
+      <c r="I26" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="J26" s="13" t="s">
-        <v>293</v>
+      <c r="J26" s="7" t="s">
+        <v>294</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="37" t="s">
-        <v>294</v>
-      </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="16"/>
+    <row r="27" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A27" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="10"/>
     </row>
-    <row r="28" ht="69.75" customHeight="1">
-      <c r="A28" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="B28" s="13" t="s">
+    <row r="28" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A28" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="B28" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="C28" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="D28" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="F28" s="13" t="s">
+      <c r="E28" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="G28" s="13"/>
-      <c r="H28" s="41" t="s">
+      <c r="F28" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="G28" s="7"/>
+      <c r="H28" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="I28" s="40" t="s">
+      <c r="I28" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J28" s="13" t="s">
-        <v>301</v>
+      <c r="J28" s="7" t="s">
+        <v>302</v>
       </c>
     </row>
-    <row r="29" ht="69.75" customHeight="1">
-      <c r="A29" s="38" t="s">
-        <v>302</v>
-      </c>
-      <c r="B29" s="38" t="s">
+    <row r="29" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A29" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="C29" s="38" t="s">
+      <c r="B29" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="D29" s="38" t="s">
+      <c r="C29" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="E29" s="38" t="s">
+      <c r="D29" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="F29" s="38" t="s">
+      <c r="E29" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="G29" s="38"/>
-      <c r="H29" s="41" t="s">
+      <c r="F29" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="G29" s="6"/>
+      <c r="H29" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="I29" s="40" t="s">
+      <c r="I29" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J29" s="38" t="s">
-        <v>308</v>
+      <c r="J29" s="6" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>
@@ -7961,7 +8581,9 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$2:$J$29"/>
+  <autoFilter ref="A2:J29">
+    <extLst/>
+  </autoFilter>
   <mergeCells count="6">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A3:J3"/>
@@ -7970,44 +8592,42 @@
     <mergeCell ref="A23:J23"/>
     <mergeCell ref="A27:J27"/>
   </mergeCells>
-  <dataValidations>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I11 I13:I19 I21:I22 I24:I26 I28:I29">
+      <formula1>"Không có,Thấp,Cao"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H11 H13:H19 H21:H22 H24:H26 H28:H29">
       <formula1>"Failed,Passed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I11 I13:I19 I21:I22 I24:I26 I28:I29">
-      <formula1>"Không có,Thấp,Cao"</formula1>
-    </dataValidation>
   </dataValidations>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J1000"/>
+  <sheetFormatPr defaultColWidth="14.4333333333333" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="9.0"/>
-    <col customWidth="1" min="2" max="2" width="32.0"/>
-    <col customWidth="1" min="3" max="3" width="36.0"/>
-    <col customWidth="1" min="4" max="4" width="28.0"/>
-    <col customWidth="1" min="5" max="5" width="46.0"/>
-    <col customWidth="1" min="6" max="6" width="44.0"/>
-    <col customWidth="1" min="7" max="7" width="20.0"/>
-    <col customWidth="1" min="8" max="8" width="14.0"/>
-    <col customWidth="1" min="9" max="9" width="13.0"/>
-    <col customWidth="1" min="10" max="10" width="34.0"/>
-    <col customWidth="1" min="11" max="26" width="8.71"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="46" customWidth="1"/>
+    <col min="6" max="6" width="44" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="34" customWidth="1"/>
+    <col min="11" max="26" width="8.70833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" s="17" t="s">
-        <v>309</v>
+    <row r="1" ht="25.5" customHeight="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>310</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8017,768 +8637,768 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="3"/>
+      <c r="J1" s="2"/>
     </row>
-    <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="5" t="s">
+    <row r="2" ht="21.75" customHeight="1" spans="1:10">
+      <c r="A2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="37" t="s">
+    <row r="3" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A3" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="16"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="10"/>
     </row>
-    <row r="4" ht="69.75" customHeight="1">
-      <c r="A4" s="38" t="s">
-        <v>310</v>
-      </c>
-      <c r="B4" s="38" t="s">
+    <row r="4" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A4" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="B4" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="C4" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="F4" s="38" t="s">
+      <c r="E4" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="G4" s="38"/>
-      <c r="H4" s="9" t="s">
+      <c r="F4" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="40" t="s">
+      <c r="I4" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J4" s="38" t="s">
-        <v>315</v>
+      <c r="J4" s="6" t="s">
+        <v>316</v>
       </c>
     </row>
-    <row r="5" ht="69.75" customHeight="1">
-      <c r="A5" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="B5" s="13" t="s">
+    <row r="5" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A5" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="B5" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="C5" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="D5" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="E5" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="9" t="s">
+      <c r="F5" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="40" t="s">
+      <c r="I5" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="13" t="s">
-        <v>322</v>
+      <c r="J5" s="7" t="s">
+        <v>323</v>
       </c>
     </row>
-    <row r="6" ht="69.75" customHeight="1">
-      <c r="A6" s="38" t="s">
-        <v>323</v>
-      </c>
-      <c r="B6" s="38" t="s">
+    <row r="6" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A6" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="B6" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="C6" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="E6" s="38" t="s">
+      <c r="D6" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="E6" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="G6" s="38"/>
-      <c r="H6" s="9" t="s">
+      <c r="G6" s="6"/>
+      <c r="H6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="40" t="s">
+      <c r="I6" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="38" t="s">
-        <v>328</v>
+      <c r="J6" s="6" t="s">
+        <v>329</v>
       </c>
     </row>
-    <row r="7" ht="69.75" customHeight="1">
-      <c r="A7" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="B7" s="13" t="s">
+    <row r="7" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A7" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="C7" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="D7" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="E7" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="9" t="s">
+      <c r="F7" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="40" t="s">
+      <c r="I7" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="13" t="s">
-        <v>335</v>
+      <c r="J7" s="7" t="s">
+        <v>336</v>
       </c>
     </row>
-    <row r="8" ht="69.75" customHeight="1">
-      <c r="A8" s="38" t="s">
-        <v>336</v>
-      </c>
-      <c r="B8" s="38" t="s">
+    <row r="8" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A8" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="B8" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="C8" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="D8" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="F8" s="38" t="s">
+      <c r="E8" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="G8" s="38"/>
-      <c r="H8" s="9" t="s">
+      <c r="F8" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="40" t="s">
+      <c r="I8" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="38" t="s">
-        <v>342</v>
+      <c r="J8" s="6" t="s">
+        <v>343</v>
       </c>
     </row>
-    <row r="9" ht="69.75" customHeight="1">
-      <c r="A9" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="B9" s="13" t="s">
+    <row r="9" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A9" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="B9" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="C9" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="13" t="s">
-        <v>346</v>
-      </c>
-      <c r="F9" s="13" t="s">
+      <c r="E9" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="9" t="s">
+      <c r="F9" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="40" t="s">
+      <c r="I9" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="13" t="s">
-        <v>348</v>
+      <c r="J9" s="7" t="s">
+        <v>349</v>
       </c>
     </row>
-    <row r="10" ht="69.75" customHeight="1">
-      <c r="A10" s="38" t="s">
-        <v>349</v>
-      </c>
-      <c r="B10" s="38" t="s">
+    <row r="10" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A10" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="B10" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="C10" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="38" t="s">
-        <v>352</v>
-      </c>
-      <c r="F10" s="38" t="s">
+      <c r="E10" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="G10" s="38"/>
-      <c r="H10" s="9" t="s">
+      <c r="F10" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I10" s="40" t="s">
+      <c r="I10" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="38" t="s">
-        <v>354</v>
+      <c r="J10" s="6" t="s">
+        <v>355</v>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="37" t="s">
-        <v>355</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="16"/>
+    <row r="11" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A11" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="10"/>
     </row>
-    <row r="12" ht="69.75" customHeight="1">
-      <c r="A12" s="38" t="s">
-        <v>356</v>
-      </c>
-      <c r="B12" s="38" t="s">
+    <row r="12" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A12" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="B12" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="C12" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="D12" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="F12" s="38" t="s">
+      <c r="E12" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="G12" s="38"/>
-      <c r="H12" s="9" t="s">
+      <c r="F12" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I12" s="40" t="s">
+      <c r="I12" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J12" s="38" t="s">
-        <v>362</v>
+      <c r="J12" s="6" t="s">
+        <v>363</v>
       </c>
     </row>
-    <row r="13" ht="69.75" customHeight="1">
-      <c r="A13" s="13" t="s">
-        <v>363</v>
-      </c>
-      <c r="B13" s="13" t="s">
+    <row r="13" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A13" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="B13" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="C13" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="D13" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="E13" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="10" t="s">
+      <c r="F13" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="G13" s="7"/>
+      <c r="H13" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I13" s="46" t="s">
+      <c r="I13" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="J13" s="13" t="s">
-        <v>369</v>
+      <c r="J13" s="7" t="s">
+        <v>370</v>
       </c>
     </row>
-    <row r="14" ht="69.75" customHeight="1">
-      <c r="A14" s="38" t="s">
-        <v>370</v>
-      </c>
-      <c r="B14" s="38" t="s">
+    <row r="14" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A14" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="B14" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="C14" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="E14" s="38" t="s">
+      <c r="D14" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="F14" s="38" t="s">
+      <c r="E14" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="G14" s="38"/>
-      <c r="H14" s="9" t="s">
+      <c r="F14" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I14" s="40" t="s">
+      <c r="I14" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J14" s="38" t="s">
-        <v>376</v>
+      <c r="J14" s="6" t="s">
+        <v>377</v>
       </c>
     </row>
-    <row r="15" ht="69.75" customHeight="1">
-      <c r="A15" s="13" t="s">
-        <v>377</v>
-      </c>
-      <c r="B15" s="13" t="s">
+    <row r="15" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A15" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="B15" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="C15" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="D15" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="E15" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="9" t="s">
+      <c r="F15" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="H15" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I15" s="40" t="s">
+      <c r="I15" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J15" s="13" t="s">
-        <v>383</v>
+      <c r="J15" s="7" t="s">
+        <v>384</v>
       </c>
     </row>
-    <row r="16" ht="69.75" customHeight="1">
-      <c r="A16" s="38" t="s">
-        <v>384</v>
-      </c>
-      <c r="B16" s="38" t="s">
+    <row r="16" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A16" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="B16" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="D16" s="38" t="s">
+      <c r="C16" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="E16" s="38" t="s">
+      <c r="D16" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="F16" s="38" t="s">
+      <c r="E16" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="G16" s="38"/>
-      <c r="H16" s="10" t="s">
+      <c r="F16" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="G16" s="6"/>
+      <c r="H16" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I16" s="46" t="s">
+      <c r="I16" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="J16" s="38" t="s">
-        <v>390</v>
+      <c r="J16" s="6" t="s">
+        <v>391</v>
       </c>
     </row>
-    <row r="17" ht="69.75" customHeight="1">
-      <c r="A17" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="B17" s="13" t="s">
+    <row r="17" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A17" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="B17" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="C17" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="D17" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="E17" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="9" t="s">
+      <c r="F17" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="G17" s="7"/>
+      <c r="H17" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I17" s="40" t="s">
+      <c r="I17" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J17" s="13" t="s">
-        <v>397</v>
+      <c r="J17" s="7" t="s">
+        <v>398</v>
       </c>
     </row>
-    <row r="18" ht="69.75" customHeight="1">
-      <c r="A18" s="38" t="s">
-        <v>398</v>
-      </c>
-      <c r="B18" s="38" t="s">
+    <row r="18" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A18" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="B18" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="C18" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="E18" s="38" t="s">
+      <c r="D18" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="F18" s="38" t="s">
+      <c r="E18" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="G18" s="38"/>
-      <c r="H18" s="9" t="s">
+      <c r="F18" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="H18" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I18" s="40" t="s">
+      <c r="I18" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J18" s="38" t="s">
-        <v>404</v>
+      <c r="J18" s="6" t="s">
+        <v>405</v>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="37" t="s">
-        <v>405</v>
-      </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="16"/>
+    <row r="19" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A19" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="10"/>
     </row>
-    <row r="20" ht="69.75" customHeight="1">
-      <c r="A20" s="38" t="s">
-        <v>406</v>
-      </c>
-      <c r="B20" s="38" t="s">
+    <row r="20" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A20" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="B20" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="C20" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="E20" s="38" t="s">
+      <c r="D20" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="F20" s="38" t="s">
+      <c r="E20" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="9" t="s">
+      <c r="F20" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="G20" s="6"/>
+      <c r="H20" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I20" s="40" t="s">
+      <c r="I20" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J20" s="38" t="s">
-        <v>412</v>
+      <c r="J20" s="6" t="s">
+        <v>413</v>
       </c>
     </row>
-    <row r="21" ht="69.75" customHeight="1">
-      <c r="A21" s="13" t="s">
-        <v>413</v>
-      </c>
-      <c r="B21" s="13" t="s">
+    <row r="21" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A21" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="B21" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="C21" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="D21" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="E21" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="G21" s="13"/>
-      <c r="H21" s="9" t="s">
+      <c r="F21" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="G21" s="7"/>
+      <c r="H21" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="40" t="s">
+      <c r="I21" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J21" s="13" t="s">
-        <v>419</v>
+      <c r="J21" s="7" t="s">
+        <v>420</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="37" t="s">
-        <v>420</v>
-      </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="16"/>
+    <row r="22" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A22" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="10"/>
     </row>
-    <row r="23" ht="69.75" customHeight="1">
-      <c r="A23" s="13" t="s">
-        <v>421</v>
-      </c>
-      <c r="B23" s="13" t="s">
+    <row r="23" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A23" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="B23" s="7" t="s">
         <v>423</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="C23" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="D23" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="E23" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="G23" s="13"/>
-      <c r="H23" s="9" t="s">
+      <c r="F23" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="G23" s="7"/>
+      <c r="H23" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I23" s="40" t="s">
+      <c r="I23" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J23" s="13" t="s">
-        <v>427</v>
+      <c r="J23" s="7" t="s">
+        <v>428</v>
       </c>
     </row>
-    <row r="24" ht="69.75" customHeight="1">
-      <c r="A24" s="38" t="s">
-        <v>428</v>
-      </c>
-      <c r="B24" s="38" t="s">
+    <row r="24" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A24" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="C24" s="38" t="s">
+      <c r="B24" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="C24" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E24" s="38" t="s">
-        <v>431</v>
-      </c>
-      <c r="F24" s="38" t="s">
+      <c r="E24" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="G24" s="38"/>
-      <c r="H24" s="9" t="s">
+      <c r="F24" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="G24" s="6"/>
+      <c r="H24" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I24" s="40" t="s">
+      <c r="I24" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J24" s="38" t="s">
-        <v>433</v>
+      <c r="J24" s="6" t="s">
+        <v>434</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="37" t="s">
-        <v>434</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="16"/>
+    <row r="25" ht="15.75" customHeight="1" spans="1:10">
+      <c r="A25" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="10"/>
     </row>
-    <row r="26" ht="69.75" customHeight="1">
-      <c r="A26" s="38" t="s">
-        <v>435</v>
-      </c>
-      <c r="B26" s="38" t="s">
+    <row r="26" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A26" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="B26" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="D26" s="38" t="s">
+      <c r="C26" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="E26" s="38" t="s">
+      <c r="D26" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="F26" s="38" t="s">
+      <c r="E26" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="G26" s="38"/>
-      <c r="H26" s="9" t="s">
+      <c r="F26" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="G26" s="6"/>
+      <c r="H26" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I26" s="40" t="s">
+      <c r="I26" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J26" s="38" t="s">
-        <v>301</v>
+      <c r="J26" s="6" t="s">
+        <v>302</v>
       </c>
     </row>
-    <row r="27" ht="69.75" customHeight="1">
-      <c r="A27" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="B27" s="13" t="s">
+    <row r="27" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A27" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="B27" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="C27" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="D27" s="7" t="s">
         <v>445</v>
       </c>
-      <c r="F27" s="13" t="s">
+      <c r="E27" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="G27" s="13"/>
-      <c r="H27" s="9" t="s">
+      <c r="F27" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="G27" s="7"/>
+      <c r="H27" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I27" s="40" t="s">
+      <c r="I27" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="13" t="s">
-        <v>447</v>
+      <c r="J27" s="7" t="s">
+        <v>448</v>
       </c>
     </row>
-    <row r="28" ht="69.75" customHeight="1">
-      <c r="A28" s="38" t="s">
-        <v>448</v>
-      </c>
-      <c r="B28" s="38" t="s">
+    <row r="28" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A28" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="C28" s="38" t="s">
+      <c r="B28" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="D28" s="38" t="s">
+      <c r="C28" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="E28" s="38" t="s">
+      <c r="D28" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="F28" s="38" t="s">
+      <c r="E28" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="G28" s="38"/>
-      <c r="H28" s="9" t="s">
+      <c r="F28" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="G28" s="6"/>
+      <c r="H28" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I28" s="40" t="s">
+      <c r="I28" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J28" s="38" t="s">
-        <v>454</v>
+      <c r="J28" s="6" t="s">
+        <v>455</v>
       </c>
     </row>
-    <row r="29" ht="69.75" customHeight="1">
-      <c r="A29" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="B29" s="13" t="s">
+    <row r="29" ht="69.75" customHeight="1" spans="1:10">
+      <c r="A29" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="B29" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="C29" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>458</v>
-      </c>
-      <c r="F29" s="13" t="s">
+      <c r="E29" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="G29" s="13"/>
-      <c r="H29" s="9" t="s">
+      <c r="F29" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="G29" s="7"/>
+      <c r="H29" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I29" s="40" t="s">
+      <c r="I29" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>460</v>
+      <c r="J29" s="7" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1"/>
@@ -9753,7 +10373,9 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$2:$J$29"/>
+  <autoFilter ref="A2:J29">
+    <extLst/>
+  </autoFilter>
   <mergeCells count="6">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A3:J3"/>
@@ -9762,9 +10384,8 @@
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A25:J25"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Testcase-OrangeHRM.xlsx
+++ b/Testcase-OrangeHRM.xlsx
@@ -769,7 +769,7 @@
     <t>Dòng 3=tên tài khoản, dòng 4=vai trò, dòng 5=trạng thái, dòng 6=tên nhân viên</t>
   </si>
   <si>
-    <t>TC-U010</t>
+    <t>TC-U10</t>
   </si>
   <si>
     <t>Thêm người dùng với vai trò Quản trị viên</t>
@@ -1717,10 +1717,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="32">
     <font>
@@ -1819,9 +1819,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1829,6 +1859,59 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1851,45 +1934,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1897,15 +1942,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1915,43 +1952,6 @@
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2030,7 +2030,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2042,175 +2204,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2359,21 +2359,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -2394,21 +2379,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2442,8 +2412,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2451,150 +2421,180 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">

--- a/Testcase-OrangeHRM.xlsx
+++ b/Testcase-OrangeHRM.xlsx
@@ -1,27 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12930" activeTab="2"/>
-  </bookViews>
   <sheets>
-    <sheet name="Tổng quan" sheetId="1" r:id="rId1"/>
-    <sheet name="Đăng nhập" sheetId="2" r:id="rId2"/>
-    <sheet name="Quản lý người dùng" sheetId="3" r:id="rId3"/>
-    <sheet name="Danh sách nhân viên" sheetId="4" r:id="rId4"/>
+    <sheet state="visible" name="Tổng quan" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Đăng nhập" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Quản lý người dùng" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Quản lý nhân viên" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Quản lý người dùng'!$A$2:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Danh sách nhân viên'!$A$2:$J$29</definedName>
+    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'Quản lý người dùng'!$A$2:$J$28</definedName>
+    <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">'Quản lý nhân viên'!$A$2:$J$30</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="419">
   <si>
     <t>MA TRẬN KIỂM THỬ – KIỂM THỬ TỰ ĐỘNG ORANGEHRM (Playwright)</t>
   </si>
@@ -77,10 +73,10 @@
     <t>3</t>
   </si>
   <si>
-    <t>Danh sách nhân viên (PIM)</t>
-  </si>
-  <si>
-    <t>Danh sách nhân viên</t>
+    <t xml:space="preserve">Quản lý nhân viên </t>
+  </si>
+  <si>
+    <t>Quản lý nhân viên</t>
   </si>
   <si>
     <t>BG53: Nhân viên mới thêm không hiện ngay trong danh sách, chỉ thấy khi tìm kiếm (TC-E09)
@@ -90,19 +86,33 @@
     <t>QUY ƯỚC CỘT DỮ LIỆU ĐẦU VÀO – Tập lệnh đọc bằng cách tách theo ký tự xuống dòng</t>
   </si>
   <si>
-    <t>ten_dang_nhap\nmat_khau[\nmat_khau_moi]</t>
+    <t>ten_dang_nhap
+mat_khau
+mat_khau_moi</t>
   </si>
   <si>
     <t>Dòng 0 = tên đăng nhập, dòng 1 = mật khẩu, dòng 2 tùy từng trường hợp kiểm thử</t>
   </si>
   <si>
-    <t>ten_tai_khoan_qtv\nmat_khau_qtv\nten_tai_khoan_moi\nvai_tro\ntrang_thai\nten_nhan_vien</t>
+    <t>ten_tai_khoan_qtv
+mat_khau_qtv
+ten_tai_khoan_moi
+vai_tro
+trang_thai
+ten_nhan_vien</t>
   </si>
   <si>
     <t>Trường hợp xem/tìm kiếm chỉ dùng 2–3 dòng đầu; trường hợp thêm mới dùng đủ 6 dòng</t>
   </si>
   <si>
-    <t>ten_tai_khoan_qtv\nmat_khau_qtv\nho\nten\nma_so</t>
+    <t>Danh sách nhân viên</t>
+  </si>
+  <si>
+    <t>ten_tai_khoan_qtv
+mat_khau_qtv
+ho
+ten
+ma_so</t>
   </si>
   <si>
     <t>Mã số để trống = tự động cấp; trường hợp tìm kiếm dùng dòng thứ 3 làm từ khóa</t>
@@ -185,13 +195,10 @@
 Tiêu đề trang hiển thị chữ Dashboard</t>
   </si>
   <si>
-    <t>Pass</t>
+    <t>Passed</t>
   </si>
   <si>
     <t>Không có</t>
-  </si>
-  <si>
-    <t>Trường hợp cơ bản – chạy trước mọi test khác</t>
   </si>
   <si>
     <t>TC-L02</t>
@@ -216,9 +223,6 @@
 Hiển thị thông báo thông tin không hợp lệ</t>
   </si>
   <si>
-    <t>Không được chuyển sang trang tổng quan</t>
-  </si>
-  <si>
     <t>TC-L03</t>
   </si>
   <si>
@@ -241,9 +245,6 @@
 Không có gợi ý về sự tồn tại của tài khoản</t>
   </si>
   <si>
-    <t>Chống dò tên tài khoản: nội dung thông báo phải giống TC-L02</t>
-  </si>
-  <si>
     <t>TC-L04</t>
   </si>
   <si>
@@ -314,9 +315,6 @@
 Không gọi lên hệ thống</t>
   </si>
   <si>
-    <t>Đếm số thông báo lỗi phải bằng 2</t>
-  </si>
-  <si>
     <t>Tính năng bổ trợ</t>
   </si>
   <si>
@@ -334,9 +332,6 @@
   </si>
   <si>
     <t>Đăng nhập thành công, chuyển về trang tổng quan</t>
-  </si>
-  <si>
-    <t>Thao tác bằng bàn phím</t>
   </si>
   <si>
     <t>TC-L08</t>
@@ -356,11 +351,14 @@
 3. Nhấn nút Đặt lại mật khẩu</t>
   </si>
   <si>
-    <t>Trang xác nhận đã gửi liên kết đặt lại
-Không có lỗi 5xx từ máy chủ</t>
-  </si>
-  <si>
-    <t>Fail</t>
+    <t xml:space="preserve">Trang xác nhận đã gửi liên kết đặt lại
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khi điền Admin vào form "Reset password" sau đó chọn reset thì bị lỗi 504 Gateway Timeout </t>
+  </si>
+  <si>
+    <t>Failed</t>
   </si>
   <si>
     <t>Cao</t>
@@ -386,11 +384,8 @@
 3. Nhấn Đặt lại mật khẩu</t>
   </si>
   <si>
-    <t>Thông báo giống hệt TC-L08
+    <t>Trang xác nhận đã gửi liên kết đặt lại
 Không có dấu hiệu gợi ý tài khoản sai</t>
-  </si>
-  <si>
-    <t>Chống dò tài khoản: nội dung thông báo giống TC-L08</t>
   </si>
   <si>
     <t>TC-L10</t>
@@ -417,6 +412,9 @@
 </t>
   </si>
   <si>
+    <t>Thông báo "Invalid Credentials"</t>
+  </si>
+  <si>
     <t>Sau khi đổi, đăng nhập bằng mật khẩu mới trả về thông báo không hợp lệ
 Dòng 0=tên đăng nhập, dòng 1=mật khẩu cũ, dòng 2=mật khẩu mới</t>
   </si>
@@ -442,9 +440,6 @@
   <si>
     <t>Chuyển về trang đăng nhập
 Nội dung trang tổng quan không hiển thị</t>
-  </si>
-  <si>
-    <t>Dữ liệu đầu vào là địa chỉ trang cần kiểm tra</t>
   </si>
   <si>
     <t>TC-L12</t>
@@ -464,9 +459,6 @@
     <t>Trang đăng nhập hiển thị, không thể xem lại dữ liệu cũ</t>
   </si>
   <si>
-    <t>Kiểm tra phiên làm việc bị hủy triệt để</t>
-  </si>
-  <si>
     <t>TC-L13</t>
   </si>
   <si>
@@ -541,6 +533,9 @@
 Hành vi phải nhất quán và không lỗi</t>
   </si>
   <si>
+    <t>Đăng nhập thành công (hệ thống cắt khoảng trắng)</t>
+  </si>
+  <si>
     <t>KIỂM THỬ CHỨC NĂNG – QUẢN LÝ NGƯỜI DÙNG</t>
   </si>
   <si>
@@ -564,12 +559,6 @@
     <t>Bảng danh sách hiển thị với các cột: Tên tài khoản, Vai trò, Tên nhân viên, Trạng thái</t>
   </si>
   <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Kiểm tra 4 tiêu đề cột tồn tại</t>
-  </si>
-  <si>
     <t>TC-U02</t>
   </si>
   <si>
@@ -593,9 +582,6 @@
 Có ít nhất 1 kết quả</t>
   </si>
   <si>
-    <t>Dòng thứ 3 của dữ liệu đầu vào là từ khóa tìm kiếm</t>
-  </si>
-  <si>
     <t>TC-U03</t>
   </si>
   <si>
@@ -619,9 +605,6 @@
 Bảng không có dòng dữ liệu</t>
   </si>
   <si>
-    <t>Kiểm tra số dòng trong bảng bằng 0</t>
-  </si>
-  <si>
     <t>TC-U04</t>
   </si>
   <si>
@@ -636,9 +619,6 @@
   </si>
   <si>
     <t>Tất cả kết quả đều có Vai trò là Quản trị viên</t>
-  </si>
-  <si>
-    <t>Dòng thứ 3 là vai trò cần lọc</t>
   </si>
   <si>
     <t>TC-U05</t>
@@ -660,9 +640,6 @@
   </si>
   <si>
     <t>Tất cả kết quả đều có trạng thái Đang hoạt động</t>
-  </si>
-  <si>
-    <t>Dòng thứ 3 là trạng thái cần lọc</t>
   </si>
   <si>
     <t>TC-U06</t>
@@ -687,9 +664,6 @@
     <t>Tất cả kết quả thỏa mãn cả hai điều kiện cùng lúc</t>
   </si>
   <si>
-    <t>Dòng 3=vai trò, dòng 4=trạng thái</t>
-  </si>
-  <si>
     <t>TC-U07</t>
   </si>
   <si>
@@ -708,9 +682,6 @@
 Danh sách hiển thị đầy đủ</t>
   </si>
   <si>
-    <t>Kiểm tra ô tìm kiếm đã trống sau khi xóa bộ lọc</t>
-  </si>
-  <si>
     <t>TC-U08</t>
   </si>
   <si>
@@ -721,11 +692,11 @@
   </si>
   <si>
     <t>1. Vào Quản lý người dùng
-2. Nhập 3 dấu cách vào ô Tên tài khoản
+2. Nhập 3 dấu cách vào ô Username
 3. Nhấn Tìm kiếm</t>
   </si>
   <si>
-    <t>Failed</t>
+    <t>Nhập khoảng trắng và Search vẫn hiển thị (10) Records Found</t>
   </si>
   <si>
     <t>Trung bình</t>
@@ -766,9 +737,6 @@
 Người dùng mới hiện ra khi tìm kiếm</t>
   </si>
   <si>
-    <t>Dòng 3=tên tài khoản, dòng 4=vai trò, dòng 5=trạng thái, dòng 6=tên nhân viên</t>
-  </si>
-  <si>
     <t>TC-U10</t>
   </si>
   <si>
@@ -796,9 +764,6 @@
 Người dùng mới hiện trong danh sách với vai trò Quản trị viên</t>
   </si>
   <si>
-    <t>Kiểm tra đủ hai loại vai trò: ESS và Admin</t>
-  </si>
-  <si>
     <t>TC-U11</t>
   </si>
   <si>
@@ -823,9 +788,6 @@
   <si>
     <t>Thông báo bắt buộc phải nhập tên tài khoản
 Không tạo được người dùng mới</t>
-  </si>
-  <si>
-    <t>Dòng thứ 3 rỗng tương ứng tên tài khoản trống</t>
   </si>
   <si>
     <t>TC-U12</t>
@@ -855,9 +817,6 @@
 Không tạo được người dùng mới</t>
   </si>
   <si>
-    <t>Dòng thứ 3 là tên tài khoản đã tồn tại</t>
-  </si>
-  <si>
     <t>TC-U13</t>
   </si>
   <si>
@@ -885,12 +844,6 @@
 Không lưu được người dùng</t>
   </si>
   <si>
-    <t>Thấp</t>
-  </si>
-  <si>
-    <t>Lỗi BG05/BG07 (09/04/2026): Tên tài khoản với @ và - được lưu thành công, không có kiểm tra dữ liệu</t>
-  </si>
-  <si>
     <t>TC-U14</t>
   </si>
   <si>
@@ -917,9 +870,6 @@
     <t>Thông báo tên tài khoản vượt giới hạn ký tự
 Hoặc ô nhập tự giới hạn
 Không lưu được người dùng</t>
-  </si>
-  <si>
-    <t>Lỗi BG06/BG07 (09/04/2026): Tên tài khoản dài trên 60 ký tự được lưu thành công</t>
   </si>
   <si>
     <t>TC-U15</t>
@@ -951,9 +901,6 @@
 Không tạo người dùng</t>
   </si>
   <si>
-    <t>Dòng 7=mật khẩu, dòng 8=xác nhận mật khẩu</t>
-  </si>
-  <si>
     <t>Chỉnh sửa người dùng</t>
   </si>
   <si>
@@ -975,35 +922,37 @@
 Không có trường nào bị trống bất thường</t>
   </si>
   <si>
-    <t>Dòng thứ 3 là tên tài khoản cần xem</t>
-  </si>
-  <si>
     <t>TC-U17</t>
   </si>
   <si>
-    <t>Thay đổi trạng thái hoạt động của người dùng</t>
-  </si>
-  <si>
-    <t>Thay đổi từ Đang hoạt động sang Vô hiệu hóa được lưu và hiển thị ngay</t>
+    <t>Chỉnh sửa toàn bộ thông tin người dùng</t>
+  </si>
+  <si>
+    <t>Cập nhật đầy đủ các trường có thể chỉnh sửa của người dùng và lưu lại thành công</t>
   </si>
   <si>
     <t>Admin
 admin123
-ngdung_hop_le_01
-Disabled</t>
-  </si>
-  <si>
-    <t>1. Tìm người dùng cần sửa
-2. Nhấn Chỉnh sửa
-3. Đổi trạng thái sang Vô hiệu hóa
-4. Nhấn Lưu</t>
+editfull_src_u17
+ESS
+Enabled
+Orange Test
+editfull_dst_u17
+Admin
+Disabled
+AUTO_DIFFERENT_EMPLOYEE</t>
+  </si>
+  <si>
+    <t>1. Tạo sẵn người dùng nguồn với dữ liệu ban đầu
+2. Tìm người dùng nguồn và mở màn hình Chỉnh sửa
+3. Cập nhật Vai trò, Tên nhân viên, Tên tài khoản và Trạng thái
+4. Nhấn Lưu
+5. Tìm lại theo tên tài khoản mới và mở lại màn hình Chỉnh sửa để đối chiếu</t>
   </si>
   <si>
     <t>Thông báo Cập nhật thành công
-Người dùng hiển thị trạng thái Vô hiệu hóa trong danh sách</t>
-  </si>
-  <si>
-    <t>Dòng 3=tên tài khoản, dòng 4=trạng thái mới</t>
+Danh sách hiển thị tên tài khoản, vai trò và trạng thái mới
+Màn hình Chỉnh sửa hiển thị lại đúng toàn bộ dữ liệu đã cập nhật</t>
   </si>
   <si>
     <t>Xóa người dùng</t>
@@ -1032,9 +981,6 @@
     <t>Người dùng không còn trong danh sách khi tìm kiếm lại</t>
   </si>
   <si>
-    <t>Dòng thứ 3 là tên tài khoản cần xóa</t>
-  </si>
-  <si>
     <t>TC-U19</t>
   </si>
   <si>
@@ -1053,34 +999,10 @@
 Không có cửa sổ xác nhận xuất hiện</t>
   </si>
   <si>
-    <t>Kiểm tra nút có thuộc tính disabled hoặc không hiển thị</t>
+    <t>Tích hợp</t>
   </si>
   <si>
     <t>TC-U20</t>
-  </si>
-  <si>
-    <t>Kiểm tra ô chọn hiển thị đầy đủ cho tất cả người dùng</t>
-  </si>
-  <si>
-    <t>Mỗi dòng trong danh sách phải có đúng một ô chọn để xóa</t>
-  </si>
-  <si>
-    <t>1. Vào Quản lý người dùng
-2. Đếm số dòng dữ liệu trong bảng
-3. Đếm số ô chọn</t>
-  </si>
-  <si>
-    <t>Số ô chọn bằng số dòng trong bảng
-Không có dòng nào thiếu ô chọn</t>
-  </si>
-  <si>
-    <t>Lỗi BG08 (09/04/2026): Ô chọn để xóa vắng mặt ở ít nhất một người dùng</t>
-  </si>
-  <si>
-    <t>Tích hợp</t>
-  </si>
-  <si>
-    <t>TC-U21</t>
   </si>
   <si>
     <t>Tìm kiếm ngay sau khi thêm người dùng mới</t>
@@ -1104,10 +1026,7 @@
     <t>Người dùng mới xuất hiện trong kết quả tìm kiếm</t>
   </si>
   <si>
-    <t>Không cần tải lại trang mới tìm được</t>
-  </si>
-  <si>
-    <t>TC-U22</t>
+    <t>TC-U21</t>
   </si>
   <si>
     <t>Kiểm tra thông tin người dùng sau khi lưu</t>
@@ -1132,10 +1051,7 @@
     <t>Tên tài khoản, vai trò, trạng thái hiển thị đúng với dữ liệu đã nhập</t>
   </si>
   <si>
-    <t>Kiểm tra tính nhất quán dữ liệu sau khi lưu</t>
-  </si>
-  <si>
-    <t>KIỂM THỬ CHỨC NĂNG – DANH SÁCH NHÂN VIÊN</t>
+    <t>KIỂM THỬ CHỨC NĂNG – QUẢN LÝ NHÂN VIÊN</t>
   </si>
   <si>
     <t>TC-E01</t>
@@ -1155,9 +1071,6 @@
     <t>Bảng hiển thị đầy đủ 7 cột: Mã số, Họ, Tên, Chức danh, Tình trạng việc làm, Đơn vị, Quản lý trực tiếp</t>
   </si>
   <si>
-    <t>Kiểm tra từng tiêu đề cột tồn tại</t>
-  </si>
-  <si>
     <t>TC-E02</t>
   </si>
   <si>
@@ -1180,9 +1093,6 @@
     <t>Các dòng kết quả đều có tên chứa từ khóa đã nhập</t>
   </si>
   <si>
-    <t>Dòng thứ 3 là từ khóa tìm kiếm</t>
-  </si>
-  <si>
     <t>TC-E03</t>
   </si>
   <si>
@@ -1201,9 +1111,6 @@
 2. Nhấn Tìm kiếm</t>
   </si>
   <si>
-    <t>Số dòng trong bảng bằng 0</t>
-  </si>
-  <si>
     <t>TC-E04</t>
   </si>
   <si>
@@ -1225,9 +1132,6 @@
     <t>Kết quả gồm tất cả nhân viên có tên chứa hoặc bắt đầu bằng Ora</t>
   </si>
   <si>
-    <t>Kiểm tra tìm kiếm một phần</t>
-  </si>
-  <si>
     <t>TC-E05</t>
   </si>
   <si>
@@ -1247,9 +1151,6 @@
   </si>
   <si>
     <t>Tất cả dòng kết quả có tình trạng việc làm bằng giá trị đã chọn</t>
-  </si>
-  <si>
-    <t>Dòng thứ 3 là tình trạng cần lọc</t>
   </si>
   <si>
     <t>TC-E06</t>
@@ -1272,9 +1173,6 @@
 Dữ liệu không bị mất</t>
   </si>
   <si>
-    <t>So sánh danh sách ô với danh sách đã sắp xếp</t>
-  </si>
-  <si>
     <t>TC-E07</t>
   </si>
   <si>
@@ -1292,13 +1190,46 @@
 Số lượng lớn hơn 0</t>
   </si>
   <si>
-    <t>Không bị lọc khi để trống từ khóa</t>
+    <t>TC-E08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tìm kiếm nhân viên bằng khoảng trắng
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đảm bảo hệ thống loại bỏ khoảng trắng thừa và trả về không tìm thấy kết quả thay vì hiện toàn bộ danh sách
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin
+admin123
+  </t>
+  </si>
+  <si>
+    <t>1. Vào Danh sách nhân viên (Employee List)
+2. Nhập vào ô tìm kiếm Employee Name giá trị là 3 khoảng trắng ("   ")
+3. Nhấn nút Tìm kiếm (Search)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bảng hiển thị thông báo không tìm thấy bản ghi nào ("No Records Found") và không có dòng dữ liệu nhân viên nào hiển thị.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tìm kiếm với khoảng trắng không lọc được dữ liệu, hệ thống vẫn hiển thị đầy đủ danh sách toàn bộ nhân viên.
+</t>
+  </si>
+  <si>
+    <t>Thấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lỗi bỏ qua bước chuẩn hóa đầu vào (trim whitespace) trước khi truy vấn tìm kiếm.
+</t>
   </si>
   <si>
     <t>Thêm nhân viên mới</t>
   </si>
   <si>
-    <t>TC-E08</t>
+    <t>TC-E09</t>
   </si>
   <si>
     <t>Thêm nhân viên mới với thông tin cơ bản</t>
@@ -1325,10 +1256,7 @@
 Mã số nhân viên được cấp tự động</t>
   </si>
   <si>
-    <t>Dòng 3=họ, dòng 4=tên, dòng 5=mã số (để trống=tự động)</t>
-  </si>
-  <si>
-    <t>TC-E09</t>
+    <t>TC-E10</t>
   </si>
   <si>
     <t>Nhân viên mới xuất hiện ngay trong danh sách</t>
@@ -1354,10 +1282,7 @@
 Nhân viên mới hiển thị trong danh sách ngay lập tức</t>
   </si>
   <si>
-    <t>Lỗi BG53 (09/04/2026): Nhân viên mới không hiện trong danh sách mặc định, chỉ tìm thấy khi tìm kiếm tên cụ thể</t>
-  </si>
-  <si>
-    <t>TC-E10</t>
+    <t>TC-E11</t>
   </si>
   <si>
     <t>Bỏ trống họ khi thêm nhân viên mới</t>
@@ -1382,10 +1307,7 @@
 Không tạo hồ sơ nhân viên</t>
   </si>
   <si>
-    <t>Dòng thứ 3 rỗng tương ứng Họ trống</t>
-  </si>
-  <si>
-    <t>TC-E11</t>
+    <t>TC-E12</t>
   </si>
   <si>
     <t>Bỏ trống tên khi thêm nhân viên mới</t>
@@ -1410,10 +1332,7 @@
 Không tạo hồ sơ nhân viên</t>
   </si>
   <si>
-    <t>Dòng thứ 4 rỗng tương ứng Tên trống</t>
-  </si>
-  <si>
-    <t>TC-E12</t>
+    <t>TC-E13</t>
   </si>
   <si>
     <t>Thêm nhân viên với mã số đã được sử dụng</t>
@@ -1444,7 +1363,7 @@
 Script tự lấy mã số từ dòng đầu tiên trong danh sách</t>
   </si>
   <si>
-    <t>TC-E13</t>
+    <t>TC-E14</t>
   </si>
   <si>
     <t>Tên nhân viên có chứa ký tự tiếng Việt</t>
@@ -1471,10 +1390,7 @@
 Họ tên hiển thị đúng ký tự trong danh sách</t>
   </si>
   <si>
-    <t>Kiểm tra mã hóa ký tự tiếng Việt</t>
-  </si>
-  <si>
-    <t>TC-E14</t>
+    <t>TC-E15</t>
   </si>
   <si>
     <t>Thêm nhân viên có tên đệm</t>
@@ -1500,13 +1416,10 @@
 Tên đệm hiển thị đúng trong hồ sơ nhân viên</t>
   </si>
   <si>
-    <t>Dòng 3=họ, dòng 4=tên, dòng 5=mã số, dòng 6=tên đệm</t>
-  </si>
-  <si>
     <t>Chỉnh sửa nhân viên</t>
   </si>
   <si>
-    <t>TC-E15</t>
+    <t>TC-E16</t>
   </si>
   <si>
     <t>Chỉnh sửa tên nhân viên</t>
@@ -1530,10 +1443,7 @@
 Tên mới hiển thị trong hồ sơ</t>
   </si>
   <si>
-    <t>Dòng 3=tên nhân viên cần sửa, dòng 4=tên mới</t>
-  </si>
-  <si>
-    <t>TC-E16</t>
+    <t>TC-E17</t>
   </si>
   <si>
     <t>Xác nhận thông tin được lưu sau khi tải lại trang</t>
@@ -1558,13 +1468,10 @@
 Không bị trở về giá trị cũ</t>
   </si>
   <si>
-    <t>Kiểm tra tính bền vững của dữ liệu sau lưu</t>
-  </si>
-  <si>
     <t>Xóa nhân viên</t>
   </si>
   <si>
-    <t>TC-E17</t>
+    <t>TC-E18</t>
   </si>
   <si>
     <t>Xóa nhân viên sau khi xác nhận</t>
@@ -1588,10 +1495,7 @@
 Tìm kiếm lại theo tên không có kết quả</t>
   </si>
   <si>
-    <t>Dòng thứ 3 là tên nhân viên cần xóa</t>
-  </si>
-  <si>
-    <t>TC-E18</t>
+    <t>TC-E19</t>
   </si>
   <si>
     <t>Thử xóa khi chưa chọn nhân viên nào</t>
@@ -1608,13 +1512,10 @@
     <t>Nút Xóa bị vô hiệu hóa hoặc không hiển thị</t>
   </si>
   <si>
-    <t>Kiểm tra trạng thái nút Xóa</t>
-  </si>
-  <si>
     <t>Toàn vẹn dữ liệu</t>
   </si>
   <si>
-    <t>TC-E19</t>
+    <t>TC-E20</t>
   </si>
   <si>
     <t>Tìm kiếm ngay sau khi thêm nhân viên mới</t>
@@ -1637,7 +1538,7 @@
     <t>Nhân viên mới xuất hiện trong kết quả tìm kiếm</t>
   </si>
   <si>
-    <t>TC-E20</t>
+    <t>TC-E21</t>
   </si>
   <si>
     <t>Tổng số nhân viên tăng thêm 1 sau khi thêm mới</t>
@@ -1662,10 +1563,7 @@
     <t>Tổng số sau bằng tổng số trước cộng thêm 1</t>
   </si>
   <si>
-    <t>Kiểm tra số hiển thị trong tiêu đề kết quả</t>
-  </si>
-  <si>
-    <t>TC-E21</t>
+    <t>TC-E22</t>
   </si>
   <si>
     <t>Tổng số nhân viên giảm 1 sau khi xóa</t>
@@ -1688,10 +1586,7 @@
     <t>Tổng số sau bằng tổng số trước trừ đi 1</t>
   </si>
   <si>
-    <t>Kết hợp với TC-E20 để kiểm tra cân bằng thêm/xóa</t>
-  </si>
-  <si>
-    <t>TC-E22</t>
+    <t>TC-E23</t>
   </si>
   <si>
     <t>Danh sách không có bản ghi trùng lặp khi phân trang</t>
@@ -1707,260 +1602,100 @@
   <si>
     <t>Không có mã số nào xuất hiện ở cả hai trang
 Phần giao là tập hợp rỗng</t>
-  </si>
-  <si>
-    <t>Tập(trang1) giao Tập(trang2) bằng rỗng</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="32">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="15">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="13.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
+    </font>
+    <font/>
+    <font>
+      <i/>
+      <sz val="9.0"/>
+      <color rgb="FF404040"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="9.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.0"/>
+      <color rgb="FF276221"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.0"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.0"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="12.0"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF1F3864"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF276221"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="12.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF404040"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1970,8 +1705,44 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
+        <bgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F8F0"/>
+        <bgColor rgb="FFF0F8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFAFA"/>
+        <bgColor rgb="FFFAFAFA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1988,240 +1759,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5E9"/>
-        <bgColor rgb="FFE8F5E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F8F0"/>
-        <bgColor rgb="FFF0F8F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAFAFA"/>
-        <bgColor rgb="FFFAFAFA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFE06666"/>
+        <bgColor rgb="FFE06666"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="15">
+    <border/>
     <border>
       <left/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -2236,34 +1793,27 @@
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
-      <right/>
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
       <right style="thin">
         <color rgb="FFBFBFBF"/>
       </right>
@@ -2273,27 +1823,27 @@
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
-      <right/>
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
-      <bottom/>
-      <diagonal/>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
     </border>
     <border>
       <left style="thin">
@@ -2308,45 +1858,27 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -2356,417 +1888,168 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+  <cellStyleXfs count="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  </cellStyleXfs>
+  <cellXfs count="48">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="38" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="38">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="4" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="10" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="11" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf borderId="11" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf borderId="4" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf borderId="11" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf borderId="11" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="12" fillId="10" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf borderId="13" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="14" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="11" fillId="12" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf borderId="11" fillId="12" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="4" fillId="12" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="12" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf quotePrefix="1" borderId="11" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="12" fillId="10" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="5" fillId="10" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf borderId="4" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf borderId="4" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf borderId="4" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf borderId="1" fillId="2" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
-    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
-    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
-    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
-    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
-    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
-    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
-    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
-    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
-    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
-    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
-    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
-    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
-    <cellStyle name="Total" xfId="25" builtinId="25"/>
-    <cellStyle name="Output" xfId="26" builtinId="21"/>
-    <cellStyle name="Currency" xfId="27" builtinId="4"/>
-    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
-    <cellStyle name="Note" xfId="29" builtinId="10"/>
-    <cellStyle name="Input" xfId="30" builtinId="20"/>
-    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
-    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
-    <cellStyle name="Good" xfId="33" builtinId="26"/>
-    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
-    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
-    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
-    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
-    <cellStyle name="Title" xfId="39" builtinId="15"/>
-    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
-    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
-    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
-    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
-    <cellStyle name="Comma" xfId="44" builtinId="3"/>
-    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
-    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
-    <cellStyle name="Percent" xfId="47" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <dxfs count="0"/>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -2956,26 +2239,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G1000"/>
-  <sheetFormatPr defaultColWidth="14.4333333333333" defaultRowHeight="15" customHeight="1" outlineLevelCol="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="14.1416666666667" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="26" width="8.70833333333333" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="14.14"/>
+    <col customWidth="1" min="2" max="2" width="28.0"/>
+    <col customWidth="1" min="3" max="3" width="22.0"/>
+    <col customWidth="1" min="4" max="6" width="10.0"/>
+    <col customWidth="1" min="7" max="7" width="50.0"/>
+    <col customWidth="1" min="8" max="26" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:7">
-      <c r="A1" s="30" t="s">
+    <row r="1" ht="30.0" customHeight="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
@@ -2983,10 +2266,10 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="G1" s="3"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A2" s="31" t="s">
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2"/>
@@ -2994,104 +2277,104 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="G2" s="3"/>
     </row>
-    <row r="3" ht="6" customHeight="1"/>
-    <row r="4" ht="19.5" customHeight="1" spans="1:7">
-      <c r="A4" s="3" t="s">
+    <row r="3" ht="6.0" customHeight="1"/>
+    <row r="4" ht="19.5" customHeight="1">
+      <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="55.5" customHeight="1" spans="1:7">
-      <c r="A5" s="32" t="s">
+    <row r="5" ht="55.5" customHeight="1">
+      <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="32">
-        <v>21</v>
-      </c>
-      <c r="E5" s="8">
-        <v>19</v>
-      </c>
-      <c r="F5" s="9">
-        <v>2</v>
-      </c>
-      <c r="G5" s="37" t="s">
+      <c r="D5" s="9">
+        <v>15.0</v>
+      </c>
+      <c r="E5" s="10">
+        <v>13.0</v>
+      </c>
+      <c r="F5" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="G5" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" ht="55.5" customHeight="1" spans="1:7">
-      <c r="A6" s="32" t="s">
+    <row r="6" ht="55.5" customHeight="1">
+      <c r="A6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="32">
-        <v>21</v>
-      </c>
-      <c r="E6" s="8">
+      <c r="D6" s="6">
+        <v>21.0</v>
+      </c>
+      <c r="E6" s="13">
+        <v>18.0</v>
+      </c>
+      <c r="F6" s="11">
+        <v>3.0</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" ht="55.5" customHeight="1">
+      <c r="A7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="9">
-        <v>3</v>
-      </c>
-      <c r="G6" s="37" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" ht="55.5" customHeight="1" spans="1:7">
-      <c r="A7" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="32">
-        <v>22</v>
-      </c>
-      <c r="E7" s="8">
-        <v>20</v>
-      </c>
-      <c r="F7" s="9">
-        <v>2</v>
-      </c>
-      <c r="G7" s="37" t="s">
+      <c r="D7" s="6">
+        <v>22.0</v>
+      </c>
+      <c r="E7" s="13">
+        <v>20.0</v>
+      </c>
+      <c r="F7" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" ht="13.5" customHeight="1"/>
-    <row r="9" ht="18" customHeight="1" spans="1:7">
-      <c r="A9" s="35" t="s">
+    <row r="9" ht="18.0" customHeight="1">
+      <c r="A9" s="16" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="2"/>
@@ -3099,82 +2382,82 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="G9" s="3"/>
     </row>
-    <row r="10" ht="54.75" customHeight="1" spans="1:7">
-      <c r="A10" s="32" t="s">
+    <row r="10" ht="54.75" customHeight="1">
+      <c r="A10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="10"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="20"/>
     </row>
-    <row r="11" ht="49.5" customHeight="1" spans="1:7">
-      <c r="A11" s="32" t="s">
+    <row r="11" ht="81.0" customHeight="1">
+      <c r="A11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="10"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="20"/>
     </row>
-    <row r="12" ht="49.5" customHeight="1" spans="1:7">
-      <c r="A12" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="7" t="s">
+    <row r="12" ht="63.75" customHeight="1">
+      <c r="A12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="B12" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="10"/>
+      <c r="C12" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="20"/>
     </row>
-    <row r="13" ht="37.5" customHeight="1" spans="1:7">
-      <c r="A13" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="7" t="s">
+    <row r="13" ht="37.5" customHeight="1">
+      <c r="A13" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="B13" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="10"/>
+      <c r="C13" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="20"/>
     </row>
-    <row r="14" ht="19.5" customHeight="1" spans="1:7">
-      <c r="A14" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="7" t="s">
+    <row r="14" ht="57.75" customHeight="1">
+      <c r="A14" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="B14" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="10"/>
+      <c r="C14" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="20"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -4167,33 +3450,35 @@
     <mergeCell ref="C13:G13"/>
     <mergeCell ref="C14:G14"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup paperSize="1" orientation="landscape"/>
-  <headerFooter/>
+  <printOptions/>
+  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J2000"/>
-  <sheetFormatPr defaultColWidth="14.4333333333333" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="46" customWidth="1"/>
-    <col min="6" max="6" width="44" customWidth="1"/>
-    <col min="7" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="34" customWidth="1"/>
-    <col min="11" max="26" width="8.70833333333333" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="9.0"/>
+    <col customWidth="1" min="2" max="2" width="29.43"/>
+    <col customWidth="1" min="3" max="3" width="36.0"/>
+    <col customWidth="1" min="4" max="4" width="23.43"/>
+    <col customWidth="1" min="5" max="5" width="40.29"/>
+    <col customWidth="1" min="6" max="6" width="41.29"/>
+    <col customWidth="1" min="7" max="7" width="27.43"/>
+    <col customWidth="1" min="8" max="8" width="20.0"/>
+    <col customWidth="1" min="9" max="10" width="16.14"/>
+    <col customWidth="1" min="11" max="26" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>33</v>
+    <row r="1" ht="25.5" customHeight="1">
+      <c r="A1" s="22" t="s">
+        <v>34</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4203,615 +3488,629 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="J1" s="3"/>
     </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:10">
-      <c r="A2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="2" ht="21.75" customHeight="1">
+      <c r="A2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="H2" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="I2" s="5" t="s">
         <v>43</v>
       </c>
+      <c r="J2" s="5" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:10">
-      <c r="A3" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
       <c r="J3" s="26"/>
     </row>
-    <row r="4" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A4" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="19" t="s">
+    <row r="4" ht="69.75" customHeight="1">
+      <c r="A4" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="B4" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="C4" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="D4" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="E4" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="8" t="s">
+      <c r="F4" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="I4" s="27" t="s">
+      <c r="G4" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J4" s="19" t="s">
+      <c r="I4" s="29" t="s">
         <v>53</v>
       </c>
+      <c r="J4" s="27"/>
     </row>
-    <row r="5" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A5" s="20" t="s">
+    <row r="5" ht="69.75" customHeight="1">
+      <c r="A5" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="20"/>
-      <c r="H5" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5" s="27" t="s">
+      <c r="G5" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="20" t="s">
+      <c r="I5" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="30"/>
+    </row>
+    <row r="6" ht="69.75" customHeight="1">
+      <c r="A6" s="27" t="s">
         <v>60</v>
       </c>
+      <c r="B6" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" s="27"/>
     </row>
-    <row r="6" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A6" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" s="19" t="s">
+    <row r="7" ht="69.75" customHeight="1">
+      <c r="A7" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I6" s="27" t="s">
+      <c r="B7" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="19" t="s">
-        <v>67</v>
+      <c r="I7" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="30" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="7" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A7" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="F7" s="20" t="s">
+    <row r="8" ht="69.75" customHeight="1">
+      <c r="A8" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="G7" s="20"/>
-      <c r="H7" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I7" s="27" t="s">
+      <c r="B8" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="20" t="s">
-        <v>74</v>
+      <c r="I8" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" s="27" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="8" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A8" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" s="19" t="s">
+    <row r="9" ht="69.75" customHeight="1">
+      <c r="A9" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8" s="27" t="s">
+      <c r="B9" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="19" t="s">
-        <v>81</v>
-      </c>
+      <c r="I9" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="30"/>
     </row>
-    <row r="9" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A9" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" s="20" t="s">
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="34"/>
+    </row>
+    <row r="11" ht="69.75" customHeight="1">
+      <c r="A11" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="G9" s="20"/>
-      <c r="H9" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I9" s="27" t="s">
+      <c r="B11" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="20" t="s">
-        <v>88</v>
-      </c>
+      <c r="I11" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" s="30"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:10">
-      <c r="A10" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="28"/>
+    <row r="12" ht="69.75" customHeight="1">
+      <c r="A12" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="F12" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="I12" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="J12" s="36" t="s">
+        <v>101</v>
+      </c>
     </row>
-    <row r="11" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A11" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="G11" s="20"/>
-      <c r="H11" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I11" s="27" t="s">
+    <row r="13" ht="69.75" customHeight="1">
+      <c r="A13" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J11" s="20" t="s">
-        <v>95</v>
-      </c>
+      <c r="I13" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" s="30"/>
     </row>
-    <row r="12" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A12" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" s="19" t="s">
+    <row r="14" ht="99.0" customHeight="1">
+      <c r="A14" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="F14" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="G14" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="H14" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="I14" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="F12" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="G12" s="19"/>
-      <c r="H12" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="I12" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>104</v>
+      <c r="J14" s="36" t="s">
+        <v>115</v>
       </c>
     </row>
-    <row r="13" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A13" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="G13" s="20"/>
-      <c r="H13" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I13" s="27" t="s">
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="34"/>
+    </row>
+    <row r="16" ht="69.75" customHeight="1">
+      <c r="A16" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="H16" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J13" s="20" t="s">
-        <v>111</v>
-      </c>
+      <c r="I16" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J16" s="27"/>
     </row>
-    <row r="14" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A14" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="G14" s="19"/>
-      <c r="H14" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="I14" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="J14" s="19" t="s">
-        <v>118</v>
-      </c>
+    <row r="17" ht="69.75" customHeight="1">
+      <c r="A17" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J17" s="30"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1" spans="1:10">
-      <c r="A15" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="28"/>
+    <row r="18" ht="69.75" customHeight="1">
+      <c r="A18" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="F18" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="G18" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="27" t="s">
+        <v>134</v>
+      </c>
     </row>
-    <row r="16" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A16" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="G16" s="19"/>
-      <c r="H16" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I16" s="27" t="s">
+    <row r="19" ht="69.75" customHeight="1">
+      <c r="A19" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="D19" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="G19" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J16" s="19" t="s">
-        <v>126</v>
+      <c r="I19" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J19" s="30" t="s">
+        <v>141</v>
       </c>
     </row>
-    <row r="17" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A17" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="G17" s="20"/>
-      <c r="H17" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I17" s="27" t="s">
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="34"/>
+    </row>
+    <row r="21" ht="69.75" customHeight="1">
+      <c r="A21" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="D21" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="E21" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="F21" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J17" s="20" t="s">
-        <v>132</v>
-      </c>
+      <c r="I21" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" s="31"/>
     </row>
-    <row r="18" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A18" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="D18" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="G18" s="19"/>
-      <c r="H18" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I18" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="J18" s="19" t="s">
-        <v>139</v>
-      </c>
+    <row r="22" ht="69.75" customHeight="1">
+      <c r="A22" s="41"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
     </row>
-    <row r="19" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A19" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="G19" s="20"/>
-      <c r="H19" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I19" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="J19" s="20" t="s">
-        <v>146</v>
-      </c>
+    <row r="23" ht="69.75" customHeight="1">
+      <c r="A23" s="41"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="41"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1" spans="1:10">
-      <c r="A20" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="28"/>
+    <row r="24" ht="69.75" customHeight="1">
+      <c r="A24" s="41"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="41"/>
     </row>
-    <row r="21" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A21" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="G21" s="20"/>
-      <c r="H21" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I21" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="J21" s="20"/>
+    <row r="25" ht="69.75" customHeight="1">
+      <c r="A25" s="41"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
     </row>
-    <row r="22" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
+    <row r="26" ht="69.75" customHeight="1">
+      <c r="A26" s="41"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="41"/>
     </row>
-    <row r="23" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A23" s="23"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-    </row>
-    <row r="24" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-    </row>
-    <row r="25" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A25" s="23"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-    </row>
-    <row r="26" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A26" s="23"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23"/>
-    </row>
-    <row r="27" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A27" s="23"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
+    <row r="27" ht="69.75" customHeight="1">
+      <c r="A27" s="41"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
     </row>
     <row r="28" ht="15.75" customHeight="1"/>
     <row r="29" ht="15.75" customHeight="1"/>
@@ -6794,39 +6093,44 @@
     <mergeCell ref="A15:J15"/>
     <mergeCell ref="A20:J20"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H21 H4:H9 H11:H14 H16:H19">
-      <formula1>"Fail,Pass"</formula1>
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I9 I11:I14 I16:I19 I21">
+      <formula1>"Trung bình,Thấp,Cao,Không có"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H9 H11:H14 H16:H19 H21">
+      <formula1>"Failed,Passed"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup paperSize="1" orientation="landscape"/>
-  <headerFooter/>
+  <printOptions/>
+  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:R1001"/>
-  <sheetFormatPr defaultColWidth="14.4333333333333" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="46" customWidth="1"/>
-    <col min="6" max="6" width="44" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="34" customWidth="1"/>
-    <col min="11" max="26" width="8.70833333333333" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="9.0"/>
+    <col customWidth="1" min="2" max="2" width="32.0"/>
+    <col customWidth="1" min="3" max="3" width="36.0"/>
+    <col customWidth="1" min="4" max="4" width="28.0"/>
+    <col customWidth="1" min="5" max="5" width="46.0"/>
+    <col customWidth="1" min="6" max="6" width="44.0"/>
+    <col customWidth="1" min="7" max="7" width="20.0"/>
+    <col customWidth="1" min="8" max="8" width="14.0"/>
+    <col customWidth="1" min="9" max="9" width="16.14"/>
+    <col customWidth="1" min="10" max="10" width="34.0"/>
+    <col customWidth="1" min="11" max="26" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>154</v>
+    <row r="1" ht="25.5" customHeight="1">
+      <c r="A1" s="22" t="s">
+        <v>150</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6836,779 +6140,2537 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="J1" s="3"/>
     </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:10">
-      <c r="A2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="2" ht="21.75" customHeight="1">
+      <c r="A2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="H2" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="I2" s="5" t="s">
         <v>43</v>
       </c>
+      <c r="J2" s="5" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:10">
-      <c r="A3" s="4" t="s">
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="20"/>
+    </row>
+    <row r="4" ht="69.75" customHeight="1">
+      <c r="A4" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="43" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="10"/>
+      <c r="F4" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="G4" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="H4" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" s="43"/>
     </row>
-    <row r="4" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A4" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="B4" s="6" t="s">
+    <row r="5" ht="69.75" customHeight="1">
+      <c r="A5" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="B5" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="C5" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="D5" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="13" t="s">
+      <c r="E5" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="F5" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="H5" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J4" s="6" t="s">
-        <v>162</v>
-      </c>
+      <c r="I5" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="21"/>
     </row>
-    <row r="5" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A5" s="7" t="s">
+    <row r="6" ht="69.75" customHeight="1">
+      <c r="A6" s="43" t="s">
         <v>163</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B6" s="43" t="s">
         <v>164</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C6" s="43" t="s">
         <v>165</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D6" s="43" t="s">
         <v>166</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E6" s="43" t="s">
         <v>167</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F6" s="43" t="s">
         <v>168</v>
       </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="I5" s="11" t="s">
+      <c r="G6" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="H6" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="I6" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" s="43"/>
+    </row>
+    <row r="7" ht="69.75" customHeight="1">
+      <c r="A7" s="21" t="s">
         <v>169</v>
       </c>
+      <c r="B7" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="H7" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="21"/>
     </row>
-    <row r="6" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A6" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="E6" s="6" t="s">
+    <row r="8" ht="69.75" customHeight="1">
+      <c r="A8" s="43" t="s">
         <v>174</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="B8" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="I6" s="11" t="s">
+      <c r="C8" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="F8" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="G8" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="H8" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="6" t="s">
-        <v>176</v>
-      </c>
+      <c r="I8" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" s="43"/>
     </row>
-    <row r="7" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A7" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="E7" s="7" t="s">
+    <row r="9" ht="69.75" customHeight="1">
+      <c r="A9" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="B9" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="I7" s="11" t="s">
+      <c r="C9" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="H9" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="I9" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="21"/>
     </row>
-    <row r="8" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A8" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="D8" s="6" t="s">
+    <row r="10" ht="69.75" customHeight="1">
+      <c r="A10" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="B10" s="43" t="s">
         <v>187</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="C10" s="43" t="s">
         <v>188</v>
       </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="I8" s="11" t="s">
+      <c r="D10" s="43" t="s">
+        <v>160</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="G10" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="H10" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="6" t="s">
-        <v>189</v>
-      </c>
+      <c r="I10" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="43"/>
     </row>
-    <row r="9" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A9" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B9" s="7" t="s">
+    <row r="11" ht="69.75" customHeight="1">
+      <c r="A11" s="45" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="B11" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="C11" s="43" t="s">
         <v>193</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="D11" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="45" t="s">
         <v>194</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F11" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="G11" s="45" t="s">
         <v>195</v>
       </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="I9" s="11" t="s">
+      <c r="H11" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I11" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="J11" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="K11" s="46"/>
+      <c r="L11" s="46"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="46"/>
+      <c r="P11" s="46"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="46"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="42" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="20"/>
+    </row>
+    <row r="13" ht="69.75" customHeight="1">
+      <c r="A13" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="B13" s="43" t="s">
+        <v>200</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>201</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>203</v>
+      </c>
+      <c r="F13" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="G13" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="H13" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="I13" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" s="43"/>
+    </row>
+    <row r="14" ht="69.75" customHeight="1">
+      <c r="A14" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J14" s="21"/>
+    </row>
+    <row r="15" ht="69.75" customHeight="1">
+      <c r="A15" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="B15" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>213</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>214</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>215</v>
+      </c>
+      <c r="F15" s="43" t="s">
+        <v>216</v>
+      </c>
+      <c r="G15" s="43" t="s">
+        <v>216</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J15" s="43"/>
+    </row>
+    <row r="16" ht="69.75" customHeight="1">
+      <c r="A16" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J16" s="21"/>
+    </row>
+    <row r="17" ht="69.75" customHeight="1">
+      <c r="A17" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="B17" s="43" t="s">
+        <v>224</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>225</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="F17" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="G17" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J17" s="43"/>
+    </row>
+    <row r="18" ht="99.75" customHeight="1">
+      <c r="A18" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="21"/>
+    </row>
+    <row r="19" ht="107.25" customHeight="1">
+      <c r="A19" s="45" t="s">
+        <v>235</v>
+      </c>
+      <c r="B19" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>237</v>
+      </c>
+      <c r="D19" s="43" t="s">
+        <v>238</v>
+      </c>
+      <c r="E19" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="F19" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="G19" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J19" s="43"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="42" t="s">
+        <v>241</v>
+      </c>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" ht="69.75" customHeight="1">
+      <c r="A21" s="45" t="s">
+        <v>242</v>
+      </c>
+      <c r="B21" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>160</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="F21" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="G21" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" s="43"/>
+    </row>
+    <row r="22" ht="116.25" customHeight="1">
+      <c r="A22" s="45" t="s">
+        <v>247</v>
+      </c>
+      <c r="B22" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="C22" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="D22" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="F22" s="43" t="s">
+        <v>252</v>
+      </c>
+      <c r="G22" s="43" t="s">
+        <v>252</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I22" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J22" s="43"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="20"/>
+    </row>
+    <row r="24" ht="69.75" customHeight="1">
+      <c r="A24" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I24" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J24" s="21"/>
+    </row>
+    <row r="25" ht="69.75" customHeight="1">
+      <c r="A25" s="45" t="s">
+        <v>260</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>261</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>262</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>263</v>
+      </c>
+      <c r="F25" s="43" t="s">
+        <v>264</v>
+      </c>
+      <c r="G25" s="43" t="s">
+        <v>264</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I25" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J25" s="43"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="20"/>
+    </row>
+    <row r="27" ht="69.75" customHeight="1">
+      <c r="A27" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I27" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J27" s="21"/>
+    </row>
+    <row r="28" ht="69.75" customHeight="1">
+      <c r="A28" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="B28" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="C28" s="43" t="s">
+        <v>274</v>
+      </c>
+      <c r="D28" s="43" t="s">
+        <v>275</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>276</v>
+      </c>
+      <c r="F28" s="43" t="s">
+        <v>277</v>
+      </c>
+      <c r="G28" s="43" t="s">
+        <v>277</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I28" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J28" s="43"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+  </sheetData>
+  <autoFilter ref="$A$2:$J$28"/>
+  <mergeCells count="6">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A26:J26"/>
+  </mergeCells>
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I11 I13:I19 I21:I22 I24:I25 I27:I28">
+      <formula1>"Trung bình,Thấp,Cao,Không có"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H11 H13:H19 H21:H22 H24:H25 H27:H28">
+      <formula1>"Failed,Passed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions/>
+  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="9.0"/>
+    <col customWidth="1" min="2" max="2" width="32.0"/>
+    <col customWidth="1" min="3" max="3" width="36.0"/>
+    <col customWidth="1" min="4" max="4" width="28.0"/>
+    <col customWidth="1" min="5" max="5" width="46.0"/>
+    <col customWidth="1" min="6" max="6" width="44.0"/>
+    <col customWidth="1" min="7" max="7" width="20.0"/>
+    <col customWidth="1" min="8" max="8" width="14.0"/>
+    <col customWidth="1" min="9" max="9" width="17.14"/>
+    <col customWidth="1" min="10" max="10" width="34.0"/>
+    <col customWidth="1" min="11" max="26" width="8.71"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customHeight="1">
+      <c r="A1" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="3"/>
+    </row>
+    <row r="2" ht="21.75" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="20"/>
+    </row>
+    <row r="4" ht="69.75" customHeight="1">
+      <c r="A4" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>280</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>281</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>282</v>
+      </c>
+      <c r="F4" s="43" t="s">
+        <v>283</v>
+      </c>
+      <c r="G4" s="43"/>
+      <c r="H4" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" s="43"/>
+    </row>
+    <row r="5" ht="69.75" customHeight="1">
+      <c r="A5" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="G5" s="21"/>
+      <c r="H5" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="21"/>
+    </row>
+    <row r="6" ht="69.75" customHeight="1">
+      <c r="A6" s="43" t="s">
+        <v>290</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>291</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>292</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>293</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>294</v>
+      </c>
+      <c r="F6" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" s="43"/>
+    </row>
+    <row r="7" ht="69.75" customHeight="1">
+      <c r="A7" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="G7" s="21"/>
+      <c r="H7" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="21"/>
+    </row>
+    <row r="8" ht="69.75" customHeight="1">
+      <c r="A8" s="43" t="s">
+        <v>301</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>302</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>303</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>304</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>305</v>
+      </c>
+      <c r="F8" s="43" t="s">
+        <v>306</v>
+      </c>
+      <c r="G8" s="43"/>
+      <c r="H8" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="I8" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" s="43"/>
+    </row>
+    <row r="9" ht="69.75" customHeight="1">
+      <c r="A9" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>310</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="G9" s="21"/>
+      <c r="H9" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="21"/>
+    </row>
+    <row r="10" ht="69.75" customHeight="1">
+      <c r="A10" s="43" t="s">
+        <v>312</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>313</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>314</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>315</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>316</v>
+      </c>
+      <c r="G10" s="43"/>
+      <c r="H10" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" s="29" t="s">
         <v>196</v>
       </c>
+      <c r="J10" s="43"/>
     </row>
-    <row r="10" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A10" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="I10" s="11" t="s">
+    <row r="11" ht="69.75" customHeight="1">
+      <c r="A11" s="45" t="s">
+        <v>317</v>
+      </c>
+      <c r="B11" s="45" t="s">
+        <v>318</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>319</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>320</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>321</v>
+      </c>
+      <c r="F11" s="45" t="s">
+        <v>322</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>323</v>
+      </c>
+      <c r="H11" s="44" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="I11" s="29" t="s">
+        <v>324</v>
+      </c>
+      <c r="J11" s="45" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="20"/>
+    </row>
+    <row r="13" ht="69.75" customHeight="1">
+      <c r="A13" s="45" t="s">
+        <v>327</v>
+      </c>
+      <c r="B13" s="43" t="s">
+        <v>328</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>329</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>330</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>331</v>
+      </c>
+      <c r="F13" s="43" t="s">
+        <v>332</v>
+      </c>
+      <c r="G13" s="43"/>
+      <c r="H13" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="6" t="s">
-        <v>202</v>
-      </c>
+      <c r="I13" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" s="43"/>
     </row>
-    <row r="11" ht="69.75" customHeight="1" spans="1:18">
-      <c r="A11" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
+    <row r="14" ht="69.75" customHeight="1">
+      <c r="A14" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="G14" s="21"/>
+      <c r="H14" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J14" s="21"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1" spans="1:10">
-      <c r="A12" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="10"/>
+    <row r="15" ht="69.75" customHeight="1">
+      <c r="A15" s="45" t="s">
+        <v>339</v>
+      </c>
+      <c r="B15" s="43" t="s">
+        <v>340</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>341</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>342</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>343</v>
+      </c>
+      <c r="F15" s="43" t="s">
+        <v>344</v>
+      </c>
+      <c r="G15" s="43"/>
+      <c r="H15" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J15" s="43"/>
     </row>
-    <row r="13" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A13" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="I13" s="11" t="s">
+    <row r="16" ht="69.75" customHeight="1">
+      <c r="A16" s="17" t="s">
+        <v>345</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="G16" s="21"/>
+      <c r="H16" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="J13" s="6" t="s">
-        <v>217</v>
-      </c>
+      <c r="I16" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J16" s="21"/>
     </row>
-    <row r="14" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A14" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G14" s="7"/>
-      <c r="H14" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="I14" s="11" t="s">
+    <row r="17" ht="69.75" customHeight="1">
+      <c r="A17" s="45" t="s">
+        <v>351</v>
+      </c>
+      <c r="B17" s="43" t="s">
+        <v>352</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>353</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>354</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>355</v>
+      </c>
+      <c r="F17" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="G17" s="43"/>
+      <c r="H17" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="I17" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="J17" s="43" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="18" ht="69.75" customHeight="1">
+      <c r="A18" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="G18" s="21"/>
+      <c r="H18" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="J14" s="7" t="s">
-        <v>224</v>
-      </c>
+      <c r="I18" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="21"/>
     </row>
-    <row r="15" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A15" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="I15" s="11" t="s">
+    <row r="19" ht="69.75" customHeight="1">
+      <c r="A19" s="45" t="s">
+        <v>364</v>
+      </c>
+      <c r="B19" s="43" t="s">
+        <v>365</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>366</v>
+      </c>
+      <c r="D19" s="43" t="s">
+        <v>367</v>
+      </c>
+      <c r="E19" s="43" t="s">
+        <v>368</v>
+      </c>
+      <c r="F19" s="43" t="s">
+        <v>369</v>
+      </c>
+      <c r="G19" s="43"/>
+      <c r="H19" s="44" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="I19" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J19" s="43"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="42" t="s">
+        <v>370</v>
+      </c>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" ht="69.75" customHeight="1">
+      <c r="A21" s="45" t="s">
+        <v>371</v>
+      </c>
+      <c r="B21" s="43" t="s">
+        <v>372</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>373</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>374</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>375</v>
+      </c>
+      <c r="F21" s="43" t="s">
+        <v>376</v>
+      </c>
+      <c r="G21" s="43"/>
+      <c r="H21" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="J15" s="6" t="s">
-        <v>231</v>
-      </c>
+      <c r="I21" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" s="43"/>
     </row>
-    <row r="16" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A16" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="I16" s="11" t="s">
+    <row r="22" ht="69.75" customHeight="1">
+      <c r="A22" s="17" t="s">
+        <v>377</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="G22" s="21"/>
+      <c r="H22" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="J16" s="7" t="s">
-        <v>238</v>
-      </c>
+      <c r="I22" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J22" s="21"/>
     </row>
-    <row r="17" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A17" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="I17" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>246</v>
-      </c>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="42" t="s">
+        <v>383</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="20"/>
     </row>
-    <row r="18" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A18" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="G18" s="7"/>
-      <c r="H18" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="I18" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>253</v>
-      </c>
+    <row r="24" ht="69.75" customHeight="1">
+      <c r="A24" s="17" t="s">
+        <v>384</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="G24" s="21"/>
+      <c r="H24" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="I24" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J24" s="21"/>
     </row>
-    <row r="19" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A19" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="I19" s="11" t="s">
+    <row r="25" ht="69.75" customHeight="1">
+      <c r="A25" s="45" t="s">
+        <v>390</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>391</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>392</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>393</v>
+      </c>
+      <c r="F25" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="G25" s="43"/>
+      <c r="H25" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="J19" s="6" t="s">
-        <v>260</v>
-      </c>
+      <c r="I25" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J25" s="43"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1" spans="1:10">
-      <c r="A20" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="10"/>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="42" t="s">
+        <v>395</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="20"/>
     </row>
-    <row r="21" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A21" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="I21" s="11" t="s">
+    <row r="27" ht="69.75" customHeight="1">
+      <c r="A27" s="45" t="s">
+        <v>396</v>
+      </c>
+      <c r="B27" s="43" t="s">
+        <v>397</v>
+      </c>
+      <c r="C27" s="43" t="s">
+        <v>398</v>
+      </c>
+      <c r="D27" s="43" t="s">
+        <v>399</v>
+      </c>
+      <c r="E27" s="43" t="s">
+        <v>400</v>
+      </c>
+      <c r="F27" s="43" t="s">
+        <v>401</v>
+      </c>
+      <c r="G27" s="43"/>
+      <c r="H27" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="J21" s="6" t="s">
-        <v>267</v>
-      </c>
+      <c r="I27" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J27" s="43"/>
     </row>
-    <row r="22" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A22" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="G22" s="7"/>
-      <c r="H22" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="I22" s="11" t="s">
+    <row r="28" ht="69.75" customHeight="1">
+      <c r="A28" s="17" t="s">
+        <v>402</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>404</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>406</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>407</v>
+      </c>
+      <c r="G28" s="21"/>
+      <c r="H28" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="7" t="s">
-        <v>274</v>
-      </c>
+      <c r="I28" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J28" s="21"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1" spans="1:10">
-      <c r="A23" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="10"/>
+    <row r="29" ht="69.75" customHeight="1">
+      <c r="A29" s="45" t="s">
+        <v>408</v>
+      </c>
+      <c r="B29" s="43" t="s">
+        <v>409</v>
+      </c>
+      <c r="C29" s="43" t="s">
+        <v>410</v>
+      </c>
+      <c r="D29" s="43" t="s">
+        <v>411</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>412</v>
+      </c>
+      <c r="F29" s="43" t="s">
+        <v>413</v>
+      </c>
+      <c r="G29" s="43"/>
+      <c r="H29" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="I29" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J29" s="43"/>
     </row>
-    <row r="24" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A24" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="G24" s="7"/>
-      <c r="H24" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="I24" s="11" t="s">
+    <row r="30" ht="69.75" customHeight="1">
+      <c r="A30" s="17" t="s">
+        <v>414</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>416</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>417</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>418</v>
+      </c>
+      <c r="G30" s="21"/>
+      <c r="H30" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="J24" s="7" t="s">
-        <v>282</v>
-      </c>
+      <c r="I30" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="J30" s="21"/>
     </row>
-    <row r="25" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A25" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="26" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A26" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="G26" s="7"/>
-      <c r="H26" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="I26" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1" spans="1:10">
-      <c r="A27" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="10"/>
-    </row>
-    <row r="28" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A28" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="G28" s="7"/>
-      <c r="H28" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="29" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A29" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="G29" s="6"/>
-      <c r="H29" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1"/>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
@@ -8581,1811 +9643,26 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A2:J29">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="$A$2:$J$30"/>
   <mergeCells count="6">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A26:J26"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I11 I13:I19 I21:I22 I24:I26 I28:I29">
-      <formula1>"Không có,Thấp,Cao"</formula1>
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I11 I13:I19 I21:I22 I24:I25 I27:I30">
+      <formula1>"Trung bình,Thấp,Cao,Không có"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H11 H13:H19 H21:H22 H24:H26 H28:H29">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H11 H13:H19 H21:H22 H24:H25 H27:H30">
       <formula1>"Failed,Passed"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup paperSize="1" orientation="landscape"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J1000"/>
-  <sheetFormatPr defaultColWidth="14.4333333333333" defaultRowHeight="15" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="46" customWidth="1"/>
-    <col min="6" max="6" width="44" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="34" customWidth="1"/>
-    <col min="11" max="26" width="8.70833333333333" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25.5" customHeight="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-    </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:10">
-      <c r="A2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:10">
-      <c r="A3" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="10"/>
-    </row>
-    <row r="4" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A4" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="5" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A5" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="6" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A6" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="7" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A7" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="8" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A8" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="9" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A9" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="10" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A10" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" spans="1:10">
-      <c r="A11" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="10"/>
-    </row>
-    <row r="12" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A12" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="G12" s="6"/>
-      <c r="H12" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="13" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A13" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="G13" s="7"/>
-      <c r="H13" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="14" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A14" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="15" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A15" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="G15" s="7"/>
-      <c r="H15" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="16" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A16" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="17" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A17" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="G17" s="7"/>
-      <c r="H17" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="18" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A18" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>403</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>404</v>
-      </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" spans="1:10">
-      <c r="A19" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="10"/>
-    </row>
-    <row r="20" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A20" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>410</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>412</v>
-      </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="21" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A21" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="G21" s="7"/>
-      <c r="H21" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" spans="1:10">
-      <c r="A22" s="4" t="s">
-        <v>421</v>
-      </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="10"/>
-    </row>
-    <row r="23" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A23" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="G23" s="7"/>
-      <c r="H23" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="24" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A24" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>430</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>431</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1" spans="1:10">
-      <c r="A25" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="10"/>
-    </row>
-    <row r="26" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A26" s="6" t="s">
-        <v>436</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>441</v>
-      </c>
-      <c r="G26" s="6"/>
-      <c r="H26" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="27" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A27" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="G27" s="7"/>
-      <c r="H27" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="28" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A28" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>450</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>452</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>453</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="G28" s="6"/>
-      <c r="H28" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="29" ht="69.75" customHeight="1" spans="1:10">
-      <c r="A29" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>457</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="G29" s="7"/>
-      <c r="H29" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
-  </sheetData>
-  <autoFilter ref="A2:J29">
-    <extLst/>
-  </autoFilter>
-  <mergeCells count="6">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A25:J25"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup paperSize="1" orientation="landscape"/>
-  <headerFooter/>
+  <printOptions/>
+  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Testcase-OrangeHRM.xlsx
+++ b/Testcase-OrangeHRM.xlsx
@@ -3558,8 +3558,10 @@
       <c r="G4" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="H4" s="10" t="s">
-        <v>52</v>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I4" s="29" t="s">
         <v>53</v>
@@ -3588,8 +3590,10 @@
       <c r="G5" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="H5" s="10" t="s">
-        <v>52</v>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I5" s="29" t="s">
         <v>53</v>
@@ -3618,8 +3622,10 @@
       <c r="G6" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="H6" s="10" t="s">
-        <v>52</v>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I6" s="29" t="s">
         <v>53</v>
@@ -3648,8 +3654,10 @@
       <c r="G7" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="H7" s="10" t="s">
-        <v>52</v>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I7" s="29" t="s">
         <v>53</v>
@@ -3680,8 +3688,10 @@
       <c r="G8" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="H8" s="10" t="s">
-        <v>52</v>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I8" s="29" t="s">
         <v>53</v>
@@ -3712,8 +3722,10 @@
       <c r="G9" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="H9" s="10" t="s">
-        <v>52</v>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I9" s="29" t="s">
         <v>53</v>
@@ -3756,8 +3768,10 @@
       <c r="G11" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="H11" s="10" t="s">
-        <v>52</v>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I11" s="29" t="s">
         <v>53</v>
@@ -3786,8 +3800,10 @@
       <c r="G12" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="H12" s="37" t="s">
-        <v>99</v>
+      <c r="H12" s="37" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
       </c>
       <c r="I12" s="38" t="s">
         <v>100</v>
@@ -3818,8 +3834,10 @@
       <c r="G13" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="H13" s="10" t="s">
-        <v>52</v>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I13" s="29" t="s">
         <v>53</v>
@@ -3848,8 +3866,10 @@
       <c r="G14" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="H14" s="37" t="s">
-        <v>99</v>
+      <c r="H14" s="37" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
       </c>
       <c r="I14" s="38" t="s">
         <v>100</v>
@@ -3894,8 +3914,10 @@
       <c r="G16" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="H16" s="10" t="s">
-        <v>52</v>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I16" s="29" t="s">
         <v>53</v>
@@ -3924,8 +3946,10 @@
       <c r="G17" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="H17" s="10" t="s">
-        <v>52</v>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I17" s="29" t="s">
         <v>53</v>
@@ -3954,8 +3978,10 @@
       <c r="G18" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="H18" s="10" t="s">
-        <v>52</v>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I18" s="29" t="s">
         <v>53</v>
@@ -3986,8 +4012,10 @@
       <c r="G19" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="H19" s="10" t="s">
-        <v>52</v>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I19" s="29" t="s">
         <v>53</v>
@@ -4032,8 +4060,10 @@
       <c r="G21" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="H21" s="10" t="s">
-        <v>52</v>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I21" s="29" t="s">
         <v>53</v>
@@ -6210,8 +6240,10 @@
       <c r="G4" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="H4" s="44" t="s">
-        <v>52</v>
+      <c r="H4" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I4" s="29" t="s">
         <v>53</v>
@@ -6240,8 +6272,10 @@
       <c r="G5" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="H5" s="10" t="s">
-        <v>52</v>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I5" s="29" t="s">
         <v>53</v>
@@ -6270,8 +6304,10 @@
       <c r="G6" s="43" t="s">
         <v>168</v>
       </c>
-      <c r="H6" s="10" t="s">
-        <v>52</v>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I6" s="29" t="s">
         <v>53</v>
@@ -6300,8 +6336,10 @@
       <c r="G7" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="H7" s="44" t="s">
-        <v>52</v>
+      <c r="H7" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I7" s="29" t="s">
         <v>53</v>
@@ -6330,8 +6368,10 @@
       <c r="G8" s="43" t="s">
         <v>179</v>
       </c>
-      <c r="H8" s="10" t="s">
-        <v>52</v>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I8" s="29" t="s">
         <v>53</v>
@@ -6360,8 +6400,10 @@
       <c r="G9" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="H9" s="10" t="s">
-        <v>52</v>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I9" s="29" t="s">
         <v>53</v>
@@ -6390,8 +6432,10 @@
       <c r="G10" s="43" t="s">
         <v>190</v>
       </c>
-      <c r="H10" s="10" t="s">
-        <v>52</v>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I10" s="29" t="s">
         <v>53</v>
@@ -6420,8 +6464,10 @@
       <c r="G11" s="45" t="s">
         <v>195</v>
       </c>
-      <c r="H11" s="10" t="s">
-        <v>99</v>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
       </c>
       <c r="I11" s="29" t="s">
         <v>196</v>
@@ -6474,8 +6520,10 @@
       <c r="G13" s="43" t="s">
         <v>204</v>
       </c>
-      <c r="H13" s="44" t="s">
-        <v>52</v>
+      <c r="H13" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I13" s="29" t="s">
         <v>53</v>
@@ -6504,8 +6552,10 @@
       <c r="G14" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="H14" s="10" t="s">
-        <v>52</v>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I14" s="29" t="s">
         <v>53</v>
@@ -6534,8 +6584,10 @@
       <c r="G15" s="43" t="s">
         <v>216</v>
       </c>
-      <c r="H15" s="10" t="s">
-        <v>52</v>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I15" s="29" t="s">
         <v>53</v>
@@ -6564,8 +6616,10 @@
       <c r="G16" s="21" t="s">
         <v>222</v>
       </c>
-      <c r="H16" s="10" t="s">
-        <v>52</v>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I16" s="29" t="s">
         <v>53</v>
@@ -6594,8 +6648,10 @@
       <c r="G17" s="43" t="s">
         <v>228</v>
       </c>
-      <c r="H17" s="10" t="s">
-        <v>52</v>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I17" s="29" t="s">
         <v>53</v>
@@ -6624,8 +6680,10 @@
       <c r="G18" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="H18" s="10" t="s">
-        <v>52</v>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I18" s="29" t="s">
         <v>53</v>
@@ -6654,8 +6712,10 @@
       <c r="G19" s="43" t="s">
         <v>240</v>
       </c>
-      <c r="H19" s="10" t="s">
-        <v>52</v>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I19" s="29" t="s">
         <v>53</v>
@@ -6698,8 +6758,10 @@
       <c r="G21" s="43" t="s">
         <v>246</v>
       </c>
-      <c r="H21" s="10" t="s">
-        <v>52</v>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I21" s="29" t="s">
         <v>53</v>
@@ -6728,8 +6790,10 @@
       <c r="G22" s="43" t="s">
         <v>252</v>
       </c>
-      <c r="H22" s="10" t="s">
-        <v>52</v>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I22" s="29" t="s">
         <v>53</v>
@@ -6772,8 +6836,10 @@
       <c r="G24" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="H24" s="10" t="s">
-        <v>52</v>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I24" s="29" t="s">
         <v>53</v>
@@ -6802,8 +6868,10 @@
       <c r="G25" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="H25" s="10" t="s">
-        <v>52</v>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I25" s="29" t="s">
         <v>53</v>
@@ -6846,8 +6914,10 @@
       <c r="G27" s="21" t="s">
         <v>271</v>
       </c>
-      <c r="H27" s="10" t="s">
-        <v>52</v>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I27" s="29" t="s">
         <v>53</v>
@@ -6876,8 +6946,10 @@
       <c r="G28" s="43" t="s">
         <v>277</v>
       </c>
-      <c r="H28" s="10" t="s">
-        <v>52</v>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I28" s="29" t="s">
         <v>53</v>
@@ -7981,8 +8053,10 @@
         <v>283</v>
       </c>
       <c r="G4" s="43"/>
-      <c r="H4" s="44" t="s">
-        <v>52</v>
+      <c r="H4" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I4" s="29" t="s">
         <v>53</v>
@@ -8009,8 +8083,10 @@
         <v>289</v>
       </c>
       <c r="G5" s="21"/>
-      <c r="H5" s="44" t="s">
-        <v>52</v>
+      <c r="H5" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I5" s="29" t="s">
         <v>53</v>
@@ -8037,8 +8113,10 @@
         <v>168</v>
       </c>
       <c r="G6" s="43"/>
-      <c r="H6" s="44" t="s">
-        <v>52</v>
+      <c r="H6" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I6" s="29" t="s">
         <v>53</v>
@@ -8065,8 +8143,10 @@
         <v>300</v>
       </c>
       <c r="G7" s="21"/>
-      <c r="H7" s="44" t="s">
-        <v>52</v>
+      <c r="H7" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I7" s="29" t="s">
         <v>53</v>
@@ -8093,8 +8173,10 @@
         <v>306</v>
       </c>
       <c r="G8" s="43"/>
-      <c r="H8" s="44" t="s">
-        <v>52</v>
+      <c r="H8" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I8" s="29" t="s">
         <v>53</v>
@@ -8121,8 +8203,10 @@
         <v>311</v>
       </c>
       <c r="G9" s="21"/>
-      <c r="H9" s="44" t="s">
-        <v>52</v>
+      <c r="H9" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I9" s="29" t="s">
         <v>53</v>
@@ -8149,8 +8233,10 @@
         <v>316</v>
       </c>
       <c r="G10" s="43"/>
-      <c r="H10" s="44" t="s">
-        <v>52</v>
+      <c r="H10" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I10" s="29" t="s">
         <v>196</v>
@@ -8225,8 +8311,10 @@
         <v>332</v>
       </c>
       <c r="G13" s="43"/>
-      <c r="H13" s="44" t="s">
-        <v>52</v>
+      <c r="H13" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I13" s="29" t="s">
         <v>53</v>
@@ -8253,8 +8341,10 @@
         <v>338</v>
       </c>
       <c r="G14" s="21"/>
-      <c r="H14" s="44" t="s">
-        <v>52</v>
+      <c r="H14" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I14" s="29" t="s">
         <v>53</v>
@@ -8281,8 +8371,10 @@
         <v>344</v>
       </c>
       <c r="G15" s="43"/>
-      <c r="H15" s="44" t="s">
-        <v>52</v>
+      <c r="H15" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I15" s="29" t="s">
         <v>53</v>
@@ -8309,8 +8401,10 @@
         <v>350</v>
       </c>
       <c r="G16" s="21"/>
-      <c r="H16" s="44" t="s">
-        <v>52</v>
+      <c r="H16" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I16" s="29" t="s">
         <v>53</v>
@@ -8337,8 +8431,10 @@
         <v>356</v>
       </c>
       <c r="G17" s="43"/>
-      <c r="H17" s="44" t="s">
-        <v>99</v>
+      <c r="H17" s="44" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
       </c>
       <c r="I17" s="29" t="s">
         <v>100</v>
@@ -8367,8 +8463,10 @@
         <v>363</v>
       </c>
       <c r="G18" s="21"/>
-      <c r="H18" s="44" t="s">
-        <v>52</v>
+      <c r="H18" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I18" s="29" t="s">
         <v>53</v>
@@ -8397,7 +8495,7 @@
       <c r="G19" s="43"/>
       <c r="H19" s="44" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="I19" s="29" t="s">
@@ -8439,8 +8537,10 @@
         <v>376</v>
       </c>
       <c r="G21" s="43"/>
-      <c r="H21" s="44" t="s">
-        <v>52</v>
+      <c r="H21" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I21" s="29" t="s">
         <v>53</v>
@@ -8467,8 +8567,10 @@
         <v>382</v>
       </c>
       <c r="G22" s="21"/>
-      <c r="H22" s="44" t="s">
-        <v>52</v>
+      <c r="H22" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I22" s="29" t="s">
         <v>53</v>
@@ -8509,8 +8611,10 @@
         <v>389</v>
       </c>
       <c r="G24" s="21"/>
-      <c r="H24" s="44" t="s">
-        <v>52</v>
+      <c r="H24" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I24" s="29" t="s">
         <v>53</v>
@@ -8537,8 +8641,10 @@
         <v>394</v>
       </c>
       <c r="G25" s="43"/>
-      <c r="H25" s="44" t="s">
-        <v>52</v>
+      <c r="H25" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I25" s="29" t="s">
         <v>53</v>
@@ -8579,8 +8685,10 @@
         <v>401</v>
       </c>
       <c r="G27" s="43"/>
-      <c r="H27" s="44" t="s">
-        <v>52</v>
+      <c r="H27" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I27" s="29" t="s">
         <v>53</v>
@@ -8607,8 +8715,10 @@
         <v>407</v>
       </c>
       <c r="G28" s="21"/>
-      <c r="H28" s="44" t="s">
-        <v>52</v>
+      <c r="H28" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I28" s="29" t="s">
         <v>53</v>
@@ -8635,8 +8745,10 @@
         <v>413</v>
       </c>
       <c r="G29" s="43"/>
-      <c r="H29" s="44" t="s">
-        <v>52</v>
+      <c r="H29" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I29" s="29" t="s">
         <v>53</v>
@@ -8663,8 +8775,10 @@
         <v>418</v>
       </c>
       <c r="G30" s="21"/>
-      <c r="H30" s="44" t="s">
-        <v>52</v>
+      <c r="H30" s="44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
       </c>
       <c r="I30" s="29" t="s">
         <v>53</v>
